--- a/Inputs/Time_Series.xlsx
+++ b/Inputs/Time_Series.xlsx
@@ -13,18 +13,16 @@
     <sheet name="network" sheetId="4" r:id="rId4"/>
     <sheet name="slack_bus" sheetId="5" r:id="rId5"/>
     <sheet name="fleet_bus" sheetId="6" r:id="rId6"/>
-    <sheet name="Sheet4" sheetId="7" r:id="rId7"/>
-    <sheet name="tariff_ladder" sheetId="8" r:id="rId8"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId7"/>
   </externalReferences>
   <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t>fleet_bus</t>
   </si>
@@ -60,24 +58,6 @@
   </si>
   <si>
     <t>S_max</t>
-  </si>
-  <si>
-    <t>vmin</t>
-  </si>
-  <si>
-    <t>vmax</t>
-  </si>
-  <si>
-    <t>v0_flag</t>
-  </si>
-  <si>
-    <t>step</t>
-  </si>
-  <si>
-    <t>lambda_bar</t>
-  </si>
-  <si>
-    <t>lambda_base</t>
   </si>
 </sst>
 </file>
@@ -5726,570 +5706,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>0.95</v>
-      </c>
-      <c r="C2">
-        <v>1.05</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>0.95</v>
-      </c>
-      <c r="C3">
-        <v>1.05</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>0.95</v>
-      </c>
-      <c r="C4">
-        <v>1.05</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>3</v>
-      </c>
-      <c r="K4">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>0.95</v>
-      </c>
-      <c r="C5">
-        <v>1.05</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>0.95</v>
-      </c>
-      <c r="C6">
-        <v>1.05</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>0.95</v>
-      </c>
-      <c r="C7">
-        <v>1.05</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>0.95</v>
-      </c>
-      <c r="C8">
-        <v>1.05</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>0.95</v>
-      </c>
-      <c r="C9">
-        <v>1.05</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>0.95</v>
-      </c>
-      <c r="C10">
-        <v>1.05</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>0.95</v>
-      </c>
-      <c r="C11">
-        <v>1.05</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12">
-        <v>0.95</v>
-      </c>
-      <c r="C12">
-        <v>1.05</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13">
-        <v>0.95</v>
-      </c>
-      <c r="C13">
-        <v>1.05</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14">
-        <v>0.95</v>
-      </c>
-      <c r="C14">
-        <v>1.05</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15">
-        <v>0.95</v>
-      </c>
-      <c r="C15">
-        <v>1.05</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16">
-        <v>0.95</v>
-      </c>
-      <c r="C16">
-        <v>1.05</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17">
-        <v>0.95</v>
-      </c>
-      <c r="C17">
-        <v>1.05</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18">
-        <v>0.95</v>
-      </c>
-      <c r="C18">
-        <v>1.05</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19">
-        <v>0.95</v>
-      </c>
-      <c r="C19">
-        <v>1.05</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20">
-        <v>0.95</v>
-      </c>
-      <c r="C20">
-        <v>1.05</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21">
-        <v>0.95</v>
-      </c>
-      <c r="C21">
-        <v>1.05</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22">
-        <v>0.95</v>
-      </c>
-      <c r="C22">
-        <v>1.05</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23">
-        <v>0.95</v>
-      </c>
-      <c r="C23">
-        <v>1.05</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24">
-        <v>0.95</v>
-      </c>
-      <c r="C24">
-        <v>1.05</v>
-      </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25">
-        <v>0.95</v>
-      </c>
-      <c r="C25">
-        <v>1.05</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26">
-        <v>0.95</v>
-      </c>
-      <c r="C26">
-        <v>1.05</v>
-      </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27">
-        <v>0.95</v>
-      </c>
-      <c r="C27">
-        <v>1.05</v>
-      </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28">
-        <v>0.95</v>
-      </c>
-      <c r="C28">
-        <v>1.05</v>
-      </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29">
-        <v>0.95</v>
-      </c>
-      <c r="C29">
-        <v>1.05</v>
-      </c>
-      <c r="D29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30">
-        <v>0.95</v>
-      </c>
-      <c r="C30">
-        <v>1.05</v>
-      </c>
-      <c r="D30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="B31">
-        <v>0.95</v>
-      </c>
-      <c r="C31">
-        <v>1.05</v>
-      </c>
-      <c r="D31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32">
-        <v>31</v>
-      </c>
-      <c r="B32">
-        <v>0.95</v>
-      </c>
-      <c r="C32">
-        <v>1.05</v>
-      </c>
-      <c r="D32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33">
-        <v>0.95</v>
-      </c>
-      <c r="C33">
-        <v>1.05</v>
-      </c>
-      <c r="D33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34">
-        <v>0.95</v>
-      </c>
-      <c r="C34">
-        <v>1.05</v>
-      </c>
-      <c r="D34">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="8">
-        <v>1</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="8">
-        <v>2</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="8">
-        <v>3</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="8">
-        <v>4</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Inputs/Time_Series.xlsx
+++ b/Inputs/Time_Series.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="load_profile" sheetId="1" r:id="rId1"/>
@@ -154,6 +154,743 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="151182336"/>
+        <c:axId val="151831296"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="151182336"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="151831296"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="151831296"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="151182336"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="6.5113517060367457E-2"/>
+          <c:y val="7.4548702245552642E-2"/>
+          <c:w val="0.70903871391076112"/>
+          <c:h val="0.8326195683872849"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>load_profile!$C$28:$C$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>0.47601400000000005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.47601400000000005</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.47601400000000005</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.48281400000000008</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.63986399999999988</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.72656399999999988</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.81411399999999989</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.1036970292500001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.6855196082499999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.0920813375000025</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7.4582971000000011</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.2826433499999996</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.0203896625</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.94076399999999982</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.88381399999999977</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.82710050824999992</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.7234262124999999</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.9990951582499985</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.4540900417499998</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.08541677925</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1.7724499667500004</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2.03244194575</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2.4538162792499998</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.66370445500000008</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="152183552"/>
+        <c:axId val="152185088"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="152183552"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="152185088"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="152185088"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="152183552"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>load_profile!$W$2:$W$25</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.7999999999999996E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.3750000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.15045</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.23800000000000002</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.3281</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.40375</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.4471</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.45135000000000003</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.44540000000000002</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.41394999999999998</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.36464999999999997</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.30769999999999997</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.22355</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.12834999999999999</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>5.525E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>8.5000000000000006E-3</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="152205184"/>
+        <c:axId val="152206720"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="152205184"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="152206720"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="152206720"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="152205184"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>load_profile!$S$2:$S$25</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>0.30869999999999997</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.30869999999999997</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.30869999999999997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.30869999999999997</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.40879999999999994</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.40879999999999994</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.40879999999999994</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.40879999999999994</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.40879999999999994</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.40879999999999994</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.40879999999999994</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.40879999999999994</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.40879999999999994</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.40879999999999994</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.40879999999999994</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.40879999999999994</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.33319999999999994</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.33319999999999994</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.33319999999999994</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.33319999999999994</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.33319999999999994</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.40879999999999994</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.40879999999999994</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.30869999999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="152239104"/>
+        <c:axId val="152371968"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="152239104"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="152371968"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="152371968"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="152239104"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>327660</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>784860</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>358140</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>815340</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>160020</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>617220</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>617220</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>502920</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -331,9 +1068,6 @@
           </cell>
         </row>
         <row r="23">
-          <cell r="B23">
-            <v>0.09</v>
-          </cell>
           <cell r="G23">
             <v>0.48171700000000001</v>
           </cell>
@@ -695,7 +1429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AH28"/>
+  <dimension ref="A1:AH54"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="7"/>
@@ -815,135 +1549,134 @@
         <v>0</v>
       </c>
       <c r="B2" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G3)*0.1</f>
+        <f>([1]Basic_load!$B$2*[1]Basic_load!G3)*0.85</f>
         <v>0</v>
       </c>
       <c r="C2" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G3)*0.1</f>
-        <v>5.6000000000000006E-4</v>
+        <f>([1]Basic_load!$B$3*[1]Basic_load!G3)*0.85</f>
+        <v>4.7600000000000003E-3</v>
       </c>
       <c r="D2" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G3)*0.1</f>
-        <v>5.04E-4</v>
+        <f>([1]Basic_load!$B$4*[1]Basic_load!G3)*0.85</f>
+        <v>4.2840000000000005E-3</v>
       </c>
       <c r="E2" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G3)*0.1</f>
-        <v>5.6000000000000006E-4</v>
+        <f>([1]Basic_load!$B$5*[1]Basic_load!G3)*0.85</f>
+        <v>4.7600000000000003E-3</v>
       </c>
       <c r="F2" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G3)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$6*[1]Basic_load!G3)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="G2" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G3)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$7*[1]Basic_load!G3)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="H2" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G3)*0.1</f>
-        <v>1.1200000000000001E-3</v>
+        <f>([1]Basic_load!$B$8*[1]Basic_load!G3)*0.85</f>
+        <v>9.5200000000000007E-3</v>
       </c>
       <c r="I2" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G3)*0.1</f>
-        <v>1.1200000000000001E-3</v>
+        <f>([1]Basic_load!$B$9*[1]Basic_load!G3)*0.85</f>
+        <v>9.5200000000000007E-3</v>
       </c>
       <c r="J2" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G3)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$10*[1]Basic_load!G3)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="K2" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G3)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$11*[1]Basic_load!G3)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="L2" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G3)*0.1</f>
-        <v>2.52E-4</v>
+        <f>([1]Basic_load!$B$12*[1]Basic_load!G3)*0.85</f>
+        <v>2.1420000000000002E-3</v>
       </c>
       <c r="M2" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G3)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$13*[1]Basic_load!G3)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="N2" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G3)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$14*[1]Basic_load!G3)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="O2" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G3)*0.1</f>
-        <v>6.7200000000000007E-4</v>
+        <f>([1]Basic_load!$B$15*[1]Basic_load!G3)*0.85</f>
+        <v>5.7120000000000001E-3</v>
       </c>
       <c r="P2" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G3)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$16*[1]Basic_load!G3)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="Q2" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G3)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$17*[1]Basic_load!G3)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="R2" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G3)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$18*[1]Basic_load!G3)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="S2" s="8">
+        <v>0.30869999999999997</v>
+      </c>
+      <c r="T2" s="7">
+        <f>([1]Basic_load!$B$20*[1]Basic_load!G3)*0.85</f>
+        <v>4.2840000000000005E-3</v>
+      </c>
+      <c r="U2" s="7">
+        <f>([1]Basic_load!$B$21*[1]Basic_load!G3)*0.85</f>
+        <v>4.2840000000000005E-3</v>
+      </c>
+      <c r="V2" s="7">
+        <f>([1]Basic_load!$B$22*[1]Basic_load!G3)*0.85</f>
+        <v>4.2840000000000005E-3</v>
+      </c>
+      <c r="W2" s="7">
         <v>0</v>
       </c>
-      <c r="T2" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G3)*0.1</f>
-        <v>5.04E-4</v>
-      </c>
-      <c r="U2" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G3)*0.1</f>
-        <v>5.04E-4</v>
-      </c>
-      <c r="V2" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G3)*0.1</f>
-        <v>5.04E-4</v>
-      </c>
-      <c r="W2" s="7">
-        <f>([1]Basic_load!$B$23*[1]Basic_load!G3)*0.1</f>
-        <v>5.04E-4</v>
-      </c>
       <c r="X2" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G3)*0.1</f>
-        <v>5.04E-4</v>
+        <f>([1]Basic_load!$B$24*[1]Basic_load!G3)*0.85</f>
+        <v>4.2840000000000005E-3</v>
       </c>
       <c r="Y2" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G3)*0.1</f>
-        <v>2.3519999999999999E-3</v>
+        <f>([1]Basic_load!$B$25*[1]Basic_load!G3)*0.85</f>
+        <v>1.9991999999999999E-2</v>
       </c>
       <c r="Z2" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G3)*0.1</f>
-        <v>2.3519999999999999E-3</v>
+        <f>([1]Basic_load!$B$26*[1]Basic_load!G3)*0.85</f>
+        <v>1.9991999999999999E-2</v>
       </c>
       <c r="AA2" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G3)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$27*[1]Basic_load!G3)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="AB2" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G3)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$28*[1]Basic_load!G3)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="AC2" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G3)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$29*[1]Basic_load!G3)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="AD2" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G3)*0.1</f>
-        <v>6.7200000000000007E-4</v>
+        <f>([1]Basic_load!$B$30*[1]Basic_load!G3)*0.85</f>
+        <v>5.7120000000000001E-3</v>
       </c>
       <c r="AE2" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G3)*0.1</f>
-        <v>1.1200000000000001E-3</v>
+        <f>([1]Basic_load!$B$31*[1]Basic_load!G3)*0.85</f>
+        <v>9.5200000000000007E-3</v>
       </c>
       <c r="AF2" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G3)*0.1</f>
-        <v>8.4000000000000003E-4</v>
+        <f>([1]Basic_load!$B$32*[1]Basic_load!G3)*0.85</f>
+        <v>7.1399999999999996E-3</v>
       </c>
       <c r="AG2" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G3)*0.1</f>
-        <v>1.176E-3</v>
+        <f>([1]Basic_load!$B$33*[1]Basic_load!G3)*0.85</f>
+        <v>9.9959999999999997E-3</v>
       </c>
       <c r="AH2" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G3)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$34*[1]Basic_load!G3)*0.85</f>
+        <v>2.856E-3</v>
       </c>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.3">
@@ -951,135 +1684,134 @@
         <v>4.1666666666666699E-2</v>
       </c>
       <c r="B3" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G4)*0.1</f>
+        <f>([1]Basic_load!$B$2*[1]Basic_load!G4)*0.85</f>
         <v>0</v>
       </c>
       <c r="C3" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G4)*0.1</f>
-        <v>5.6000000000000006E-4</v>
+        <f>([1]Basic_load!$B$3*[1]Basic_load!G4)*0.85</f>
+        <v>4.7600000000000003E-3</v>
       </c>
       <c r="D3" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G4)*0.1</f>
-        <v>5.04E-4</v>
+        <f>([1]Basic_load!$B$4*[1]Basic_load!G4)*0.85</f>
+        <v>4.2840000000000005E-3</v>
       </c>
       <c r="E3" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G4)*0.1</f>
-        <v>5.6000000000000006E-4</v>
+        <f>([1]Basic_load!$B$5*[1]Basic_load!G4)*0.85</f>
+        <v>4.7600000000000003E-3</v>
       </c>
       <c r="F3" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G4)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$6*[1]Basic_load!G4)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="G3" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G4)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$7*[1]Basic_load!G4)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="H3" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G4)*0.1</f>
-        <v>1.1200000000000001E-3</v>
+        <f>([1]Basic_load!$B$8*[1]Basic_load!G4)*0.85</f>
+        <v>9.5200000000000007E-3</v>
       </c>
       <c r="I3" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G4)*0.1</f>
-        <v>1.1200000000000001E-3</v>
+        <f>([1]Basic_load!$B$9*[1]Basic_load!G4)*0.85</f>
+        <v>9.5200000000000007E-3</v>
       </c>
       <c r="J3" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G4)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$10*[1]Basic_load!G4)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="K3" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G4)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$11*[1]Basic_load!G4)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="L3" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G4)*0.1</f>
-        <v>2.52E-4</v>
+        <f>([1]Basic_load!$B$12*[1]Basic_load!G4)*0.85</f>
+        <v>2.1420000000000002E-3</v>
       </c>
       <c r="M3" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G4)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$13*[1]Basic_load!G4)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="N3" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G4)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$14*[1]Basic_load!G4)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="O3" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G4)*0.1</f>
-        <v>6.7200000000000007E-4</v>
+        <f>([1]Basic_load!$B$15*[1]Basic_load!G4)*0.85</f>
+        <v>5.7120000000000001E-3</v>
       </c>
       <c r="P3" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G4)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$16*[1]Basic_load!G4)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="Q3" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G4)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$17*[1]Basic_load!G4)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="R3" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G4)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$18*[1]Basic_load!G4)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="S3" s="8">
+        <v>0.30869999999999997</v>
+      </c>
+      <c r="T3" s="7">
+        <f>([1]Basic_load!$B$20*[1]Basic_load!G4)*0.85</f>
+        <v>4.2840000000000005E-3</v>
+      </c>
+      <c r="U3" s="7">
+        <f>([1]Basic_load!$B$21*[1]Basic_load!G4)*0.85</f>
+        <v>4.2840000000000005E-3</v>
+      </c>
+      <c r="V3" s="7">
+        <f>([1]Basic_load!$B$22*[1]Basic_load!G4)*0.85</f>
+        <v>4.2840000000000005E-3</v>
+      </c>
+      <c r="W3" s="7">
         <v>0</v>
       </c>
-      <c r="T3" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G4)*0.1</f>
-        <v>5.04E-4</v>
-      </c>
-      <c r="U3" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G4)*0.1</f>
-        <v>5.04E-4</v>
-      </c>
-      <c r="V3" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G4)*0.1</f>
-        <v>5.04E-4</v>
-      </c>
-      <c r="W3" s="7">
-        <f>([1]Basic_load!$B$23*[1]Basic_load!G4)*0.1</f>
-        <v>5.04E-4</v>
-      </c>
       <c r="X3" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G4)*0.1</f>
-        <v>5.04E-4</v>
+        <f>([1]Basic_load!$B$24*[1]Basic_load!G4)*0.85</f>
+        <v>4.2840000000000005E-3</v>
       </c>
       <c r="Y3" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G4)*0.1</f>
-        <v>2.3519999999999999E-3</v>
+        <f>([1]Basic_load!$B$25*[1]Basic_load!G4)*0.85</f>
+        <v>1.9991999999999999E-2</v>
       </c>
       <c r="Z3" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G4)*0.1</f>
-        <v>2.3519999999999999E-3</v>
+        <f>([1]Basic_load!$B$26*[1]Basic_load!G4)*0.85</f>
+        <v>1.9991999999999999E-2</v>
       </c>
       <c r="AA3" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G4)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$27*[1]Basic_load!G4)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="AB3" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G4)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$28*[1]Basic_load!G4)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="AC3" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G4)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$29*[1]Basic_load!G4)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="AD3" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G4)*0.1</f>
-        <v>6.7200000000000007E-4</v>
+        <f>([1]Basic_load!$B$30*[1]Basic_load!G4)*0.85</f>
+        <v>5.7120000000000001E-3</v>
       </c>
       <c r="AE3" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G4)*0.1</f>
-        <v>1.1200000000000001E-3</v>
+        <f>([1]Basic_load!$B$31*[1]Basic_load!G4)*0.85</f>
+        <v>9.5200000000000007E-3</v>
       </c>
       <c r="AF3" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G4)*0.1</f>
-        <v>8.4000000000000003E-4</v>
+        <f>([1]Basic_load!$B$32*[1]Basic_load!G4)*0.85</f>
+        <v>7.1399999999999996E-3</v>
       </c>
       <c r="AG3" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G4)*0.1</f>
-        <v>1.176E-3</v>
+        <f>([1]Basic_load!$B$33*[1]Basic_load!G4)*0.85</f>
+        <v>9.9959999999999997E-3</v>
       </c>
       <c r="AH3" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G4)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$34*[1]Basic_load!G4)*0.85</f>
+        <v>2.856E-3</v>
       </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.3">
@@ -1087,135 +1819,134 @@
         <v>8.3333333333333301E-2</v>
       </c>
       <c r="B4" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G5)*0.1</f>
+        <f>([1]Basic_load!$B$2*[1]Basic_load!G5)*0.85</f>
         <v>0</v>
       </c>
       <c r="C4" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G5)*0.1</f>
-        <v>5.6000000000000006E-4</v>
+        <f>([1]Basic_load!$B$3*[1]Basic_load!G5)*0.85</f>
+        <v>4.7600000000000003E-3</v>
       </c>
       <c r="D4" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G5)*0.1</f>
-        <v>5.04E-4</v>
+        <f>([1]Basic_load!$B$4*[1]Basic_load!G5)*0.85</f>
+        <v>4.2840000000000005E-3</v>
       </c>
       <c r="E4" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G5)*0.1</f>
-        <v>5.6000000000000006E-4</v>
+        <f>([1]Basic_load!$B$5*[1]Basic_load!G5)*0.85</f>
+        <v>4.7600000000000003E-3</v>
       </c>
       <c r="F4" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G5)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$6*[1]Basic_load!G5)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="G4" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G5)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$7*[1]Basic_load!G5)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="H4" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G5)*0.1</f>
-        <v>1.1200000000000001E-3</v>
+        <f>([1]Basic_load!$B$8*[1]Basic_load!G5)*0.85</f>
+        <v>9.5200000000000007E-3</v>
       </c>
       <c r="I4" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G5)*0.1</f>
-        <v>1.1200000000000001E-3</v>
+        <f>([1]Basic_load!$B$9*[1]Basic_load!G5)*0.85</f>
+        <v>9.5200000000000007E-3</v>
       </c>
       <c r="J4" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G5)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$10*[1]Basic_load!G5)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="K4" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G5)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$11*[1]Basic_load!G5)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="L4" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G5)*0.1</f>
-        <v>2.52E-4</v>
+        <f>([1]Basic_load!$B$12*[1]Basic_load!G5)*0.85</f>
+        <v>2.1420000000000002E-3</v>
       </c>
       <c r="M4" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G5)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$13*[1]Basic_load!G5)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="N4" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G5)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$14*[1]Basic_load!G5)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="O4" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G5)*0.1</f>
-        <v>6.7200000000000007E-4</v>
+        <f>([1]Basic_load!$B$15*[1]Basic_load!G5)*0.85</f>
+        <v>5.7120000000000001E-3</v>
       </c>
       <c r="P4" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G5)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$16*[1]Basic_load!G5)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="Q4" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G5)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$17*[1]Basic_load!G5)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="R4" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G5)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$18*[1]Basic_load!G5)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="S4" s="8">
+        <v>0.30869999999999997</v>
+      </c>
+      <c r="T4" s="7">
+        <f>([1]Basic_load!$B$20*[1]Basic_load!G5)*0.85</f>
+        <v>4.2840000000000005E-3</v>
+      </c>
+      <c r="U4" s="7">
+        <f>([1]Basic_load!$B$21*[1]Basic_load!G5)*0.85</f>
+        <v>4.2840000000000005E-3</v>
+      </c>
+      <c r="V4" s="7">
+        <f>([1]Basic_load!$B$22*[1]Basic_load!G5)*0.85</f>
+        <v>4.2840000000000005E-3</v>
+      </c>
+      <c r="W4" s="7">
         <v>0</v>
       </c>
-      <c r="T4" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G5)*0.1</f>
-        <v>5.04E-4</v>
-      </c>
-      <c r="U4" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G5)*0.1</f>
-        <v>5.04E-4</v>
-      </c>
-      <c r="V4" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G5)*0.1</f>
-        <v>5.04E-4</v>
-      </c>
-      <c r="W4" s="7">
-        <f>([1]Basic_load!$B$23*[1]Basic_load!G5)*0.1</f>
-        <v>5.04E-4</v>
-      </c>
       <c r="X4" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G5)*0.1</f>
-        <v>5.04E-4</v>
+        <f>([1]Basic_load!$B$24*[1]Basic_load!G5)*0.85</f>
+        <v>4.2840000000000005E-3</v>
       </c>
       <c r="Y4" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G5)*0.1</f>
-        <v>2.3519999999999999E-3</v>
+        <f>([1]Basic_load!$B$25*[1]Basic_load!G5)*0.85</f>
+        <v>1.9991999999999999E-2</v>
       </c>
       <c r="Z4" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G5)*0.1</f>
-        <v>2.3519999999999999E-3</v>
+        <f>([1]Basic_load!$B$26*[1]Basic_load!G5)*0.85</f>
+        <v>1.9991999999999999E-2</v>
       </c>
       <c r="AA4" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G5)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$27*[1]Basic_load!G5)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="AB4" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G5)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$28*[1]Basic_load!G5)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="AC4" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G5)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$29*[1]Basic_load!G5)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="AD4" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G5)*0.1</f>
-        <v>6.7200000000000007E-4</v>
+        <f>([1]Basic_load!$B$30*[1]Basic_load!G5)*0.85</f>
+        <v>5.7120000000000001E-3</v>
       </c>
       <c r="AE4" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G5)*0.1</f>
-        <v>1.1200000000000001E-3</v>
+        <f>([1]Basic_load!$B$31*[1]Basic_load!G5)*0.85</f>
+        <v>9.5200000000000007E-3</v>
       </c>
       <c r="AF4" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G5)*0.1</f>
-        <v>8.4000000000000003E-4</v>
+        <f>([1]Basic_load!$B$32*[1]Basic_load!G5)*0.85</f>
+        <v>7.1399999999999996E-3</v>
       </c>
       <c r="AG4" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G5)*0.1</f>
-        <v>1.176E-3</v>
+        <f>([1]Basic_load!$B$33*[1]Basic_load!G5)*0.85</f>
+        <v>9.9959999999999997E-3</v>
       </c>
       <c r="AH4" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G5)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$34*[1]Basic_load!G5)*0.85</f>
+        <v>2.856E-3</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.3">
@@ -1223,135 +1954,134 @@
         <v>0.125</v>
       </c>
       <c r="B5" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G6)*0.1</f>
+        <f>([1]Basic_load!$B$2*[1]Basic_load!G6)*0.85</f>
         <v>0</v>
       </c>
       <c r="C5" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G6)*0.1</f>
-        <v>5.6000000000000006E-4</v>
+        <f>([1]Basic_load!$B$3*[1]Basic_load!G6)*0.85</f>
+        <v>4.7600000000000003E-3</v>
       </c>
       <c r="D5" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G6)*0.1</f>
-        <v>5.04E-4</v>
+        <f>([1]Basic_load!$B$4*[1]Basic_load!G6)*0.85</f>
+        <v>4.2840000000000005E-3</v>
       </c>
       <c r="E5" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G6)*0.1</f>
-        <v>5.6000000000000006E-4</v>
+        <f>([1]Basic_load!$B$5*[1]Basic_load!G6)*0.85</f>
+        <v>4.7600000000000003E-3</v>
       </c>
       <c r="F5" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G6)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$6*[1]Basic_load!G6)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="G5" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G6)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$7*[1]Basic_load!G6)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="H5" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G6)*0.1</f>
-        <v>1.1200000000000001E-3</v>
+        <f>([1]Basic_load!$B$8*[1]Basic_load!G6)*0.85</f>
+        <v>9.5200000000000007E-3</v>
       </c>
       <c r="I5" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G6)*0.1</f>
-        <v>1.1200000000000001E-3</v>
+        <f>([1]Basic_load!$B$9*[1]Basic_load!G6)*0.85</f>
+        <v>9.5200000000000007E-3</v>
       </c>
       <c r="J5" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G6)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$10*[1]Basic_load!G6)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="K5" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G6)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$11*[1]Basic_load!G6)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="L5" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G6)*0.1</f>
-        <v>2.52E-4</v>
+        <f>([1]Basic_load!$B$12*[1]Basic_load!G6)*0.85</f>
+        <v>2.1420000000000002E-3</v>
       </c>
       <c r="M5" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G6)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$13*[1]Basic_load!G6)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="N5" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G6)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$14*[1]Basic_load!G6)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="O5" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G6)*0.1</f>
-        <v>6.7200000000000007E-4</v>
+        <f>([1]Basic_load!$B$15*[1]Basic_load!G6)*0.85</f>
+        <v>5.7120000000000001E-3</v>
       </c>
       <c r="P5" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G6)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$16*[1]Basic_load!G6)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="Q5" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G6)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$17*[1]Basic_load!G6)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="R5" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G6)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$18*[1]Basic_load!G6)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="S5" s="8">
-        <v>0</v>
+        <v>0.30869999999999997</v>
       </c>
       <c r="T5" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G6)*0.1</f>
-        <v>5.04E-4</v>
+        <f>([1]Basic_load!$B$20*[1]Basic_load!G6)*0.85</f>
+        <v>4.2840000000000005E-3</v>
       </c>
       <c r="U5" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G6)*0.1</f>
-        <v>5.04E-4</v>
+        <f>([1]Basic_load!$B$21*[1]Basic_load!G6)*0.85</f>
+        <v>4.2840000000000005E-3</v>
       </c>
       <c r="V5" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G6)*0.1</f>
-        <v>5.04E-4</v>
+        <f>([1]Basic_load!$B$22*[1]Basic_load!G6)*0.85</f>
+        <v>4.2840000000000005E-3</v>
       </c>
       <c r="W5" s="7">
-        <f>([1]Basic_load!$B$23*[1]Basic_load!G6)*0.1</f>
-        <v>5.04E-4</v>
+        <v>6.7999999999999996E-3</v>
       </c>
       <c r="X5" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G6)*0.1</f>
-        <v>5.04E-4</v>
+        <f>([1]Basic_load!$B$24*[1]Basic_load!G6)*0.85</f>
+        <v>4.2840000000000005E-3</v>
       </c>
       <c r="Y5" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G6)*0.1</f>
-        <v>2.3519999999999999E-3</v>
+        <f>([1]Basic_load!$B$25*[1]Basic_load!G6)*0.85</f>
+        <v>1.9991999999999999E-2</v>
       </c>
       <c r="Z5" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G6)*0.1</f>
-        <v>2.3519999999999999E-3</v>
+        <f>([1]Basic_load!$B$26*[1]Basic_load!G6)*0.85</f>
+        <v>1.9991999999999999E-2</v>
       </c>
       <c r="AA5" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G6)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$27*[1]Basic_load!G6)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="AB5" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G6)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$28*[1]Basic_load!G6)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="AC5" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G6)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$29*[1]Basic_load!G6)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="AD5" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G6)*0.1</f>
-        <v>6.7200000000000007E-4</v>
+        <f>([1]Basic_load!$B$30*[1]Basic_load!G6)*0.85</f>
+        <v>5.7120000000000001E-3</v>
       </c>
       <c r="AE5" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G6)*0.1</f>
-        <v>1.1200000000000001E-3</v>
+        <f>([1]Basic_load!$B$31*[1]Basic_load!G6)*0.85</f>
+        <v>9.5200000000000007E-3</v>
       </c>
       <c r="AF5" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G6)*0.1</f>
-        <v>8.4000000000000003E-4</v>
+        <f>([1]Basic_load!$B$32*[1]Basic_load!G6)*0.85</f>
+        <v>7.1399999999999996E-3</v>
       </c>
       <c r="AG5" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G6)*0.1</f>
-        <v>1.176E-3</v>
+        <f>([1]Basic_load!$B$33*[1]Basic_load!G6)*0.85</f>
+        <v>9.9959999999999997E-3</v>
       </c>
       <c r="AH5" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G6)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$34*[1]Basic_load!G6)*0.85</f>
+        <v>2.856E-3</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.3">
@@ -1359,135 +2089,134 @@
         <v>0.16666666666666699</v>
       </c>
       <c r="B6" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G7)*0.1</f>
+        <f>([1]Basic_load!$B$2*[1]Basic_load!G7)*0.85</f>
         <v>0</v>
       </c>
       <c r="C6" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G7)*0.1</f>
-        <v>5.6000000000000006E-4</v>
+        <f>([1]Basic_load!$B$3*[1]Basic_load!G7)*0.85</f>
+        <v>4.7600000000000003E-3</v>
       </c>
       <c r="D6" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G7)*0.1</f>
-        <v>5.04E-4</v>
+        <f>([1]Basic_load!$B$4*[1]Basic_load!G7)*0.85</f>
+        <v>4.2840000000000005E-3</v>
       </c>
       <c r="E6" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G7)*0.1</f>
-        <v>5.6000000000000006E-4</v>
+        <f>([1]Basic_load!$B$5*[1]Basic_load!G7)*0.85</f>
+        <v>4.7600000000000003E-3</v>
       </c>
       <c r="F6" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G7)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$6*[1]Basic_load!G7)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="G6" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G7)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$7*[1]Basic_load!G7)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="H6" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G7)*0.1</f>
-        <v>1.1200000000000001E-3</v>
+        <f>([1]Basic_load!$B$8*[1]Basic_load!G7)*0.85</f>
+        <v>9.5200000000000007E-3</v>
       </c>
       <c r="I6" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G7)*0.1</f>
-        <v>1.1200000000000001E-3</v>
+        <f>([1]Basic_load!$B$9*[1]Basic_load!G7)*0.85</f>
+        <v>9.5200000000000007E-3</v>
       </c>
       <c r="J6" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G7)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$10*[1]Basic_load!G7)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="K6" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G7)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$11*[1]Basic_load!G7)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="L6" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G7)*0.1</f>
-        <v>2.52E-4</v>
+        <f>([1]Basic_load!$B$12*[1]Basic_load!G7)*0.85</f>
+        <v>2.1420000000000002E-3</v>
       </c>
       <c r="M6" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G7)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$13*[1]Basic_load!G7)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="N6" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G7)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$14*[1]Basic_load!G7)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="O6" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G7)*0.1</f>
-        <v>6.7200000000000007E-4</v>
+        <f>([1]Basic_load!$B$15*[1]Basic_load!G7)*0.85</f>
+        <v>5.7120000000000001E-3</v>
       </c>
       <c r="P6" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G7)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$16*[1]Basic_load!G7)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="Q6" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G7)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$17*[1]Basic_load!G7)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="R6" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G7)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$18*[1]Basic_load!G7)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="S6" s="8">
-        <v>0</v>
+        <v>0.40879999999999994</v>
       </c>
       <c r="T6" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G7)*0.1</f>
-        <v>5.04E-4</v>
+        <f>([1]Basic_load!$B$20*[1]Basic_load!G7)*0.85</f>
+        <v>4.2840000000000005E-3</v>
       </c>
       <c r="U6" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G7)*0.1</f>
-        <v>5.04E-4</v>
+        <f>([1]Basic_load!$B$21*[1]Basic_load!G7)*0.85</f>
+        <v>4.2840000000000005E-3</v>
       </c>
       <c r="V6" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G7)*0.1</f>
-        <v>5.04E-4</v>
+        <f>([1]Basic_load!$B$22*[1]Basic_load!G7)*0.85</f>
+        <v>4.2840000000000005E-3</v>
       </c>
       <c r="W6" s="7">
-        <f>([1]Basic_load!$B$23*[1]Basic_load!G7)*0.1</f>
-        <v>5.04E-4</v>
+        <v>6.3750000000000001E-2</v>
       </c>
       <c r="X6" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G7)*0.1</f>
-        <v>5.04E-4</v>
+        <f>([1]Basic_load!$B$24*[1]Basic_load!G7)*0.85</f>
+        <v>4.2840000000000005E-3</v>
       </c>
       <c r="Y6" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G7)*0.1</f>
-        <v>2.3519999999999999E-3</v>
+        <f>([1]Basic_load!$B$25*[1]Basic_load!G7)*0.85</f>
+        <v>1.9991999999999999E-2</v>
       </c>
       <c r="Z6" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G7)*0.1</f>
-        <v>2.3519999999999999E-3</v>
+        <f>([1]Basic_load!$B$26*[1]Basic_load!G7)*0.85</f>
+        <v>1.9991999999999999E-2</v>
       </c>
       <c r="AA6" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G7)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$27*[1]Basic_load!G7)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="AB6" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G7)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$28*[1]Basic_load!G7)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="AC6" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G7)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$29*[1]Basic_load!G7)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="AD6" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G7)*0.1</f>
-        <v>6.7200000000000007E-4</v>
+        <f>([1]Basic_load!$B$30*[1]Basic_load!G7)*0.85</f>
+        <v>5.7120000000000001E-3</v>
       </c>
       <c r="AE6" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G7)*0.1</f>
-        <v>1.1200000000000001E-3</v>
+        <f>([1]Basic_load!$B$31*[1]Basic_load!G7)*0.85</f>
+        <v>9.5200000000000007E-3</v>
       </c>
       <c r="AF6" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G7)*0.1</f>
-        <v>8.4000000000000003E-4</v>
+        <f>([1]Basic_load!$B$32*[1]Basic_load!G7)*0.85</f>
+        <v>7.1399999999999996E-3</v>
       </c>
       <c r="AG6" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G7)*0.1</f>
-        <v>1.176E-3</v>
+        <f>([1]Basic_load!$B$33*[1]Basic_load!G7)*0.85</f>
+        <v>9.9959999999999997E-3</v>
       </c>
       <c r="AH6" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G7)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$34*[1]Basic_load!G7)*0.85</f>
+        <v>2.856E-3</v>
       </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.3">
@@ -1495,135 +2224,134 @@
         <v>0.20833333333333301</v>
       </c>
       <c r="B7" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G8)*0.1</f>
+        <f>([1]Basic_load!$B$2*[1]Basic_load!G8)*0.85</f>
         <v>0</v>
       </c>
       <c r="C7" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G8)*0.1</f>
-        <v>5.6000000000000006E-4</v>
+        <f>([1]Basic_load!$B$3*[1]Basic_load!G8)*0.85</f>
+        <v>4.7600000000000003E-3</v>
       </c>
       <c r="D7" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G8)*0.1</f>
-        <v>5.04E-4</v>
+        <f>([1]Basic_load!$B$4*[1]Basic_load!G8)*0.85</f>
+        <v>4.2840000000000005E-3</v>
       </c>
       <c r="E7" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G8)*0.1</f>
-        <v>5.6000000000000006E-4</v>
+        <f>([1]Basic_load!$B$5*[1]Basic_load!G8)*0.85</f>
+        <v>4.7600000000000003E-3</v>
       </c>
       <c r="F7" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G8)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$6*[1]Basic_load!G8)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="G7" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G8)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$7*[1]Basic_load!G8)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="H7" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G8)*0.1</f>
-        <v>1.1200000000000001E-3</v>
+        <f>([1]Basic_load!$B$8*[1]Basic_load!G8)*0.85</f>
+        <v>9.5200000000000007E-3</v>
       </c>
       <c r="I7" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G8)*0.1</f>
-        <v>1.1200000000000001E-3</v>
+        <f>([1]Basic_load!$B$9*[1]Basic_load!G8)*0.85</f>
+        <v>9.5200000000000007E-3</v>
       </c>
       <c r="J7" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G8)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$10*[1]Basic_load!G8)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="K7" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G8)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$11*[1]Basic_load!G8)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="L7" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G8)*0.1</f>
-        <v>2.52E-4</v>
+        <f>([1]Basic_load!$B$12*[1]Basic_load!G8)*0.85</f>
+        <v>2.1420000000000002E-3</v>
       </c>
       <c r="M7" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G8)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$13*[1]Basic_load!G8)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="N7" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G8)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$14*[1]Basic_load!G8)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="O7" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G8)*0.1</f>
-        <v>6.7200000000000007E-4</v>
+        <f>([1]Basic_load!$B$15*[1]Basic_load!G8)*0.85</f>
+        <v>5.7120000000000001E-3</v>
       </c>
       <c r="P7" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G8)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$16*[1]Basic_load!G8)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="Q7" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G8)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$17*[1]Basic_load!G8)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="R7" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G8)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$18*[1]Basic_load!G8)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="S7" s="8">
-        <v>0</v>
+        <v>0.40879999999999994</v>
       </c>
       <c r="T7" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G8)*0.1</f>
-        <v>5.04E-4</v>
+        <f>([1]Basic_load!$B$20*[1]Basic_load!G8)*0.85</f>
+        <v>4.2840000000000005E-3</v>
       </c>
       <c r="U7" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G8)*0.1</f>
-        <v>5.04E-4</v>
+        <f>([1]Basic_load!$B$21*[1]Basic_load!G8)*0.85</f>
+        <v>4.2840000000000005E-3</v>
       </c>
       <c r="V7" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G8)*0.1</f>
-        <v>5.04E-4</v>
+        <f>([1]Basic_load!$B$22*[1]Basic_load!G8)*0.85</f>
+        <v>4.2840000000000005E-3</v>
       </c>
       <c r="W7" s="7">
-        <f>([1]Basic_load!$B$23*[1]Basic_load!G8)*0.1</f>
-        <v>5.04E-4</v>
+        <v>0.15045</v>
       </c>
       <c r="X7" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G8)*0.1</f>
-        <v>5.04E-4</v>
+        <f>([1]Basic_load!$B$24*[1]Basic_load!G8)*0.85</f>
+        <v>4.2840000000000005E-3</v>
       </c>
       <c r="Y7" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G8)*0.1</f>
-        <v>2.3519999999999999E-3</v>
+        <f>([1]Basic_load!$B$25*[1]Basic_load!G8)*0.85</f>
+        <v>1.9991999999999999E-2</v>
       </c>
       <c r="Z7" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G8)*0.1</f>
-        <v>2.3519999999999999E-3</v>
+        <f>([1]Basic_load!$B$26*[1]Basic_load!G8)*0.85</f>
+        <v>1.9991999999999999E-2</v>
       </c>
       <c r="AA7" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G8)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$27*[1]Basic_load!G8)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="AB7" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G8)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$28*[1]Basic_load!G8)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="AC7" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G8)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$29*[1]Basic_load!G8)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="AD7" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G8)*0.1</f>
-        <v>6.7200000000000007E-4</v>
+        <f>([1]Basic_load!$B$30*[1]Basic_load!G8)*0.85</f>
+        <v>5.7120000000000001E-3</v>
       </c>
       <c r="AE7" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G8)*0.1</f>
-        <v>1.1200000000000001E-3</v>
+        <f>([1]Basic_load!$B$31*[1]Basic_load!G8)*0.85</f>
+        <v>9.5200000000000007E-3</v>
       </c>
       <c r="AF7" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G8)*0.1</f>
-        <v>8.4000000000000003E-4</v>
+        <f>([1]Basic_load!$B$32*[1]Basic_load!G8)*0.85</f>
+        <v>7.1399999999999996E-3</v>
       </c>
       <c r="AG7" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G8)*0.1</f>
-        <v>1.176E-3</v>
+        <f>([1]Basic_load!$B$33*[1]Basic_load!G8)*0.85</f>
+        <v>9.9959999999999997E-3</v>
       </c>
       <c r="AH7" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G8)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$34*[1]Basic_load!G8)*0.85</f>
+        <v>2.856E-3</v>
       </c>
     </row>
     <row r="8" spans="1:34" x14ac:dyDescent="0.3">
@@ -1631,135 +2359,134 @@
         <v>0.25</v>
       </c>
       <c r="B8" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G9)*0.1</f>
+        <f>([1]Basic_load!$B$2*[1]Basic_load!G9)*0.85</f>
         <v>0</v>
       </c>
       <c r="C8" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G9)*0.1</f>
-        <v>5.6000000000000006E-4</v>
+        <f>([1]Basic_load!$B$3*[1]Basic_load!G9)*0.85</f>
+        <v>4.7600000000000003E-3</v>
       </c>
       <c r="D8" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G9)*0.1</f>
-        <v>5.04E-4</v>
+        <f>([1]Basic_load!$B$4*[1]Basic_load!G9)*0.85</f>
+        <v>4.2840000000000005E-3</v>
       </c>
       <c r="E8" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G9)*0.1</f>
-        <v>5.6000000000000006E-4</v>
+        <f>([1]Basic_load!$B$5*[1]Basic_load!G9)*0.85</f>
+        <v>4.7600000000000003E-3</v>
       </c>
       <c r="F8" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G9)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$6*[1]Basic_load!G9)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="G8" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G9)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$7*[1]Basic_load!G9)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="H8" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G9)*0.1</f>
-        <v>1.1200000000000001E-3</v>
+        <f>([1]Basic_load!$B$8*[1]Basic_load!G9)*0.85</f>
+        <v>9.5200000000000007E-3</v>
       </c>
       <c r="I8" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G9)*0.1</f>
-        <v>1.1200000000000001E-3</v>
+        <f>([1]Basic_load!$B$9*[1]Basic_load!G9)*0.85</f>
+        <v>9.5200000000000007E-3</v>
       </c>
       <c r="J8" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G9)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$10*[1]Basic_load!G9)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="K8" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G9)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$11*[1]Basic_load!G9)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="L8" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G9)*0.1</f>
-        <v>2.52E-4</v>
+        <f>([1]Basic_load!$B$12*[1]Basic_load!G9)*0.85</f>
+        <v>2.1420000000000002E-3</v>
       </c>
       <c r="M8" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G9)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$13*[1]Basic_load!G9)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="N8" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G9)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$14*[1]Basic_load!G9)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="O8" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G9)*0.1</f>
-        <v>6.7200000000000007E-4</v>
+        <f>([1]Basic_load!$B$15*[1]Basic_load!G9)*0.85</f>
+        <v>5.7120000000000001E-3</v>
       </c>
       <c r="P8" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G9)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$16*[1]Basic_load!G9)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="Q8" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G9)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$17*[1]Basic_load!G9)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="R8" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G9)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$18*[1]Basic_load!G9)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="S8" s="8">
-        <v>4.5</v>
+        <v>0.40879999999999994</v>
       </c>
       <c r="T8" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G9)*0.1</f>
-        <v>5.04E-4</v>
+        <f>([1]Basic_load!$B$20*[1]Basic_load!G9)*0.85</f>
+        <v>4.2840000000000005E-3</v>
       </c>
       <c r="U8" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G9)*0.1</f>
-        <v>5.04E-4</v>
+        <f>([1]Basic_load!$B$21*[1]Basic_load!G9)*0.85</f>
+        <v>4.2840000000000005E-3</v>
       </c>
       <c r="V8" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G9)*0.1</f>
-        <v>5.04E-4</v>
+        <f>([1]Basic_load!$B$22*[1]Basic_load!G9)*0.85</f>
+        <v>4.2840000000000005E-3</v>
       </c>
       <c r="W8" s="7">
-        <f>([1]Basic_load!$B$23*[1]Basic_load!G9)*0.1</f>
-        <v>5.04E-4</v>
+        <v>0.23800000000000002</v>
       </c>
       <c r="X8" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G9)*0.1</f>
-        <v>5.04E-4</v>
+        <f>([1]Basic_load!$B$24*[1]Basic_load!G9)*0.85</f>
+        <v>4.2840000000000005E-3</v>
       </c>
       <c r="Y8" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G9)*0.1</f>
-        <v>2.3519999999999999E-3</v>
+        <f>([1]Basic_load!$B$25*[1]Basic_load!G9)*0.85</f>
+        <v>1.9991999999999999E-2</v>
       </c>
       <c r="Z8" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G9)*0.1</f>
-        <v>2.3519999999999999E-3</v>
+        <f>([1]Basic_load!$B$26*[1]Basic_load!G9)*0.85</f>
+        <v>1.9991999999999999E-2</v>
       </c>
       <c r="AA8" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G9)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$27*[1]Basic_load!G9)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="AB8" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G9)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$28*[1]Basic_load!G9)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="AC8" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G9)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$29*[1]Basic_load!G9)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="AD8" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G9)*0.1</f>
-        <v>6.7200000000000007E-4</v>
+        <f>([1]Basic_load!$B$30*[1]Basic_load!G9)*0.85</f>
+        <v>5.7120000000000001E-3</v>
       </c>
       <c r="AE8" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G9)*0.1</f>
-        <v>1.1200000000000001E-3</v>
+        <f>([1]Basic_load!$B$31*[1]Basic_load!G9)*0.85</f>
+        <v>9.5200000000000007E-3</v>
       </c>
       <c r="AF8" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G9)*0.1</f>
-        <v>8.4000000000000003E-4</v>
+        <f>([1]Basic_load!$B$32*[1]Basic_load!G9)*0.85</f>
+        <v>7.1399999999999996E-3</v>
       </c>
       <c r="AG8" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G9)*0.1</f>
-        <v>1.176E-3</v>
+        <f>([1]Basic_load!$B$33*[1]Basic_load!G9)*0.85</f>
+        <v>9.9959999999999997E-3</v>
       </c>
       <c r="AH8" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G9)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$34*[1]Basic_load!G9)*0.85</f>
+        <v>2.856E-3</v>
       </c>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.3">
@@ -1767,135 +2494,134 @@
         <v>0.29166666666666702</v>
       </c>
       <c r="B9" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G10)*0.1</f>
+        <f>([1]Basic_load!$B$2*[1]Basic_load!G10)*0.85</f>
         <v>0</v>
       </c>
       <c r="C9" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G10)*0.1</f>
-        <v>4.5746700000000003E-3</v>
+        <f>([1]Basic_load!$B$3*[1]Basic_load!G10)*0.85</f>
+        <v>3.8884694999999997E-2</v>
       </c>
       <c r="D9" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G10)*0.1</f>
-        <v>4.1172029999999998E-3</v>
+        <f>([1]Basic_load!$B$4*[1]Basic_load!G10)*0.85</f>
+        <v>3.4996225499999999E-2</v>
       </c>
       <c r="E9" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G10)*0.1</f>
-        <v>4.5746700000000003E-3</v>
+        <f>([1]Basic_load!$B$5*[1]Basic_load!G10)*0.85</f>
+        <v>3.8884694999999997E-2</v>
       </c>
       <c r="F9" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G10)*0.1</f>
-        <v>2.7448020000000002E-3</v>
+        <f>([1]Basic_load!$B$6*[1]Basic_load!G10)*0.85</f>
+        <v>2.3330817E-2</v>
       </c>
       <c r="G9" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G10)*0.1</f>
-        <v>2.7448020000000002E-3</v>
+        <f>([1]Basic_load!$B$7*[1]Basic_load!G10)*0.85</f>
+        <v>2.3330817E-2</v>
       </c>
       <c r="H9" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G10)*0.1</f>
-        <v>9.1493400000000006E-3</v>
+        <f>([1]Basic_load!$B$8*[1]Basic_load!G10)*0.85</f>
+        <v>7.7769389999999994E-2</v>
       </c>
       <c r="I9" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G10)*0.1</f>
-        <v>9.1493400000000006E-3</v>
+        <f>([1]Basic_load!$B$9*[1]Basic_load!G10)*0.85</f>
+        <v>7.7769389999999994E-2</v>
       </c>
       <c r="J9" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G10)*0.1</f>
-        <v>2.7448020000000002E-3</v>
+        <f>([1]Basic_load!$B$10*[1]Basic_load!G10)*0.85</f>
+        <v>2.3330817E-2</v>
       </c>
       <c r="K9" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G10)*0.1</f>
-        <v>2.7448020000000002E-3</v>
+        <f>([1]Basic_load!$B$11*[1]Basic_load!G10)*0.85</f>
+        <v>2.3330817E-2</v>
       </c>
       <c r="L9" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G10)*0.1</f>
-        <v>2.0586014999999999E-3</v>
+        <f>([1]Basic_load!$B$12*[1]Basic_load!G10)*0.85</f>
+        <v>1.7498112749999999E-2</v>
       </c>
       <c r="M9" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G10)*0.1</f>
-        <v>2.7448020000000002E-3</v>
+        <f>([1]Basic_load!$B$13*[1]Basic_load!G10)*0.85</f>
+        <v>2.3330817E-2</v>
       </c>
       <c r="N9" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G10)*0.1</f>
-        <v>2.7448020000000002E-3</v>
+        <f>([1]Basic_load!$B$14*[1]Basic_load!G10)*0.85</f>
+        <v>2.3330817E-2</v>
       </c>
       <c r="O9" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G10)*0.1</f>
-        <v>5.4896040000000004E-3</v>
+        <f>([1]Basic_load!$B$15*[1]Basic_load!G10)*0.85</f>
+        <v>4.6661634E-2</v>
       </c>
       <c r="P9" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G10)*0.1</f>
-        <v>2.7448020000000002E-3</v>
+        <f>([1]Basic_load!$B$16*[1]Basic_load!G10)*0.85</f>
+        <v>2.3330817E-2</v>
       </c>
       <c r="Q9" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G10)*0.1</f>
-        <v>2.7448020000000002E-3</v>
+        <f>([1]Basic_load!$B$17*[1]Basic_load!G10)*0.85</f>
+        <v>2.3330817E-2</v>
       </c>
       <c r="R9" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G10)*0.1</f>
-        <v>2.7448020000000002E-3</v>
+        <f>([1]Basic_load!$B$18*[1]Basic_load!G10)*0.85</f>
+        <v>2.3330817E-2</v>
       </c>
       <c r="S9" s="8">
-        <v>2.25</v>
+        <v>0.40879999999999994</v>
       </c>
       <c r="T9" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G10)*0.1</f>
-        <v>4.1172029999999998E-3</v>
+        <f>([1]Basic_load!$B$20*[1]Basic_load!G10)*0.85</f>
+        <v>3.4996225499999999E-2</v>
       </c>
       <c r="U9" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G10)*0.1</f>
-        <v>4.1172029999999998E-3</v>
+        <f>([1]Basic_load!$B$21*[1]Basic_load!G10)*0.85</f>
+        <v>3.4996225499999999E-2</v>
       </c>
       <c r="V9" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G10)*0.1</f>
-        <v>4.1172029999999998E-3</v>
+        <f>([1]Basic_load!$B$22*[1]Basic_load!G10)*0.85</f>
+        <v>3.4996225499999999E-2</v>
       </c>
       <c r="W9" s="7">
-        <f>([1]Basic_load!$B$23*[1]Basic_load!G10)*0.1</f>
-        <v>4.1172029999999998E-3</v>
+        <v>0.3281</v>
       </c>
       <c r="X9" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G10)*0.1</f>
-        <v>4.1172029999999998E-3</v>
+        <f>([1]Basic_load!$B$24*[1]Basic_load!G10)*0.85</f>
+        <v>3.4996225499999999E-2</v>
       </c>
       <c r="Y9" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G10)*0.1</f>
-        <v>1.9213614000000004E-2</v>
+        <f>([1]Basic_load!$B$25*[1]Basic_load!G10)*0.85</f>
+        <v>0.163315719</v>
       </c>
       <c r="Z9" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G10)*0.1</f>
-        <v>1.9213614000000004E-2</v>
+        <f>([1]Basic_load!$B$26*[1]Basic_load!G10)*0.85</f>
+        <v>0.163315719</v>
       </c>
       <c r="AA9" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G10)*0.1</f>
-        <v>2.7448020000000002E-3</v>
+        <f>([1]Basic_load!$B$27*[1]Basic_load!G10)*0.85</f>
+        <v>2.3330817E-2</v>
       </c>
       <c r="AB9" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G10)*0.1</f>
-        <v>2.7448020000000002E-3</v>
+        <f>([1]Basic_load!$B$28*[1]Basic_load!G10)*0.85</f>
+        <v>2.3330817E-2</v>
       </c>
       <c r="AC9" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G10)*0.1</f>
-        <v>2.7448020000000002E-3</v>
+        <f>([1]Basic_load!$B$29*[1]Basic_load!G10)*0.85</f>
+        <v>2.3330817E-2</v>
       </c>
       <c r="AD9" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G10)*0.1</f>
-        <v>5.4896040000000004E-3</v>
+        <f>([1]Basic_load!$B$30*[1]Basic_load!G10)*0.85</f>
+        <v>4.6661634E-2</v>
       </c>
       <c r="AE9" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G10)*0.1</f>
-        <v>9.1493400000000006E-3</v>
+        <f>([1]Basic_load!$B$31*[1]Basic_load!G10)*0.85</f>
+        <v>7.7769389999999994E-2</v>
       </c>
       <c r="AF9" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G10)*0.1</f>
-        <v>6.8620050000000009E-3</v>
+        <f>([1]Basic_load!$B$32*[1]Basic_load!G10)*0.85</f>
+        <v>5.8327042500000002E-2</v>
       </c>
       <c r="AG9" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G10)*0.1</f>
-        <v>9.6068070000000019E-3</v>
+        <f>([1]Basic_load!$B$33*[1]Basic_load!G10)*0.85</f>
+        <v>8.1657859499999999E-2</v>
       </c>
       <c r="AH9" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G10)*0.1</f>
-        <v>2.7448020000000002E-3</v>
+        <f>([1]Basic_load!$B$34*[1]Basic_load!G10)*0.85</f>
+        <v>2.3330817E-2</v>
       </c>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.3">
@@ -1903,135 +2629,134 @@
         <v>0.33333333333333398</v>
       </c>
       <c r="B10" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G11)*0.1</f>
+        <f>([1]Basic_load!$B$2*[1]Basic_load!G11)*0.85</f>
         <v>0</v>
       </c>
       <c r="C10" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G11)*0.1</f>
-        <v>9.6158300000000006E-3</v>
+        <f>([1]Basic_load!$B$3*[1]Basic_load!G11)*0.85</f>
+        <v>8.1734555E-2</v>
       </c>
       <c r="D10" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G11)*0.1</f>
-        <v>8.6542470000000003E-3</v>
+        <f>([1]Basic_load!$B$4*[1]Basic_load!G11)*0.85</f>
+        <v>7.3561099499999991E-2</v>
       </c>
       <c r="E10" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G11)*0.1</f>
-        <v>9.6158300000000006E-3</v>
+        <f>([1]Basic_load!$B$5*[1]Basic_load!G11)*0.85</f>
+        <v>8.1734555E-2</v>
       </c>
       <c r="F10" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G11)*0.1</f>
-        <v>5.7694979999999996E-3</v>
+        <f>([1]Basic_load!$B$6*[1]Basic_load!G11)*0.85</f>
+        <v>4.9040732999999996E-2</v>
       </c>
       <c r="G10" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G11)*0.1</f>
-        <v>5.7694979999999996E-3</v>
+        <f>([1]Basic_load!$B$7*[1]Basic_load!G11)*0.85</f>
+        <v>4.9040732999999996E-2</v>
       </c>
       <c r="H10" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G11)*0.1</f>
-        <v>1.9231660000000001E-2</v>
+        <f>([1]Basic_load!$B$8*[1]Basic_load!G11)*0.85</f>
+        <v>0.16346911</v>
       </c>
       <c r="I10" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G11)*0.1</f>
-        <v>1.9231660000000001E-2</v>
+        <f>([1]Basic_load!$B$9*[1]Basic_load!G11)*0.85</f>
+        <v>0.16346911</v>
       </c>
       <c r="J10" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G11)*0.1</f>
-        <v>5.7694979999999996E-3</v>
+        <f>([1]Basic_load!$B$10*[1]Basic_load!G11)*0.85</f>
+        <v>4.9040732999999996E-2</v>
       </c>
       <c r="K10" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G11)*0.1</f>
-        <v>5.7694979999999996E-3</v>
+        <f>([1]Basic_load!$B$11*[1]Basic_load!G11)*0.85</f>
+        <v>4.9040732999999996E-2</v>
       </c>
       <c r="L10" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G11)*0.1</f>
-        <v>4.3271235000000002E-3</v>
+        <f>([1]Basic_load!$B$12*[1]Basic_load!G11)*0.85</f>
+        <v>3.6780549749999995E-2</v>
       </c>
       <c r="M10" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G11)*0.1</f>
-        <v>5.7694979999999996E-3</v>
+        <f>([1]Basic_load!$B$13*[1]Basic_load!G11)*0.85</f>
+        <v>4.9040732999999996E-2</v>
       </c>
       <c r="N10" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G11)*0.1</f>
-        <v>5.7694979999999996E-3</v>
+        <f>([1]Basic_load!$B$14*[1]Basic_load!G11)*0.85</f>
+        <v>4.9040732999999996E-2</v>
       </c>
       <c r="O10" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G11)*0.1</f>
-        <v>1.1538995999999999E-2</v>
+        <f>([1]Basic_load!$B$15*[1]Basic_load!G11)*0.85</f>
+        <v>9.8081465999999992E-2</v>
       </c>
       <c r="P10" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G11)*0.1</f>
-        <v>5.7694979999999996E-3</v>
+        <f>([1]Basic_load!$B$16*[1]Basic_load!G11)*0.85</f>
+        <v>4.9040732999999996E-2</v>
       </c>
       <c r="Q10" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G11)*0.1</f>
-        <v>5.7694979999999996E-3</v>
+        <f>([1]Basic_load!$B$17*[1]Basic_load!G11)*0.85</f>
+        <v>4.9040732999999996E-2</v>
       </c>
       <c r="R10" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G11)*0.1</f>
-        <v>5.7694979999999996E-3</v>
+        <f>([1]Basic_load!$B$18*[1]Basic_load!G11)*0.85</f>
+        <v>4.9040732999999996E-2</v>
       </c>
       <c r="S10" s="8">
-        <v>3</v>
+        <v>0.40879999999999994</v>
       </c>
       <c r="T10" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G11)*0.1</f>
-        <v>8.6542470000000003E-3</v>
+        <f>([1]Basic_load!$B$20*[1]Basic_load!G11)*0.85</f>
+        <v>7.3561099499999991E-2</v>
       </c>
       <c r="U10" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G11)*0.1</f>
-        <v>8.6542470000000003E-3</v>
+        <f>([1]Basic_load!$B$21*[1]Basic_load!G11)*0.85</f>
+        <v>7.3561099499999991E-2</v>
       </c>
       <c r="V10" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G11)*0.1</f>
-        <v>8.6542470000000003E-3</v>
+        <f>([1]Basic_load!$B$22*[1]Basic_load!G11)*0.85</f>
+        <v>7.3561099499999991E-2</v>
       </c>
       <c r="W10" s="7">
-        <f>([1]Basic_load!$B$23*[1]Basic_load!G11)*0.1</f>
-        <v>8.6542470000000003E-3</v>
+        <v>0.40375</v>
       </c>
       <c r="X10" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G11)*0.1</f>
-        <v>8.6542470000000003E-3</v>
+        <f>([1]Basic_load!$B$24*[1]Basic_load!G11)*0.85</f>
+        <v>7.3561099499999991E-2</v>
       </c>
       <c r="Y10" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G11)*0.1</f>
-        <v>4.0386485999999999E-2</v>
+        <f>([1]Basic_load!$B$25*[1]Basic_load!G11)*0.85</f>
+        <v>0.34328513099999997</v>
       </c>
       <c r="Z10" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G11)*0.1</f>
-        <v>4.0386485999999999E-2</v>
+        <f>([1]Basic_load!$B$26*[1]Basic_load!G11)*0.85</f>
+        <v>0.34328513099999997</v>
       </c>
       <c r="AA10" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G11)*0.1</f>
-        <v>5.7694979999999996E-3</v>
+        <f>([1]Basic_load!$B$27*[1]Basic_load!G11)*0.85</f>
+        <v>4.9040732999999996E-2</v>
       </c>
       <c r="AB10" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G11)*0.1</f>
-        <v>5.7694979999999996E-3</v>
+        <f>([1]Basic_load!$B$28*[1]Basic_load!G11)*0.85</f>
+        <v>4.9040732999999996E-2</v>
       </c>
       <c r="AC10" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G11)*0.1</f>
-        <v>5.7694979999999996E-3</v>
+        <f>([1]Basic_load!$B$29*[1]Basic_load!G11)*0.85</f>
+        <v>4.9040732999999996E-2</v>
       </c>
       <c r="AD10" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G11)*0.1</f>
-        <v>1.1538995999999999E-2</v>
+        <f>([1]Basic_load!$B$30*[1]Basic_load!G11)*0.85</f>
+        <v>9.8081465999999992E-2</v>
       </c>
       <c r="AE10" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G11)*0.1</f>
-        <v>1.9231660000000001E-2</v>
+        <f>([1]Basic_load!$B$31*[1]Basic_load!G11)*0.85</f>
+        <v>0.16346911</v>
       </c>
       <c r="AF10" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G11)*0.1</f>
-        <v>1.4423745E-2</v>
+        <f>([1]Basic_load!$B$32*[1]Basic_load!G11)*0.85</f>
+        <v>0.12260183249999999</v>
       </c>
       <c r="AG10" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G11)*0.1</f>
-        <v>2.0193243E-2</v>
+        <f>([1]Basic_load!$B$33*[1]Basic_load!G11)*0.85</f>
+        <v>0.17164256549999998</v>
       </c>
       <c r="AH10" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G11)*0.1</f>
-        <v>5.7694979999999996E-3</v>
+        <f>([1]Basic_load!$B$34*[1]Basic_load!G11)*0.85</f>
+        <v>4.9040732999999996E-2</v>
       </c>
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.3">
@@ -2039,135 +2764,134 @@
         <v>0.375</v>
       </c>
       <c r="B11" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G12)*0.1</f>
+        <f>([1]Basic_load!$B$2*[1]Basic_load!G12)*0.85</f>
         <v>0</v>
       </c>
       <c r="C11" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G12)*0.1</f>
-        <v>1.4178500000000004E-2</v>
+        <f>([1]Basic_load!$B$3*[1]Basic_load!G12)*0.85</f>
+        <v>0.12051725000000002</v>
       </c>
       <c r="D11" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G12)*0.1</f>
-        <v>1.2760650000000002E-2</v>
+        <f>([1]Basic_load!$B$4*[1]Basic_load!G12)*0.85</f>
+        <v>0.10846552500000001</v>
       </c>
       <c r="E11" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G12)*0.1</f>
-        <v>1.4178500000000004E-2</v>
+        <f>([1]Basic_load!$B$5*[1]Basic_load!G12)*0.85</f>
+        <v>0.12051725000000002</v>
       </c>
       <c r="F11" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G12)*0.1</f>
-        <v>8.5071000000000001E-3</v>
+        <f>([1]Basic_load!$B$6*[1]Basic_load!G12)*0.85</f>
+        <v>7.2310349999999995E-2</v>
       </c>
       <c r="G11" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G12)*0.1</f>
-        <v>8.5071000000000001E-3</v>
+        <f>([1]Basic_load!$B$7*[1]Basic_load!G12)*0.85</f>
+        <v>7.2310349999999995E-2</v>
       </c>
       <c r="H11" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G12)*0.1</f>
-        <v>2.8357000000000007E-2</v>
+        <f>([1]Basic_load!$B$8*[1]Basic_load!G12)*0.85</f>
+        <v>0.24103450000000004</v>
       </c>
       <c r="I11" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G12)*0.1</f>
-        <v>2.8357000000000007E-2</v>
+        <f>([1]Basic_load!$B$9*[1]Basic_load!G12)*0.85</f>
+        <v>0.24103450000000004</v>
       </c>
       <c r="J11" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G12)*0.1</f>
-        <v>8.5071000000000001E-3</v>
+        <f>([1]Basic_load!$B$10*[1]Basic_load!G12)*0.85</f>
+        <v>7.2310349999999995E-2</v>
       </c>
       <c r="K11" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G12)*0.1</f>
-        <v>8.5071000000000001E-3</v>
+        <f>([1]Basic_load!$B$11*[1]Basic_load!G12)*0.85</f>
+        <v>7.2310349999999995E-2</v>
       </c>
       <c r="L11" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G12)*0.1</f>
-        <v>6.3803250000000009E-3</v>
+        <f>([1]Basic_load!$B$12*[1]Basic_load!G12)*0.85</f>
+        <v>5.4232762500000004E-2</v>
       </c>
       <c r="M11" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G12)*0.1</f>
-        <v>8.5071000000000001E-3</v>
+        <f>([1]Basic_load!$B$13*[1]Basic_load!G12)*0.85</f>
+        <v>7.2310349999999995E-2</v>
       </c>
       <c r="N11" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G12)*0.1</f>
-        <v>8.5071000000000001E-3</v>
+        <f>([1]Basic_load!$B$14*[1]Basic_load!G12)*0.85</f>
+        <v>7.2310349999999995E-2</v>
       </c>
       <c r="O11" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G12)*0.1</f>
-        <v>1.70142E-2</v>
+        <f>([1]Basic_load!$B$15*[1]Basic_load!G12)*0.85</f>
+        <v>0.14462069999999999</v>
       </c>
       <c r="P11" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G12)*0.1</f>
-        <v>8.5071000000000001E-3</v>
+        <f>([1]Basic_load!$B$16*[1]Basic_load!G12)*0.85</f>
+        <v>7.2310349999999995E-2</v>
       </c>
       <c r="Q11" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G12)*0.1</f>
-        <v>8.5071000000000001E-3</v>
+        <f>([1]Basic_load!$B$17*[1]Basic_load!G12)*0.85</f>
+        <v>7.2310349999999995E-2</v>
       </c>
       <c r="R11" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G12)*0.1</f>
-        <v>8.5071000000000001E-3</v>
+        <f>([1]Basic_load!$B$18*[1]Basic_load!G12)*0.85</f>
+        <v>7.2310349999999995E-2</v>
       </c>
       <c r="S11" s="8">
-        <v>3.7500000000000004</v>
+        <v>0.40879999999999994</v>
       </c>
       <c r="T11" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G12)*0.1</f>
-        <v>1.2760650000000002E-2</v>
+        <f>([1]Basic_load!$B$20*[1]Basic_load!G12)*0.85</f>
+        <v>0.10846552500000001</v>
       </c>
       <c r="U11" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G12)*0.1</f>
-        <v>1.2760650000000002E-2</v>
+        <f>([1]Basic_load!$B$21*[1]Basic_load!G12)*0.85</f>
+        <v>0.10846552500000001</v>
       </c>
       <c r="V11" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G12)*0.1</f>
-        <v>1.2760650000000002E-2</v>
+        <f>([1]Basic_load!$B$22*[1]Basic_load!G12)*0.85</f>
+        <v>0.10846552500000001</v>
       </c>
       <c r="W11" s="7">
-        <f>([1]Basic_load!$B$23*[1]Basic_load!G12)*0.1</f>
-        <v>1.2760650000000002E-2</v>
+        <v>0.4471</v>
       </c>
       <c r="X11" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G12)*0.1</f>
-        <v>1.2760650000000002E-2</v>
+        <f>([1]Basic_load!$B$24*[1]Basic_load!G12)*0.85</f>
+        <v>0.10846552500000001</v>
       </c>
       <c r="Y11" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G12)*0.1</f>
-        <v>5.9549700000000011E-2</v>
+        <f>([1]Basic_load!$B$25*[1]Basic_load!G12)*0.85</f>
+        <v>0.50617245</v>
       </c>
       <c r="Z11" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G12)*0.1</f>
-        <v>5.9549700000000011E-2</v>
+        <f>([1]Basic_load!$B$26*[1]Basic_load!G12)*0.85</f>
+        <v>0.50617245</v>
       </c>
       <c r="AA11" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G12)*0.1</f>
-        <v>8.5071000000000001E-3</v>
+        <f>([1]Basic_load!$B$27*[1]Basic_load!G12)*0.85</f>
+        <v>7.2310349999999995E-2</v>
       </c>
       <c r="AB11" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G12)*0.1</f>
-        <v>8.5071000000000001E-3</v>
+        <f>([1]Basic_load!$B$28*[1]Basic_load!G12)*0.85</f>
+        <v>7.2310349999999995E-2</v>
       </c>
       <c r="AC11" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G12)*0.1</f>
-        <v>8.5071000000000001E-3</v>
+        <f>([1]Basic_load!$B$29*[1]Basic_load!G12)*0.85</f>
+        <v>7.2310349999999995E-2</v>
       </c>
       <c r="AD11" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G12)*0.1</f>
-        <v>1.70142E-2</v>
+        <f>([1]Basic_load!$B$30*[1]Basic_load!G12)*0.85</f>
+        <v>0.14462069999999999</v>
       </c>
       <c r="AE11" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G12)*0.1</f>
-        <v>2.8357000000000007E-2</v>
+        <f>([1]Basic_load!$B$31*[1]Basic_load!G12)*0.85</f>
+        <v>0.24103450000000004</v>
       </c>
       <c r="AF11" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G12)*0.1</f>
-        <v>2.1267750000000002E-2</v>
+        <f>([1]Basic_load!$B$32*[1]Basic_load!G12)*0.85</f>
+        <v>0.18077587499999997</v>
       </c>
       <c r="AG11" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G12)*0.1</f>
-        <v>2.9774850000000005E-2</v>
+        <f>([1]Basic_load!$B$33*[1]Basic_load!G12)*0.85</f>
+        <v>0.253086225</v>
       </c>
       <c r="AH11" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G12)*0.1</f>
-        <v>8.5071000000000001E-3</v>
+        <f>([1]Basic_load!$B$34*[1]Basic_load!G12)*0.85</f>
+        <v>7.2310349999999995E-2</v>
       </c>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.3">
@@ -2175,135 +2899,134 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B12" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G13)*0.1</f>
+        <f>([1]Basic_load!$B$2*[1]Basic_load!G13)*0.85</f>
         <v>0</v>
       </c>
       <c r="C12" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G13)*0.1</f>
-        <v>2.2084000000000006E-2</v>
+        <f>([1]Basic_load!$B$3*[1]Basic_load!G13)*0.85</f>
+        <v>0.18771400000000002</v>
       </c>
       <c r="D12" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G13)*0.1</f>
-        <v>1.9875600000000004E-2</v>
+        <f>([1]Basic_load!$B$4*[1]Basic_load!G13)*0.85</f>
+        <v>0.1689426</v>
       </c>
       <c r="E12" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G13)*0.1</f>
-        <v>2.2084000000000006E-2</v>
+        <f>([1]Basic_load!$B$5*[1]Basic_load!G13)*0.85</f>
+        <v>0.18771400000000002</v>
       </c>
       <c r="F12" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G13)*0.1</f>
-        <v>1.3250400000000002E-2</v>
+        <f>([1]Basic_load!$B$6*[1]Basic_load!G13)*0.85</f>
+        <v>0.1126284</v>
       </c>
       <c r="G12" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G13)*0.1</f>
-        <v>1.3250400000000002E-2</v>
+        <f>([1]Basic_load!$B$7*[1]Basic_load!G13)*0.85</f>
+        <v>0.1126284</v>
       </c>
       <c r="H12" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G13)*0.1</f>
-        <v>4.4168000000000013E-2</v>
+        <f>([1]Basic_load!$B$8*[1]Basic_load!G13)*0.85</f>
+        <v>0.37542800000000004</v>
       </c>
       <c r="I12" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G13)*0.1</f>
-        <v>4.4168000000000013E-2</v>
+        <f>([1]Basic_load!$B$9*[1]Basic_load!G13)*0.85</f>
+        <v>0.37542800000000004</v>
       </c>
       <c r="J12" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G13)*0.1</f>
-        <v>1.3250400000000002E-2</v>
+        <f>([1]Basic_load!$B$10*[1]Basic_load!G13)*0.85</f>
+        <v>0.1126284</v>
       </c>
       <c r="K12" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G13)*0.1</f>
-        <v>1.3250400000000002E-2</v>
+        <f>([1]Basic_load!$B$11*[1]Basic_load!G13)*0.85</f>
+        <v>0.1126284</v>
       </c>
       <c r="L12" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G13)*0.1</f>
-        <v>9.9378000000000018E-3</v>
+        <f>([1]Basic_load!$B$12*[1]Basic_load!G13)*0.85</f>
+        <v>8.4471299999999999E-2</v>
       </c>
       <c r="M12" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G13)*0.1</f>
-        <v>1.3250400000000002E-2</v>
+        <f>([1]Basic_load!$B$13*[1]Basic_load!G13)*0.85</f>
+        <v>0.1126284</v>
       </c>
       <c r="N12" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G13)*0.1</f>
-        <v>1.3250400000000002E-2</v>
+        <f>([1]Basic_load!$B$14*[1]Basic_load!G13)*0.85</f>
+        <v>0.1126284</v>
       </c>
       <c r="O12" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G13)*0.1</f>
-        <v>2.6500800000000005E-2</v>
+        <f>([1]Basic_load!$B$15*[1]Basic_load!G13)*0.85</f>
+        <v>0.22525680000000001</v>
       </c>
       <c r="P12" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G13)*0.1</f>
-        <v>1.3250400000000002E-2</v>
+        <f>([1]Basic_load!$B$16*[1]Basic_load!G13)*0.85</f>
+        <v>0.1126284</v>
       </c>
       <c r="Q12" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G13)*0.1</f>
-        <v>1.3250400000000002E-2</v>
+        <f>([1]Basic_load!$B$17*[1]Basic_load!G13)*0.85</f>
+        <v>0.1126284</v>
       </c>
       <c r="R12" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G13)*0.1</f>
-        <v>1.3250400000000002E-2</v>
+        <f>([1]Basic_load!$B$18*[1]Basic_load!G13)*0.85</f>
+        <v>0.1126284</v>
       </c>
       <c r="S12" s="8">
-        <v>3.7500000000000004</v>
+        <v>0.40879999999999994</v>
       </c>
       <c r="T12" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G13)*0.1</f>
-        <v>1.9875600000000004E-2</v>
+        <f>([1]Basic_load!$B$20*[1]Basic_load!G13)*0.85</f>
+        <v>0.1689426</v>
       </c>
       <c r="U12" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G13)*0.1</f>
-        <v>1.9875600000000004E-2</v>
+        <f>([1]Basic_load!$B$21*[1]Basic_load!G13)*0.85</f>
+        <v>0.1689426</v>
       </c>
       <c r="V12" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G13)*0.1</f>
-        <v>1.9875600000000004E-2</v>
+        <f>([1]Basic_load!$B$22*[1]Basic_load!G13)*0.85</f>
+        <v>0.1689426</v>
       </c>
       <c r="W12" s="7">
-        <f>([1]Basic_load!$B$23*[1]Basic_load!G13)*0.1</f>
-        <v>1.9875600000000004E-2</v>
+        <v>0.45135000000000003</v>
       </c>
       <c r="X12" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G13)*0.1</f>
-        <v>1.9875600000000004E-2</v>
+        <f>([1]Basic_load!$B$24*[1]Basic_load!G13)*0.85</f>
+        <v>0.1689426</v>
       </c>
       <c r="Y12" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G13)*0.1</f>
-        <v>9.275280000000001E-2</v>
+        <f>([1]Basic_load!$B$25*[1]Basic_load!G13)*0.85</f>
+        <v>0.78839879999999996</v>
       </c>
       <c r="Z12" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G13)*0.1</f>
-        <v>9.275280000000001E-2</v>
+        <f>([1]Basic_load!$B$26*[1]Basic_load!G13)*0.85</f>
+        <v>0.78839879999999996</v>
       </c>
       <c r="AA12" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G13)*0.1</f>
-        <v>1.3250400000000002E-2</v>
+        <f>([1]Basic_load!$B$27*[1]Basic_load!G13)*0.85</f>
+        <v>0.1126284</v>
       </c>
       <c r="AB12" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G13)*0.1</f>
-        <v>1.3250400000000002E-2</v>
+        <f>([1]Basic_load!$B$28*[1]Basic_load!G13)*0.85</f>
+        <v>0.1126284</v>
       </c>
       <c r="AC12" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G13)*0.1</f>
-        <v>1.3250400000000002E-2</v>
+        <f>([1]Basic_load!$B$29*[1]Basic_load!G13)*0.85</f>
+        <v>0.1126284</v>
       </c>
       <c r="AD12" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G13)*0.1</f>
-        <v>2.6500800000000005E-2</v>
+        <f>([1]Basic_load!$B$30*[1]Basic_load!G13)*0.85</f>
+        <v>0.22525680000000001</v>
       </c>
       <c r="AE12" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G13)*0.1</f>
-        <v>4.4168000000000013E-2</v>
+        <f>([1]Basic_load!$B$31*[1]Basic_load!G13)*0.85</f>
+        <v>0.37542800000000004</v>
       </c>
       <c r="AF12" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G13)*0.1</f>
-        <v>3.3126000000000003E-2</v>
+        <f>([1]Basic_load!$B$32*[1]Basic_load!G13)*0.85</f>
+        <v>0.28157100000000002</v>
       </c>
       <c r="AG12" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G13)*0.1</f>
-        <v>4.6376400000000005E-2</v>
+        <f>([1]Basic_load!$B$33*[1]Basic_load!G13)*0.85</f>
+        <v>0.39419939999999998</v>
       </c>
       <c r="AH12" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G13)*0.1</f>
-        <v>1.3250400000000002E-2</v>
+        <f>([1]Basic_load!$B$34*[1]Basic_load!G13)*0.85</f>
+        <v>0.1126284</v>
       </c>
     </row>
     <row r="13" spans="1:34" x14ac:dyDescent="0.3">
@@ -2311,135 +3034,134 @@
         <v>0.45833333333333398</v>
       </c>
       <c r="B13" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G14)*0.1</f>
+        <f>([1]Basic_load!$B$2*[1]Basic_load!G14)*0.85</f>
         <v>0</v>
       </c>
       <c r="C13" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G14)*0.1</f>
-        <v>1.4340000000000002E-3</v>
+        <f>([1]Basic_load!$B$3*[1]Basic_load!G14)*0.85</f>
+        <v>1.2189E-2</v>
       </c>
       <c r="D13" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G14)*0.1</f>
-        <v>1.2906E-3</v>
+        <f>([1]Basic_load!$B$4*[1]Basic_load!G14)*0.85</f>
+        <v>1.0970099999999998E-2</v>
       </c>
       <c r="E13" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G14)*0.1</f>
-        <v>1.4340000000000002E-3</v>
+        <f>([1]Basic_load!$B$5*[1]Basic_load!G14)*0.85</f>
+        <v>1.2189E-2</v>
       </c>
       <c r="F13" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G14)*0.1</f>
-        <v>8.6039999999999988E-4</v>
+        <f>([1]Basic_load!$B$6*[1]Basic_load!G14)*0.85</f>
+        <v>7.3133999999999985E-3</v>
       </c>
       <c r="G13" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G14)*0.1</f>
-        <v>8.6039999999999988E-4</v>
+        <f>([1]Basic_load!$B$7*[1]Basic_load!G14)*0.85</f>
+        <v>7.3133999999999985E-3</v>
       </c>
       <c r="H13" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G14)*0.1</f>
-        <v>2.8680000000000003E-3</v>
+        <f>([1]Basic_load!$B$8*[1]Basic_load!G14)*0.85</f>
+        <v>2.4378E-2</v>
       </c>
       <c r="I13" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G14)*0.1</f>
-        <v>2.8680000000000003E-3</v>
+        <f>([1]Basic_load!$B$9*[1]Basic_load!G14)*0.85</f>
+        <v>2.4378E-2</v>
       </c>
       <c r="J13" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G14)*0.1</f>
-        <v>8.6039999999999988E-4</v>
+        <f>([1]Basic_load!$B$10*[1]Basic_load!G14)*0.85</f>
+        <v>7.3133999999999985E-3</v>
       </c>
       <c r="K13" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G14)*0.1</f>
-        <v>8.6039999999999988E-4</v>
+        <f>([1]Basic_load!$B$11*[1]Basic_load!G14)*0.85</f>
+        <v>7.3133999999999985E-3</v>
       </c>
       <c r="L13" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G14)*0.1</f>
-        <v>6.4530000000000002E-4</v>
+        <f>([1]Basic_load!$B$12*[1]Basic_load!G14)*0.85</f>
+        <v>5.4850499999999991E-3</v>
       </c>
       <c r="M13" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G14)*0.1</f>
-        <v>8.6039999999999988E-4</v>
+        <f>([1]Basic_load!$B$13*[1]Basic_load!G14)*0.85</f>
+        <v>7.3133999999999985E-3</v>
       </c>
       <c r="N13" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G14)*0.1</f>
-        <v>8.6039999999999988E-4</v>
+        <f>([1]Basic_load!$B$14*[1]Basic_load!G14)*0.85</f>
+        <v>7.3133999999999985E-3</v>
       </c>
       <c r="O13" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G14)*0.1</f>
-        <v>1.7207999999999998E-3</v>
+        <f>([1]Basic_load!$B$15*[1]Basic_load!G14)*0.85</f>
+        <v>1.4626799999999997E-2</v>
       </c>
       <c r="P13" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G14)*0.1</f>
-        <v>8.6039999999999988E-4</v>
+        <f>([1]Basic_load!$B$16*[1]Basic_load!G14)*0.85</f>
+        <v>7.3133999999999985E-3</v>
       </c>
       <c r="Q13" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G14)*0.1</f>
-        <v>8.6039999999999988E-4</v>
+        <f>([1]Basic_load!$B$17*[1]Basic_load!G14)*0.85</f>
+        <v>7.3133999999999985E-3</v>
       </c>
       <c r="R13" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G14)*0.1</f>
-        <v>8.6039999999999988E-4</v>
+        <f>([1]Basic_load!$B$18*[1]Basic_load!G14)*0.85</f>
+        <v>7.3133999999999985E-3</v>
       </c>
       <c r="S13" s="8">
-        <v>3.5000000000000004</v>
+        <v>0.40879999999999994</v>
       </c>
       <c r="T13" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G14)*0.1</f>
-        <v>1.2906E-3</v>
+        <f>([1]Basic_load!$B$20*[1]Basic_load!G14)*0.85</f>
+        <v>1.0970099999999998E-2</v>
       </c>
       <c r="U13" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G14)*0.1</f>
-        <v>1.2906E-3</v>
+        <f>([1]Basic_load!$B$21*[1]Basic_load!G14)*0.85</f>
+        <v>1.0970099999999998E-2</v>
       </c>
       <c r="V13" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G14)*0.1</f>
-        <v>1.2906E-3</v>
+        <f>([1]Basic_load!$B$22*[1]Basic_load!G14)*0.85</f>
+        <v>1.0970099999999998E-2</v>
       </c>
       <c r="W13" s="7">
-        <f>([1]Basic_load!$B$23*[1]Basic_load!G14)*0.1</f>
-        <v>1.2906E-3</v>
+        <v>0.44540000000000002</v>
       </c>
       <c r="X13" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G14)*0.1</f>
-        <v>1.2906E-3</v>
+        <f>([1]Basic_load!$B$24*[1]Basic_load!G14)*0.85</f>
+        <v>1.0970099999999998E-2</v>
       </c>
       <c r="Y13" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G14)*0.1</f>
-        <v>6.0228E-3</v>
+        <f>([1]Basic_load!$B$25*[1]Basic_load!G14)*0.85</f>
+        <v>5.1193799999999998E-2</v>
       </c>
       <c r="Z13" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G14)*0.1</f>
-        <v>6.0228E-3</v>
+        <f>([1]Basic_load!$B$26*[1]Basic_load!G14)*0.85</f>
+        <v>5.1193799999999998E-2</v>
       </c>
       <c r="AA13" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G14)*0.1</f>
-        <v>8.6039999999999988E-4</v>
+        <f>([1]Basic_load!$B$27*[1]Basic_load!G14)*0.85</f>
+        <v>7.3133999999999985E-3</v>
       </c>
       <c r="AB13" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G14)*0.1</f>
-        <v>8.6039999999999988E-4</v>
+        <f>([1]Basic_load!$B$28*[1]Basic_load!G14)*0.85</f>
+        <v>7.3133999999999985E-3</v>
       </c>
       <c r="AC13" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G14)*0.1</f>
-        <v>8.6039999999999988E-4</v>
+        <f>([1]Basic_load!$B$29*[1]Basic_load!G14)*0.85</f>
+        <v>7.3133999999999985E-3</v>
       </c>
       <c r="AD13" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G14)*0.1</f>
-        <v>1.7207999999999998E-3</v>
+        <f>([1]Basic_load!$B$30*[1]Basic_load!G14)*0.85</f>
+        <v>1.4626799999999997E-2</v>
       </c>
       <c r="AE13" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G14)*0.1</f>
-        <v>2.8680000000000003E-3</v>
+        <f>([1]Basic_load!$B$31*[1]Basic_load!G14)*0.85</f>
+        <v>2.4378E-2</v>
       </c>
       <c r="AF13" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G14)*0.1</f>
-        <v>2.1509999999999997E-3</v>
+        <f>([1]Basic_load!$B$32*[1]Basic_load!G14)*0.85</f>
+        <v>1.8283499999999998E-2</v>
       </c>
       <c r="AG13" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G14)*0.1</f>
-        <v>3.0114E-3</v>
+        <f>([1]Basic_load!$B$33*[1]Basic_load!G14)*0.85</f>
+        <v>2.5596899999999999E-2</v>
       </c>
       <c r="AH13" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G14)*0.1</f>
-        <v>8.6039999999999988E-4</v>
+        <f>([1]Basic_load!$B$34*[1]Basic_load!G14)*0.85</f>
+        <v>7.3133999999999985E-3</v>
       </c>
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.3">
@@ -2447,135 +3169,134 @@
         <v>0.5</v>
       </c>
       <c r="B14" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G15)*0.1</f>
+        <f>([1]Basic_load!$B$2*[1]Basic_load!G15)*0.85</f>
         <v>0</v>
       </c>
       <c r="C14" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G15)*0.1</f>
-        <v>6.6150000000000009E-4</v>
+        <f>([1]Basic_load!$B$3*[1]Basic_load!G15)*0.85</f>
+        <v>5.6227500000000001E-3</v>
       </c>
       <c r="D14" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G15)*0.1</f>
-        <v>5.9535000000000002E-4</v>
+        <f>([1]Basic_load!$B$4*[1]Basic_load!G15)*0.85</f>
+        <v>5.0604749999999992E-3</v>
       </c>
       <c r="E14" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G15)*0.1</f>
-        <v>6.6150000000000009E-4</v>
+        <f>([1]Basic_load!$B$5*[1]Basic_load!G15)*0.85</f>
+        <v>5.6227500000000001E-3</v>
       </c>
       <c r="F14" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G15)*0.1</f>
-        <v>3.9690000000000005E-4</v>
+        <f>([1]Basic_load!$B$6*[1]Basic_load!G15)*0.85</f>
+        <v>3.3736500000000002E-3</v>
       </c>
       <c r="G14" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G15)*0.1</f>
-        <v>3.9690000000000005E-4</v>
+        <f>([1]Basic_load!$B$7*[1]Basic_load!G15)*0.85</f>
+        <v>3.3736500000000002E-3</v>
       </c>
       <c r="H14" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G15)*0.1</f>
-        <v>1.3230000000000002E-3</v>
+        <f>([1]Basic_load!$B$8*[1]Basic_load!G15)*0.85</f>
+        <v>1.12455E-2</v>
       </c>
       <c r="I14" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G15)*0.1</f>
-        <v>1.3230000000000002E-3</v>
+        <f>([1]Basic_load!$B$9*[1]Basic_load!G15)*0.85</f>
+        <v>1.12455E-2</v>
       </c>
       <c r="J14" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G15)*0.1</f>
-        <v>3.9690000000000005E-4</v>
+        <f>([1]Basic_load!$B$10*[1]Basic_load!G15)*0.85</f>
+        <v>3.3736500000000002E-3</v>
       </c>
       <c r="K14" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G15)*0.1</f>
-        <v>3.9690000000000005E-4</v>
+        <f>([1]Basic_load!$B$11*[1]Basic_load!G15)*0.85</f>
+        <v>3.3736500000000002E-3</v>
       </c>
       <c r="L14" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G15)*0.1</f>
-        <v>2.9767500000000001E-4</v>
+        <f>([1]Basic_load!$B$12*[1]Basic_load!G15)*0.85</f>
+        <v>2.5302374999999996E-3</v>
       </c>
       <c r="M14" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G15)*0.1</f>
-        <v>3.9690000000000005E-4</v>
+        <f>([1]Basic_load!$B$13*[1]Basic_load!G15)*0.85</f>
+        <v>3.3736500000000002E-3</v>
       </c>
       <c r="N14" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G15)*0.1</f>
-        <v>3.9690000000000005E-4</v>
+        <f>([1]Basic_load!$B$14*[1]Basic_load!G15)*0.85</f>
+        <v>3.3736500000000002E-3</v>
       </c>
       <c r="O14" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G15)*0.1</f>
-        <v>7.938000000000001E-4</v>
+        <f>([1]Basic_load!$B$15*[1]Basic_load!G15)*0.85</f>
+        <v>6.7473000000000003E-3</v>
       </c>
       <c r="P14" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G15)*0.1</f>
-        <v>3.9690000000000005E-4</v>
+        <f>([1]Basic_load!$B$16*[1]Basic_load!G15)*0.85</f>
+        <v>3.3736500000000002E-3</v>
       </c>
       <c r="Q14" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G15)*0.1</f>
-        <v>3.9690000000000005E-4</v>
+        <f>([1]Basic_load!$B$17*[1]Basic_load!G15)*0.85</f>
+        <v>3.3736500000000002E-3</v>
       </c>
       <c r="R14" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G15)*0.1</f>
-        <v>3.9690000000000005E-4</v>
+        <f>([1]Basic_load!$B$18*[1]Basic_load!G15)*0.85</f>
+        <v>3.3736500000000002E-3</v>
       </c>
       <c r="S14" s="8">
-        <v>3</v>
+        <v>0.40879999999999994</v>
       </c>
       <c r="T14" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G15)*0.1</f>
-        <v>5.9535000000000002E-4</v>
+        <f>([1]Basic_load!$B$20*[1]Basic_load!G15)*0.85</f>
+        <v>5.0604749999999992E-3</v>
       </c>
       <c r="U14" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G15)*0.1</f>
-        <v>5.9535000000000002E-4</v>
+        <f>([1]Basic_load!$B$21*[1]Basic_load!G15)*0.85</f>
+        <v>5.0604749999999992E-3</v>
       </c>
       <c r="V14" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G15)*0.1</f>
-        <v>5.9535000000000002E-4</v>
+        <f>([1]Basic_load!$B$22*[1]Basic_load!G15)*0.85</f>
+        <v>5.0604749999999992E-3</v>
       </c>
       <c r="W14" s="7">
-        <f>([1]Basic_load!$B$23*[1]Basic_load!G15)*0.1</f>
-        <v>5.9535000000000002E-4</v>
+        <v>0.41394999999999998</v>
       </c>
       <c r="X14" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G15)*0.1</f>
-        <v>5.9535000000000002E-4</v>
+        <f>([1]Basic_load!$B$24*[1]Basic_load!G15)*0.85</f>
+        <v>5.0604749999999992E-3</v>
       </c>
       <c r="Y14" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G15)*0.1</f>
-        <v>2.7783E-3</v>
+        <f>([1]Basic_load!$B$25*[1]Basic_load!G15)*0.85</f>
+        <v>2.3615549999999999E-2</v>
       </c>
       <c r="Z14" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G15)*0.1</f>
-        <v>2.7783E-3</v>
+        <f>([1]Basic_load!$B$26*[1]Basic_load!G15)*0.85</f>
+        <v>2.3615549999999999E-2</v>
       </c>
       <c r="AA14" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G15)*0.1</f>
-        <v>3.9690000000000005E-4</v>
+        <f>([1]Basic_load!$B$27*[1]Basic_load!G15)*0.85</f>
+        <v>3.3736500000000002E-3</v>
       </c>
       <c r="AB14" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G15)*0.1</f>
-        <v>3.9690000000000005E-4</v>
+        <f>([1]Basic_load!$B$28*[1]Basic_load!G15)*0.85</f>
+        <v>3.3736500000000002E-3</v>
       </c>
       <c r="AC14" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G15)*0.1</f>
-        <v>3.9690000000000005E-4</v>
+        <f>([1]Basic_load!$B$29*[1]Basic_load!G15)*0.85</f>
+        <v>3.3736500000000002E-3</v>
       </c>
       <c r="AD14" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G15)*0.1</f>
-        <v>7.938000000000001E-4</v>
+        <f>([1]Basic_load!$B$30*[1]Basic_load!G15)*0.85</f>
+        <v>6.7473000000000003E-3</v>
       </c>
       <c r="AE14" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G15)*0.1</f>
-        <v>1.3230000000000002E-3</v>
+        <f>([1]Basic_load!$B$31*[1]Basic_load!G15)*0.85</f>
+        <v>1.12455E-2</v>
       </c>
       <c r="AF14" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G15)*0.1</f>
-        <v>9.9224999999999986E-4</v>
+        <f>([1]Basic_load!$B$32*[1]Basic_load!G15)*0.85</f>
+        <v>8.4341249999999989E-3</v>
       </c>
       <c r="AG14" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G15)*0.1</f>
-        <v>1.38915E-3</v>
+        <f>([1]Basic_load!$B$33*[1]Basic_load!G15)*0.85</f>
+        <v>1.1807775E-2</v>
       </c>
       <c r="AH14" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G15)*0.1</f>
-        <v>3.9690000000000005E-4</v>
+        <f>([1]Basic_load!$B$34*[1]Basic_load!G15)*0.85</f>
+        <v>3.3736500000000002E-3</v>
       </c>
     </row>
     <row r="15" spans="1:34" x14ac:dyDescent="0.3">
@@ -2583,135 +3304,134 @@
         <v>0.54166666666666696</v>
       </c>
       <c r="B15" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G16)*0.1</f>
+        <f>([1]Basic_load!$B$2*[1]Basic_load!G16)*0.85</f>
         <v>0</v>
       </c>
       <c r="C15" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G16)*0.1</f>
-        <v>5.6000000000000006E-4</v>
+        <f>([1]Basic_load!$B$3*[1]Basic_load!G16)*0.85</f>
+        <v>4.7600000000000003E-3</v>
       </c>
       <c r="D15" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G16)*0.1</f>
-        <v>5.04E-4</v>
+        <f>([1]Basic_load!$B$4*[1]Basic_load!G16)*0.85</f>
+        <v>4.2840000000000005E-3</v>
       </c>
       <c r="E15" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G16)*0.1</f>
-        <v>5.6000000000000006E-4</v>
+        <f>([1]Basic_load!$B$5*[1]Basic_load!G16)*0.85</f>
+        <v>4.7600000000000003E-3</v>
       </c>
       <c r="F15" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G16)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$6*[1]Basic_load!G16)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="G15" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G16)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$7*[1]Basic_load!G16)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="H15" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G16)*0.1</f>
-        <v>1.1200000000000001E-3</v>
+        <f>([1]Basic_load!$B$8*[1]Basic_load!G16)*0.85</f>
+        <v>9.5200000000000007E-3</v>
       </c>
       <c r="I15" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G16)*0.1</f>
-        <v>1.1200000000000001E-3</v>
+        <f>([1]Basic_load!$B$9*[1]Basic_load!G16)*0.85</f>
+        <v>9.5200000000000007E-3</v>
       </c>
       <c r="J15" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G16)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$10*[1]Basic_load!G16)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="K15" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G16)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$11*[1]Basic_load!G16)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="L15" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G16)*0.1</f>
-        <v>2.52E-4</v>
+        <f>([1]Basic_load!$B$12*[1]Basic_load!G16)*0.85</f>
+        <v>2.1420000000000002E-3</v>
       </c>
       <c r="M15" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G16)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$13*[1]Basic_load!G16)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="N15" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G16)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$14*[1]Basic_load!G16)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="O15" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G16)*0.1</f>
-        <v>6.7200000000000007E-4</v>
+        <f>([1]Basic_load!$B$15*[1]Basic_load!G16)*0.85</f>
+        <v>5.7120000000000001E-3</v>
       </c>
       <c r="P15" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G16)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$16*[1]Basic_load!G16)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="Q15" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G16)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$17*[1]Basic_load!G16)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="R15" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G16)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$18*[1]Basic_load!G16)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="S15" s="8">
-        <v>2.5</v>
+        <v>0.40879999999999994</v>
       </c>
       <c r="T15" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G16)*0.1</f>
-        <v>5.04E-4</v>
+        <f>([1]Basic_load!$B$20*[1]Basic_load!G16)*0.85</f>
+        <v>4.2840000000000005E-3</v>
       </c>
       <c r="U15" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G16)*0.1</f>
-        <v>5.04E-4</v>
+        <f>([1]Basic_load!$B$21*[1]Basic_load!G16)*0.85</f>
+        <v>4.2840000000000005E-3</v>
       </c>
       <c r="V15" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G16)*0.1</f>
-        <v>5.04E-4</v>
+        <f>([1]Basic_load!$B$22*[1]Basic_load!G16)*0.85</f>
+        <v>4.2840000000000005E-3</v>
       </c>
       <c r="W15" s="7">
-        <f>([1]Basic_load!$B$23*[1]Basic_load!G16)*0.1</f>
-        <v>5.04E-4</v>
+        <v>0.36464999999999997</v>
       </c>
       <c r="X15" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G16)*0.1</f>
-        <v>5.04E-4</v>
+        <f>([1]Basic_load!$B$24*[1]Basic_load!G16)*0.85</f>
+        <v>4.2840000000000005E-3</v>
       </c>
       <c r="Y15" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G16)*0.1</f>
-        <v>2.3519999999999999E-3</v>
+        <f>([1]Basic_load!$B$25*[1]Basic_load!G16)*0.85</f>
+        <v>1.9991999999999999E-2</v>
       </c>
       <c r="Z15" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G16)*0.1</f>
-        <v>2.3519999999999999E-3</v>
+        <f>([1]Basic_load!$B$26*[1]Basic_load!G16)*0.85</f>
+        <v>1.9991999999999999E-2</v>
       </c>
       <c r="AA15" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G16)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$27*[1]Basic_load!G16)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="AB15" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G16)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$28*[1]Basic_load!G16)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="AC15" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G16)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$29*[1]Basic_load!G16)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="AD15" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G16)*0.1</f>
-        <v>6.7200000000000007E-4</v>
+        <f>([1]Basic_load!$B$30*[1]Basic_load!G16)*0.85</f>
+        <v>5.7120000000000001E-3</v>
       </c>
       <c r="AE15" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G16)*0.1</f>
-        <v>1.1200000000000001E-3</v>
+        <f>([1]Basic_load!$B$31*[1]Basic_load!G16)*0.85</f>
+        <v>9.5200000000000007E-3</v>
       </c>
       <c r="AF15" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G16)*0.1</f>
-        <v>8.4000000000000003E-4</v>
+        <f>([1]Basic_load!$B$32*[1]Basic_load!G16)*0.85</f>
+        <v>7.1399999999999996E-3</v>
       </c>
       <c r="AG15" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G16)*0.1</f>
-        <v>1.176E-3</v>
+        <f>([1]Basic_load!$B$33*[1]Basic_load!G16)*0.85</f>
+        <v>9.9959999999999997E-3</v>
       </c>
       <c r="AH15" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G16)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$34*[1]Basic_load!G16)*0.85</f>
+        <v>2.856E-3</v>
       </c>
     </row>
     <row r="16" spans="1:34" x14ac:dyDescent="0.3">
@@ -2719,135 +3439,134 @@
         <v>0.58333333333333404</v>
       </c>
       <c r="B16" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G17)*0.1</f>
+        <f>([1]Basic_load!$B$2*[1]Basic_load!G17)*0.85</f>
         <v>0</v>
       </c>
       <c r="C16" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G17)*0.1</f>
-        <v>5.6000000000000006E-4</v>
+        <f>([1]Basic_load!$B$3*[1]Basic_load!G17)*0.85</f>
+        <v>4.7600000000000003E-3</v>
       </c>
       <c r="D16" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G17)*0.1</f>
-        <v>5.04E-4</v>
+        <f>([1]Basic_load!$B$4*[1]Basic_load!G17)*0.85</f>
+        <v>4.2840000000000005E-3</v>
       </c>
       <c r="E16" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G17)*0.1</f>
-        <v>5.6000000000000006E-4</v>
+        <f>([1]Basic_load!$B$5*[1]Basic_load!G17)*0.85</f>
+        <v>4.7600000000000003E-3</v>
       </c>
       <c r="F16" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G17)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$6*[1]Basic_load!G17)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="G16" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G17)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$7*[1]Basic_load!G17)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="H16" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G17)*0.1</f>
-        <v>1.1200000000000001E-3</v>
+        <f>([1]Basic_load!$B$8*[1]Basic_load!G17)*0.85</f>
+        <v>9.5200000000000007E-3</v>
       </c>
       <c r="I16" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G17)*0.1</f>
-        <v>1.1200000000000001E-3</v>
+        <f>([1]Basic_load!$B$9*[1]Basic_load!G17)*0.85</f>
+        <v>9.5200000000000007E-3</v>
       </c>
       <c r="J16" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G17)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$10*[1]Basic_load!G17)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="K16" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G17)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$11*[1]Basic_load!G17)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="L16" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G17)*0.1</f>
-        <v>2.52E-4</v>
+        <f>([1]Basic_load!$B$12*[1]Basic_load!G17)*0.85</f>
+        <v>2.1420000000000002E-3</v>
       </c>
       <c r="M16" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G17)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$13*[1]Basic_load!G17)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="N16" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G17)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$14*[1]Basic_load!G17)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="O16" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G17)*0.1</f>
-        <v>6.7200000000000007E-4</v>
+        <f>([1]Basic_load!$B$15*[1]Basic_load!G17)*0.85</f>
+        <v>5.7120000000000001E-3</v>
       </c>
       <c r="P16" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G17)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$16*[1]Basic_load!G17)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="Q16" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G17)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$17*[1]Basic_load!G17)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="R16" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G17)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$18*[1]Basic_load!G17)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="S16" s="8">
-        <v>1.7500000000000002</v>
+        <v>0.40879999999999994</v>
       </c>
       <c r="T16" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G17)*0.1</f>
-        <v>5.04E-4</v>
+        <f>([1]Basic_load!$B$20*[1]Basic_load!G17)*0.85</f>
+        <v>4.2840000000000005E-3</v>
       </c>
       <c r="U16" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G17)*0.1</f>
-        <v>5.04E-4</v>
+        <f>([1]Basic_load!$B$21*[1]Basic_load!G17)*0.85</f>
+        <v>4.2840000000000005E-3</v>
       </c>
       <c r="V16" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G17)*0.1</f>
-        <v>5.04E-4</v>
+        <f>([1]Basic_load!$B$22*[1]Basic_load!G17)*0.85</f>
+        <v>4.2840000000000005E-3</v>
       </c>
       <c r="W16" s="7">
-        <f>([1]Basic_load!$B$23*[1]Basic_load!G17)*0.1</f>
-        <v>5.04E-4</v>
+        <v>0.30769999999999997</v>
       </c>
       <c r="X16" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G17)*0.1</f>
-        <v>5.04E-4</v>
+        <f>([1]Basic_load!$B$24*[1]Basic_load!G17)*0.85</f>
+        <v>4.2840000000000005E-3</v>
       </c>
       <c r="Y16" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G17)*0.1</f>
-        <v>2.3519999999999999E-3</v>
+        <f>([1]Basic_load!$B$25*[1]Basic_load!G17)*0.85</f>
+        <v>1.9991999999999999E-2</v>
       </c>
       <c r="Z16" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G17)*0.1</f>
-        <v>2.3519999999999999E-3</v>
+        <f>([1]Basic_load!$B$26*[1]Basic_load!G17)*0.85</f>
+        <v>1.9991999999999999E-2</v>
       </c>
       <c r="AA16" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G17)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$27*[1]Basic_load!G17)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="AB16" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G17)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$28*[1]Basic_load!G17)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="AC16" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G17)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$29*[1]Basic_load!G17)*0.85</f>
+        <v>2.856E-3</v>
       </c>
       <c r="AD16" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G17)*0.1</f>
-        <v>6.7200000000000007E-4</v>
+        <f>([1]Basic_load!$B$30*[1]Basic_load!G17)*0.85</f>
+        <v>5.7120000000000001E-3</v>
       </c>
       <c r="AE16" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G17)*0.1</f>
-        <v>1.1200000000000001E-3</v>
+        <f>([1]Basic_load!$B$31*[1]Basic_load!G17)*0.85</f>
+        <v>9.5200000000000007E-3</v>
       </c>
       <c r="AF16" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G17)*0.1</f>
-        <v>8.4000000000000003E-4</v>
+        <f>([1]Basic_load!$B$32*[1]Basic_load!G17)*0.85</f>
+        <v>7.1399999999999996E-3</v>
       </c>
       <c r="AG16" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G17)*0.1</f>
-        <v>1.176E-3</v>
+        <f>([1]Basic_load!$B$33*[1]Basic_load!G17)*0.85</f>
+        <v>9.9959999999999997E-3</v>
       </c>
       <c r="AH16" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G17)*0.1</f>
-        <v>3.3600000000000004E-4</v>
+        <f>([1]Basic_load!$B$34*[1]Basic_load!G17)*0.85</f>
+        <v>2.856E-3</v>
       </c>
     </row>
     <row r="17" spans="1:34" x14ac:dyDescent="0.3">
@@ -2855,135 +3574,134 @@
         <v>0.625</v>
       </c>
       <c r="B17" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G18)*0.1</f>
+        <f>([1]Basic_load!$B$2*[1]Basic_load!G18)*0.85</f>
         <v>0</v>
       </c>
       <c r="C17" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G18)*0.1</f>
-        <v>6.5183000000000016E-4</v>
+        <f>([1]Basic_load!$B$3*[1]Basic_load!G18)*0.85</f>
+        <v>5.5405550000000008E-3</v>
       </c>
       <c r="D17" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G18)*0.1</f>
-        <v>5.8664700000000004E-4</v>
+        <f>([1]Basic_load!$B$4*[1]Basic_load!G18)*0.85</f>
+        <v>4.9864994999999999E-3</v>
       </c>
       <c r="E17" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G18)*0.1</f>
-        <v>6.5183000000000016E-4</v>
+        <f>([1]Basic_load!$B$5*[1]Basic_load!G18)*0.85</f>
+        <v>5.5405550000000008E-3</v>
       </c>
       <c r="F17" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G18)*0.1</f>
-        <v>3.910980000000001E-4</v>
+        <f>([1]Basic_load!$B$6*[1]Basic_load!G18)*0.85</f>
+        <v>3.3243330000000005E-3</v>
       </c>
       <c r="G17" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G18)*0.1</f>
-        <v>3.910980000000001E-4</v>
+        <f>([1]Basic_load!$B$7*[1]Basic_load!G18)*0.85</f>
+        <v>3.3243330000000005E-3</v>
       </c>
       <c r="H17" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G18)*0.1</f>
-        <v>1.3036600000000003E-3</v>
+        <f>([1]Basic_load!$B$8*[1]Basic_load!G18)*0.85</f>
+        <v>1.1081110000000002E-2</v>
       </c>
       <c r="I17" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G18)*0.1</f>
-        <v>1.3036600000000003E-3</v>
+        <f>([1]Basic_load!$B$9*[1]Basic_load!G18)*0.85</f>
+        <v>1.1081110000000002E-2</v>
       </c>
       <c r="J17" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G18)*0.1</f>
-        <v>3.910980000000001E-4</v>
+        <f>([1]Basic_load!$B$10*[1]Basic_load!G18)*0.85</f>
+        <v>3.3243330000000005E-3</v>
       </c>
       <c r="K17" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G18)*0.1</f>
-        <v>3.910980000000001E-4</v>
+        <f>([1]Basic_load!$B$11*[1]Basic_load!G18)*0.85</f>
+        <v>3.3243330000000005E-3</v>
       </c>
       <c r="L17" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G18)*0.1</f>
-        <v>2.9332350000000002E-4</v>
+        <f>([1]Basic_load!$B$12*[1]Basic_load!G18)*0.85</f>
+        <v>2.4932497499999999E-3</v>
       </c>
       <c r="M17" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G18)*0.1</f>
-        <v>3.910980000000001E-4</v>
+        <f>([1]Basic_load!$B$13*[1]Basic_load!G18)*0.85</f>
+        <v>3.3243330000000005E-3</v>
       </c>
       <c r="N17" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G18)*0.1</f>
-        <v>3.910980000000001E-4</v>
+        <f>([1]Basic_load!$B$14*[1]Basic_load!G18)*0.85</f>
+        <v>3.3243330000000005E-3</v>
       </c>
       <c r="O17" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G18)*0.1</f>
-        <v>7.8219600000000019E-4</v>
+        <f>([1]Basic_load!$B$15*[1]Basic_load!G18)*0.85</f>
+        <v>6.648666000000001E-3</v>
       </c>
       <c r="P17" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G18)*0.1</f>
-        <v>3.910980000000001E-4</v>
+        <f>([1]Basic_load!$B$16*[1]Basic_load!G18)*0.85</f>
+        <v>3.3243330000000005E-3</v>
       </c>
       <c r="Q17" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G18)*0.1</f>
-        <v>3.910980000000001E-4</v>
+        <f>([1]Basic_load!$B$17*[1]Basic_load!G18)*0.85</f>
+        <v>3.3243330000000005E-3</v>
       </c>
       <c r="R17" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G18)*0.1</f>
-        <v>3.910980000000001E-4</v>
+        <f>([1]Basic_load!$B$18*[1]Basic_load!G18)*0.85</f>
+        <v>3.3243330000000005E-3</v>
       </c>
       <c r="S17" s="8">
-        <v>0</v>
+        <v>0.40879999999999994</v>
       </c>
       <c r="T17" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G18)*0.1</f>
-        <v>5.8664700000000004E-4</v>
+        <f>([1]Basic_load!$B$20*[1]Basic_load!G18)*0.85</f>
+        <v>4.9864994999999999E-3</v>
       </c>
       <c r="U17" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G18)*0.1</f>
-        <v>5.8664700000000004E-4</v>
+        <f>([1]Basic_load!$B$21*[1]Basic_load!G18)*0.85</f>
+        <v>4.9864994999999999E-3</v>
       </c>
       <c r="V17" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G18)*0.1</f>
-        <v>5.8664700000000004E-4</v>
+        <f>([1]Basic_load!$B$22*[1]Basic_load!G18)*0.85</f>
+        <v>4.9864994999999999E-3</v>
       </c>
       <c r="W17" s="7">
-        <f>([1]Basic_load!$B$23*[1]Basic_load!G18)*0.1</f>
-        <v>5.8664700000000004E-4</v>
+        <v>0.22355</v>
       </c>
       <c r="X17" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G18)*0.1</f>
-        <v>5.8664700000000004E-4</v>
+        <f>([1]Basic_load!$B$24*[1]Basic_load!G18)*0.85</f>
+        <v>4.9864994999999999E-3</v>
       </c>
       <c r="Y17" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G18)*0.1</f>
-        <v>2.737686E-3</v>
+        <f>([1]Basic_load!$B$25*[1]Basic_load!G18)*0.85</f>
+        <v>2.3270330999999998E-2</v>
       </c>
       <c r="Z17" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G18)*0.1</f>
-        <v>2.737686E-3</v>
+        <f>([1]Basic_load!$B$26*[1]Basic_load!G18)*0.85</f>
+        <v>2.3270330999999998E-2</v>
       </c>
       <c r="AA17" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G18)*0.1</f>
-        <v>3.910980000000001E-4</v>
+        <f>([1]Basic_load!$B$27*[1]Basic_load!G18)*0.85</f>
+        <v>3.3243330000000005E-3</v>
       </c>
       <c r="AB17" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G18)*0.1</f>
-        <v>3.910980000000001E-4</v>
+        <f>([1]Basic_load!$B$28*[1]Basic_load!G18)*0.85</f>
+        <v>3.3243330000000005E-3</v>
       </c>
       <c r="AC17" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G18)*0.1</f>
-        <v>3.910980000000001E-4</v>
+        <f>([1]Basic_load!$B$29*[1]Basic_load!G18)*0.85</f>
+        <v>3.3243330000000005E-3</v>
       </c>
       <c r="AD17" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G18)*0.1</f>
-        <v>7.8219600000000019E-4</v>
+        <f>([1]Basic_load!$B$30*[1]Basic_load!G18)*0.85</f>
+        <v>6.648666000000001E-3</v>
       </c>
       <c r="AE17" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G18)*0.1</f>
-        <v>1.3036600000000003E-3</v>
+        <f>([1]Basic_load!$B$31*[1]Basic_load!G18)*0.85</f>
+        <v>1.1081110000000002E-2</v>
       </c>
       <c r="AF17" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G18)*0.1</f>
-        <v>9.7774500000000013E-4</v>
+        <f>([1]Basic_load!$B$32*[1]Basic_load!G18)*0.85</f>
+        <v>8.3108325000000004E-3</v>
       </c>
       <c r="AG17" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G18)*0.1</f>
-        <v>1.368843E-3</v>
+        <f>([1]Basic_load!$B$33*[1]Basic_load!G18)*0.85</f>
+        <v>1.1635165499999999E-2</v>
       </c>
       <c r="AH17" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G18)*0.1</f>
-        <v>3.910980000000001E-4</v>
+        <f>([1]Basic_load!$B$34*[1]Basic_load!G18)*0.85</f>
+        <v>3.3243330000000005E-3</v>
       </c>
     </row>
     <row r="18" spans="1:34" x14ac:dyDescent="0.3">
@@ -2991,135 +3709,134 @@
         <v>0.66666666666666696</v>
       </c>
       <c r="B18" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G19)*0.1</f>
+        <f>([1]Basic_load!$B$2*[1]Basic_load!G19)*0.85</f>
         <v>0</v>
       </c>
       <c r="C18" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G19)*0.1</f>
-        <v>4.2235000000000007E-3</v>
+        <f>([1]Basic_load!$B$3*[1]Basic_load!G19)*0.85</f>
+        <v>3.5899750000000001E-2</v>
       </c>
       <c r="D18" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G19)*0.1</f>
-        <v>3.8011499999999997E-3</v>
+        <f>([1]Basic_load!$B$4*[1]Basic_load!G19)*0.85</f>
+        <v>3.2309774999999999E-2</v>
       </c>
       <c r="E18" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G19)*0.1</f>
-        <v>4.2235000000000007E-3</v>
+        <f>([1]Basic_load!$B$5*[1]Basic_load!G19)*0.85</f>
+        <v>3.5899750000000001E-2</v>
       </c>
       <c r="F18" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G19)*0.1</f>
-        <v>2.5341000000000001E-3</v>
+        <f>([1]Basic_load!$B$6*[1]Basic_load!G19)*0.85</f>
+        <v>2.1539849999999999E-2</v>
       </c>
       <c r="G18" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G19)*0.1</f>
-        <v>2.5341000000000001E-3</v>
+        <f>([1]Basic_load!$B$7*[1]Basic_load!G19)*0.85</f>
+        <v>2.1539849999999999E-2</v>
       </c>
       <c r="H18" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G19)*0.1</f>
-        <v>8.4470000000000014E-3</v>
+        <f>([1]Basic_load!$B$8*[1]Basic_load!G19)*0.85</f>
+        <v>7.1799500000000002E-2</v>
       </c>
       <c r="I18" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G19)*0.1</f>
-        <v>8.4470000000000014E-3</v>
+        <f>([1]Basic_load!$B$9*[1]Basic_load!G19)*0.85</f>
+        <v>7.1799500000000002E-2</v>
       </c>
       <c r="J18" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G19)*0.1</f>
-        <v>2.5341000000000001E-3</v>
+        <f>([1]Basic_load!$B$10*[1]Basic_load!G19)*0.85</f>
+        <v>2.1539849999999999E-2</v>
       </c>
       <c r="K18" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G19)*0.1</f>
-        <v>2.5341000000000001E-3</v>
+        <f>([1]Basic_load!$B$11*[1]Basic_load!G19)*0.85</f>
+        <v>2.1539849999999999E-2</v>
       </c>
       <c r="L18" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G19)*0.1</f>
-        <v>1.9005749999999998E-3</v>
+        <f>([1]Basic_load!$B$12*[1]Basic_load!G19)*0.85</f>
+        <v>1.6154887499999999E-2</v>
       </c>
       <c r="M18" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G19)*0.1</f>
-        <v>2.5341000000000001E-3</v>
+        <f>([1]Basic_load!$B$13*[1]Basic_load!G19)*0.85</f>
+        <v>2.1539849999999999E-2</v>
       </c>
       <c r="N18" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G19)*0.1</f>
-        <v>2.5341000000000001E-3</v>
+        <f>([1]Basic_load!$B$14*[1]Basic_load!G19)*0.85</f>
+        <v>2.1539849999999999E-2</v>
       </c>
       <c r="O18" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G19)*0.1</f>
-        <v>5.0682000000000001E-3</v>
+        <f>([1]Basic_load!$B$15*[1]Basic_load!G19)*0.85</f>
+        <v>4.3079699999999999E-2</v>
       </c>
       <c r="P18" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G19)*0.1</f>
-        <v>2.5341000000000001E-3</v>
+        <f>([1]Basic_load!$B$16*[1]Basic_load!G19)*0.85</f>
+        <v>2.1539849999999999E-2</v>
       </c>
       <c r="Q18" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G19)*0.1</f>
-        <v>2.5341000000000001E-3</v>
+        <f>([1]Basic_load!$B$17*[1]Basic_load!G19)*0.85</f>
+        <v>2.1539849999999999E-2</v>
       </c>
       <c r="R18" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G19)*0.1</f>
-        <v>2.5341000000000001E-3</v>
+        <f>([1]Basic_load!$B$18*[1]Basic_load!G19)*0.85</f>
+        <v>2.1539849999999999E-2</v>
       </c>
       <c r="S18" s="8">
-        <v>0</v>
+        <v>0.33319999999999994</v>
       </c>
       <c r="T18" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G19)*0.1</f>
-        <v>3.8011499999999997E-3</v>
+        <f>([1]Basic_load!$B$20*[1]Basic_load!G19)*0.85</f>
+        <v>3.2309774999999999E-2</v>
       </c>
       <c r="U18" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G19)*0.1</f>
-        <v>3.8011499999999997E-3</v>
+        <f>([1]Basic_load!$B$21*[1]Basic_load!G19)*0.85</f>
+        <v>3.2309774999999999E-2</v>
       </c>
       <c r="V18" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G19)*0.1</f>
-        <v>3.8011499999999997E-3</v>
+        <f>([1]Basic_load!$B$22*[1]Basic_load!G19)*0.85</f>
+        <v>3.2309774999999999E-2</v>
       </c>
       <c r="W18" s="7">
-        <f>([1]Basic_load!$B$23*[1]Basic_load!G19)*0.1</f>
-        <v>3.8011499999999997E-3</v>
+        <v>0.12834999999999999</v>
       </c>
       <c r="X18" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G19)*0.1</f>
-        <v>3.8011499999999997E-3</v>
+        <f>([1]Basic_load!$B$24*[1]Basic_load!G19)*0.85</f>
+        <v>3.2309774999999999E-2</v>
       </c>
       <c r="Y18" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G19)*0.1</f>
-        <v>1.77387E-2</v>
+        <f>([1]Basic_load!$B$25*[1]Basic_load!G19)*0.85</f>
+        <v>0.15077894999999999</v>
       </c>
       <c r="Z18" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G19)*0.1</f>
-        <v>1.77387E-2</v>
+        <f>([1]Basic_load!$B$26*[1]Basic_load!G19)*0.85</f>
+        <v>0.15077894999999999</v>
       </c>
       <c r="AA18" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G19)*0.1</f>
-        <v>2.5341000000000001E-3</v>
+        <f>([1]Basic_load!$B$27*[1]Basic_load!G19)*0.85</f>
+        <v>2.1539849999999999E-2</v>
       </c>
       <c r="AB18" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G19)*0.1</f>
-        <v>2.5341000000000001E-3</v>
+        <f>([1]Basic_load!$B$28*[1]Basic_load!G19)*0.85</f>
+        <v>2.1539849999999999E-2</v>
       </c>
       <c r="AC18" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G19)*0.1</f>
-        <v>2.5341000000000001E-3</v>
+        <f>([1]Basic_load!$B$29*[1]Basic_load!G19)*0.85</f>
+        <v>2.1539849999999999E-2</v>
       </c>
       <c r="AD18" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G19)*0.1</f>
-        <v>5.0682000000000001E-3</v>
+        <f>([1]Basic_load!$B$30*[1]Basic_load!G19)*0.85</f>
+        <v>4.3079699999999999E-2</v>
       </c>
       <c r="AE18" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G19)*0.1</f>
-        <v>8.4470000000000014E-3</v>
+        <f>([1]Basic_load!$B$31*[1]Basic_load!G19)*0.85</f>
+        <v>7.1799500000000002E-2</v>
       </c>
       <c r="AF18" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G19)*0.1</f>
-        <v>6.3352499999999997E-3</v>
+        <f>([1]Basic_load!$B$32*[1]Basic_load!G19)*0.85</f>
+        <v>5.3849624999999991E-2</v>
       </c>
       <c r="AG18" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G19)*0.1</f>
-        <v>8.8693499999999998E-3</v>
+        <f>([1]Basic_load!$B$33*[1]Basic_load!G19)*0.85</f>
+        <v>7.5389474999999997E-2</v>
       </c>
       <c r="AH18" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G19)*0.1</f>
-        <v>2.5341000000000001E-3</v>
+        <f>([1]Basic_load!$B$34*[1]Basic_load!G19)*0.85</f>
+        <v>2.1539849999999999E-2</v>
       </c>
     </row>
     <row r="19" spans="1:34" x14ac:dyDescent="0.3">
@@ -3127,135 +3844,134 @@
         <v>0.70833333333333404</v>
       </c>
       <c r="B19" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G20)*0.1</f>
+        <f>([1]Basic_load!$B$2*[1]Basic_load!G20)*0.85</f>
         <v>0</v>
       </c>
       <c r="C19" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G20)*0.1</f>
-        <v>8.7378300000000002E-3</v>
+        <f>([1]Basic_load!$B$3*[1]Basic_load!G20)*0.85</f>
+        <v>7.4271555000000003E-2</v>
       </c>
       <c r="D19" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G20)*0.1</f>
-        <v>7.864046999999999E-3</v>
+        <f>([1]Basic_load!$B$4*[1]Basic_load!G20)*0.85</f>
+        <v>6.6844399499999985E-2</v>
       </c>
       <c r="E19" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G20)*0.1</f>
-        <v>8.7378300000000002E-3</v>
+        <f>([1]Basic_load!$B$5*[1]Basic_load!G20)*0.85</f>
+        <v>7.4271555000000003E-2</v>
       </c>
       <c r="F19" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G20)*0.1</f>
-        <v>5.2426980000000005E-3</v>
+        <f>([1]Basic_load!$B$6*[1]Basic_load!G20)*0.85</f>
+        <v>4.4562932999999999E-2</v>
       </c>
       <c r="G19" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G20)*0.1</f>
-        <v>5.2426980000000005E-3</v>
+        <f>([1]Basic_load!$B$7*[1]Basic_load!G20)*0.85</f>
+        <v>4.4562932999999999E-2</v>
       </c>
       <c r="H19" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G20)*0.1</f>
-        <v>1.747566E-2</v>
+        <f>([1]Basic_load!$B$8*[1]Basic_load!G20)*0.85</f>
+        <v>0.14854311000000001</v>
       </c>
       <c r="I19" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G20)*0.1</f>
-        <v>1.747566E-2</v>
+        <f>([1]Basic_load!$B$9*[1]Basic_load!G20)*0.85</f>
+        <v>0.14854311000000001</v>
       </c>
       <c r="J19" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G20)*0.1</f>
-        <v>5.2426980000000005E-3</v>
+        <f>([1]Basic_load!$B$10*[1]Basic_load!G20)*0.85</f>
+        <v>4.4562932999999999E-2</v>
       </c>
       <c r="K19" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G20)*0.1</f>
-        <v>5.2426980000000005E-3</v>
+        <f>([1]Basic_load!$B$11*[1]Basic_load!G20)*0.85</f>
+        <v>4.4562932999999999E-2</v>
       </c>
       <c r="L19" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G20)*0.1</f>
-        <v>3.9320234999999995E-3</v>
+        <f>([1]Basic_load!$B$12*[1]Basic_load!G20)*0.85</f>
+        <v>3.3422199749999992E-2</v>
       </c>
       <c r="M19" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G20)*0.1</f>
-        <v>5.2426980000000005E-3</v>
+        <f>([1]Basic_load!$B$13*[1]Basic_load!G20)*0.85</f>
+        <v>4.4562932999999999E-2</v>
       </c>
       <c r="N19" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G20)*0.1</f>
-        <v>5.2426980000000005E-3</v>
+        <f>([1]Basic_load!$B$14*[1]Basic_load!G20)*0.85</f>
+        <v>4.4562932999999999E-2</v>
       </c>
       <c r="O19" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G20)*0.1</f>
-        <v>1.0485396000000001E-2</v>
+        <f>([1]Basic_load!$B$15*[1]Basic_load!G20)*0.85</f>
+        <v>8.9125865999999998E-2</v>
       </c>
       <c r="P19" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G20)*0.1</f>
-        <v>5.2426980000000005E-3</v>
+        <f>([1]Basic_load!$B$16*[1]Basic_load!G20)*0.85</f>
+        <v>4.4562932999999999E-2</v>
       </c>
       <c r="Q19" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G20)*0.1</f>
-        <v>5.2426980000000005E-3</v>
+        <f>([1]Basic_load!$B$17*[1]Basic_load!G20)*0.85</f>
+        <v>4.4562932999999999E-2</v>
       </c>
       <c r="R19" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G20)*0.1</f>
-        <v>5.2426980000000005E-3</v>
+        <f>([1]Basic_load!$B$18*[1]Basic_load!G20)*0.85</f>
+        <v>4.4562932999999999E-2</v>
       </c>
       <c r="S19" s="8">
-        <v>0</v>
+        <v>0.33319999999999994</v>
       </c>
       <c r="T19" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G20)*0.1</f>
-        <v>7.864046999999999E-3</v>
+        <f>([1]Basic_load!$B$20*[1]Basic_load!G20)*0.85</f>
+        <v>6.6844399499999985E-2</v>
       </c>
       <c r="U19" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G20)*0.1</f>
-        <v>7.864046999999999E-3</v>
+        <f>([1]Basic_load!$B$21*[1]Basic_load!G20)*0.85</f>
+        <v>6.6844399499999985E-2</v>
       </c>
       <c r="V19" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G20)*0.1</f>
-        <v>7.864046999999999E-3</v>
+        <f>([1]Basic_load!$B$22*[1]Basic_load!G20)*0.85</f>
+        <v>6.6844399499999985E-2</v>
       </c>
       <c r="W19" s="7">
-        <f>([1]Basic_load!$B$23*[1]Basic_load!G20)*0.1</f>
-        <v>7.864046999999999E-3</v>
+        <v>5.525E-2</v>
       </c>
       <c r="X19" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G20)*0.1</f>
-        <v>7.864046999999999E-3</v>
+        <f>([1]Basic_load!$B$24*[1]Basic_load!G20)*0.85</f>
+        <v>6.6844399499999985E-2</v>
       </c>
       <c r="Y19" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G20)*0.1</f>
-        <v>3.6698886E-2</v>
+        <f>([1]Basic_load!$B$25*[1]Basic_load!G20)*0.85</f>
+        <v>0.31194053099999997</v>
       </c>
       <c r="Z19" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G20)*0.1</f>
-        <v>3.6698886E-2</v>
+        <f>([1]Basic_load!$B$26*[1]Basic_load!G20)*0.85</f>
+        <v>0.31194053099999997</v>
       </c>
       <c r="AA19" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G20)*0.1</f>
-        <v>5.2426980000000005E-3</v>
+        <f>([1]Basic_load!$B$27*[1]Basic_load!G20)*0.85</f>
+        <v>4.4562932999999999E-2</v>
       </c>
       <c r="AB19" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G20)*0.1</f>
-        <v>5.2426980000000005E-3</v>
+        <f>([1]Basic_load!$B$28*[1]Basic_load!G20)*0.85</f>
+        <v>4.4562932999999999E-2</v>
       </c>
       <c r="AC19" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G20)*0.1</f>
-        <v>5.2426980000000005E-3</v>
+        <f>([1]Basic_load!$B$29*[1]Basic_load!G20)*0.85</f>
+        <v>4.4562932999999999E-2</v>
       </c>
       <c r="AD19" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G20)*0.1</f>
-        <v>1.0485396000000001E-2</v>
+        <f>([1]Basic_load!$B$30*[1]Basic_load!G20)*0.85</f>
+        <v>8.9125865999999998E-2</v>
       </c>
       <c r="AE19" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G20)*0.1</f>
-        <v>1.747566E-2</v>
+        <f>([1]Basic_load!$B$31*[1]Basic_load!G20)*0.85</f>
+        <v>0.14854311000000001</v>
       </c>
       <c r="AF19" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G20)*0.1</f>
-        <v>1.3106745000000001E-2</v>
+        <f>([1]Basic_load!$B$32*[1]Basic_load!G20)*0.85</f>
+        <v>0.1114073325</v>
       </c>
       <c r="AG19" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G20)*0.1</f>
-        <v>1.8349443E-2</v>
+        <f>([1]Basic_load!$B$33*[1]Basic_load!G20)*0.85</f>
+        <v>0.15597026549999998</v>
       </c>
       <c r="AH19" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G20)*0.1</f>
-        <v>5.2426980000000005E-3</v>
+        <f>([1]Basic_load!$B$34*[1]Basic_load!G20)*0.85</f>
+        <v>4.4562932999999999E-2</v>
       </c>
     </row>
     <row r="20" spans="1:34" x14ac:dyDescent="0.3">
@@ -3263,135 +3979,134 @@
         <v>0.750000000000001</v>
       </c>
       <c r="B20" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G21)*0.1</f>
+        <f>([1]Basic_load!$B$2*[1]Basic_load!G21)*0.85</f>
         <v>0</v>
       </c>
       <c r="C20" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G21)*0.1</f>
-        <v>7.0701700000000006E-3</v>
+        <f>([1]Basic_load!$B$3*[1]Basic_load!G21)*0.85</f>
+        <v>6.0096445000000005E-2</v>
       </c>
       <c r="D20" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G21)*0.1</f>
-        <v>6.3631529999999999E-3</v>
+        <f>([1]Basic_load!$B$4*[1]Basic_load!G21)*0.85</f>
+        <v>5.408680049999999E-2</v>
       </c>
       <c r="E20" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G21)*0.1</f>
-        <v>7.0701700000000006E-3</v>
+        <f>([1]Basic_load!$B$5*[1]Basic_load!G21)*0.85</f>
+        <v>6.0096445000000005E-2</v>
       </c>
       <c r="F20" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G21)*0.1</f>
-        <v>4.2421020000000002E-3</v>
+        <f>([1]Basic_load!$B$6*[1]Basic_load!G21)*0.85</f>
+        <v>3.6057866999999993E-2</v>
       </c>
       <c r="G20" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G21)*0.1</f>
-        <v>4.2421020000000002E-3</v>
+        <f>([1]Basic_load!$B$7*[1]Basic_load!G21)*0.85</f>
+        <v>3.6057866999999993E-2</v>
       </c>
       <c r="H20" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G21)*0.1</f>
-        <v>1.4140340000000001E-2</v>
+        <f>([1]Basic_load!$B$8*[1]Basic_load!G21)*0.85</f>
+        <v>0.12019289000000001</v>
       </c>
       <c r="I20" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G21)*0.1</f>
-        <v>1.4140340000000001E-2</v>
+        <f>([1]Basic_load!$B$9*[1]Basic_load!G21)*0.85</f>
+        <v>0.12019289000000001</v>
       </c>
       <c r="J20" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G21)*0.1</f>
-        <v>4.2421020000000002E-3</v>
+        <f>([1]Basic_load!$B$10*[1]Basic_load!G21)*0.85</f>
+        <v>3.6057866999999993E-2</v>
       </c>
       <c r="K20" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G21)*0.1</f>
-        <v>4.2421020000000002E-3</v>
+        <f>([1]Basic_load!$B$11*[1]Basic_load!G21)*0.85</f>
+        <v>3.6057866999999993E-2</v>
       </c>
       <c r="L20" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G21)*0.1</f>
-        <v>3.1815764999999999E-3</v>
+        <f>([1]Basic_load!$B$12*[1]Basic_load!G21)*0.85</f>
+        <v>2.7043400249999995E-2</v>
       </c>
       <c r="M20" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G21)*0.1</f>
-        <v>4.2421020000000002E-3</v>
+        <f>([1]Basic_load!$B$13*[1]Basic_load!G21)*0.85</f>
+        <v>3.6057866999999993E-2</v>
       </c>
       <c r="N20" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G21)*0.1</f>
-        <v>4.2421020000000002E-3</v>
+        <f>([1]Basic_load!$B$14*[1]Basic_load!G21)*0.85</f>
+        <v>3.6057866999999993E-2</v>
       </c>
       <c r="O20" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G21)*0.1</f>
-        <v>8.4842040000000004E-3</v>
+        <f>([1]Basic_load!$B$15*[1]Basic_load!G21)*0.85</f>
+        <v>7.2115733999999987E-2</v>
       </c>
       <c r="P20" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G21)*0.1</f>
-        <v>4.2421020000000002E-3</v>
+        <f>([1]Basic_load!$B$16*[1]Basic_load!G21)*0.85</f>
+        <v>3.6057866999999993E-2</v>
       </c>
       <c r="Q20" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G21)*0.1</f>
-        <v>4.2421020000000002E-3</v>
+        <f>([1]Basic_load!$B$17*[1]Basic_load!G21)*0.85</f>
+        <v>3.6057866999999993E-2</v>
       </c>
       <c r="R20" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G21)*0.1</f>
-        <v>4.2421020000000002E-3</v>
+        <f>([1]Basic_load!$B$18*[1]Basic_load!G21)*0.85</f>
+        <v>3.6057866999999993E-2</v>
       </c>
       <c r="S20" s="8">
-        <v>0</v>
+        <v>0.33319999999999994</v>
       </c>
       <c r="T20" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G21)*0.1</f>
-        <v>6.3631529999999999E-3</v>
+        <f>([1]Basic_load!$B$20*[1]Basic_load!G21)*0.85</f>
+        <v>5.408680049999999E-2</v>
       </c>
       <c r="U20" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G21)*0.1</f>
-        <v>6.3631529999999999E-3</v>
+        <f>([1]Basic_load!$B$21*[1]Basic_load!G21)*0.85</f>
+        <v>5.408680049999999E-2</v>
       </c>
       <c r="V20" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G21)*0.1</f>
-        <v>6.3631529999999999E-3</v>
+        <f>([1]Basic_load!$B$22*[1]Basic_load!G21)*0.85</f>
+        <v>5.408680049999999E-2</v>
       </c>
       <c r="W20" s="7">
-        <f>([1]Basic_load!$B$23*[1]Basic_load!G21)*0.1</f>
-        <v>6.3631529999999999E-3</v>
+        <v>8.5000000000000006E-3</v>
       </c>
       <c r="X20" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G21)*0.1</f>
-        <v>6.3631529999999999E-3</v>
+        <f>([1]Basic_load!$B$24*[1]Basic_load!G21)*0.85</f>
+        <v>5.408680049999999E-2</v>
       </c>
       <c r="Y20" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G21)*0.1</f>
-        <v>2.9694714000000001E-2</v>
+        <f>([1]Basic_load!$B$25*[1]Basic_load!G21)*0.85</f>
+        <v>0.25240506899999998</v>
       </c>
       <c r="Z20" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G21)*0.1</f>
-        <v>2.9694714000000001E-2</v>
+        <f>([1]Basic_load!$B$26*[1]Basic_load!G21)*0.85</f>
+        <v>0.25240506899999998</v>
       </c>
       <c r="AA20" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G21)*0.1</f>
-        <v>4.2421020000000002E-3</v>
+        <f>([1]Basic_load!$B$27*[1]Basic_load!G21)*0.85</f>
+        <v>3.6057866999999993E-2</v>
       </c>
       <c r="AB20" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G21)*0.1</f>
-        <v>4.2421020000000002E-3</v>
+        <f>([1]Basic_load!$B$28*[1]Basic_load!G21)*0.85</f>
+        <v>3.6057866999999993E-2</v>
       </c>
       <c r="AC20" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G21)*0.1</f>
-        <v>4.2421020000000002E-3</v>
+        <f>([1]Basic_load!$B$29*[1]Basic_load!G21)*0.85</f>
+        <v>3.6057866999999993E-2</v>
       </c>
       <c r="AD20" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G21)*0.1</f>
-        <v>8.4842040000000004E-3</v>
+        <f>([1]Basic_load!$B$30*[1]Basic_load!G21)*0.85</f>
+        <v>7.2115733999999987E-2</v>
       </c>
       <c r="AE20" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G21)*0.1</f>
-        <v>1.4140340000000001E-2</v>
+        <f>([1]Basic_load!$B$31*[1]Basic_load!G21)*0.85</f>
+        <v>0.12019289000000001</v>
       </c>
       <c r="AF20" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G21)*0.1</f>
-        <v>1.0605255000000001E-2</v>
+        <f>([1]Basic_load!$B$32*[1]Basic_load!G21)*0.85</f>
+        <v>9.0144667499999998E-2</v>
       </c>
       <c r="AG20" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G21)*0.1</f>
-        <v>1.4847357E-2</v>
+        <f>([1]Basic_load!$B$33*[1]Basic_load!G21)*0.85</f>
+        <v>0.12620253449999999</v>
       </c>
       <c r="AH20" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G21)*0.1</f>
-        <v>4.2421020000000002E-3</v>
+        <f>([1]Basic_load!$B$34*[1]Basic_load!G21)*0.85</f>
+        <v>3.6057866999999993E-2</v>
       </c>
     </row>
     <row r="21" spans="1:34" x14ac:dyDescent="0.3">
@@ -3399,135 +4114,134 @@
         <v>0.79166666666666696</v>
       </c>
       <c r="B21" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G22)*0.1</f>
+        <f>([1]Basic_load!$B$2*[1]Basic_load!G22)*0.85</f>
         <v>0</v>
       </c>
       <c r="C21" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G22)*0.1</f>
-        <v>5.8646699999999998E-3</v>
+        <f>([1]Basic_load!$B$3*[1]Basic_load!G22)*0.85</f>
+        <v>4.9849694999999992E-2</v>
       </c>
       <c r="D21" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G22)*0.1</f>
-        <v>5.2782029999999995E-3</v>
+        <f>([1]Basic_load!$B$4*[1]Basic_load!G22)*0.85</f>
+        <v>4.4864725499999994E-2</v>
       </c>
       <c r="E21" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G22)*0.1</f>
-        <v>5.8646699999999998E-3</v>
+        <f>([1]Basic_load!$B$5*[1]Basic_load!G22)*0.85</f>
+        <v>4.9849694999999992E-2</v>
       </c>
       <c r="F21" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G22)*0.1</f>
-        <v>3.5188019999999997E-3</v>
+        <f>([1]Basic_load!$B$6*[1]Basic_load!G22)*0.85</f>
+        <v>2.9909816999999995E-2</v>
       </c>
       <c r="G21" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G22)*0.1</f>
-        <v>3.5188019999999997E-3</v>
+        <f>([1]Basic_load!$B$7*[1]Basic_load!G22)*0.85</f>
+        <v>2.9909816999999995E-2</v>
       </c>
       <c r="H21" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G22)*0.1</f>
-        <v>1.172934E-2</v>
+        <f>([1]Basic_load!$B$8*[1]Basic_load!G22)*0.85</f>
+        <v>9.9699389999999985E-2</v>
       </c>
       <c r="I21" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G22)*0.1</f>
-        <v>1.172934E-2</v>
+        <f>([1]Basic_load!$B$9*[1]Basic_load!G22)*0.85</f>
+        <v>9.9699389999999985E-2</v>
       </c>
       <c r="J21" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G22)*0.1</f>
-        <v>3.5188019999999997E-3</v>
+        <f>([1]Basic_load!$B$10*[1]Basic_load!G22)*0.85</f>
+        <v>2.9909816999999995E-2</v>
       </c>
       <c r="K21" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G22)*0.1</f>
-        <v>3.5188019999999997E-3</v>
+        <f>([1]Basic_load!$B$11*[1]Basic_load!G22)*0.85</f>
+        <v>2.9909816999999995E-2</v>
       </c>
       <c r="L21" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G22)*0.1</f>
-        <v>2.6391014999999998E-3</v>
+        <f>([1]Basic_load!$B$12*[1]Basic_load!G22)*0.85</f>
+        <v>2.2432362749999997E-2</v>
       </c>
       <c r="M21" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G22)*0.1</f>
-        <v>3.5188019999999997E-3</v>
+        <f>([1]Basic_load!$B$13*[1]Basic_load!G22)*0.85</f>
+        <v>2.9909816999999995E-2</v>
       </c>
       <c r="N21" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G22)*0.1</f>
-        <v>3.5188019999999997E-3</v>
+        <f>([1]Basic_load!$B$14*[1]Basic_load!G22)*0.85</f>
+        <v>2.9909816999999995E-2</v>
       </c>
       <c r="O21" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G22)*0.1</f>
-        <v>7.0376039999999994E-3</v>
+        <f>([1]Basic_load!$B$15*[1]Basic_load!G22)*0.85</f>
+        <v>5.981963399999999E-2</v>
       </c>
       <c r="P21" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G22)*0.1</f>
-        <v>3.5188019999999997E-3</v>
+        <f>([1]Basic_load!$B$16*[1]Basic_load!G22)*0.85</f>
+        <v>2.9909816999999995E-2</v>
       </c>
       <c r="Q21" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G22)*0.1</f>
-        <v>3.5188019999999997E-3</v>
+        <f>([1]Basic_load!$B$17*[1]Basic_load!G22)*0.85</f>
+        <v>2.9909816999999995E-2</v>
       </c>
       <c r="R21" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G22)*0.1</f>
-        <v>3.5188019999999997E-3</v>
+        <f>([1]Basic_load!$B$18*[1]Basic_load!G22)*0.85</f>
+        <v>2.9909816999999995E-2</v>
       </c>
       <c r="S21" s="8">
+        <v>0.33319999999999994</v>
+      </c>
+      <c r="T21" s="7">
+        <f>([1]Basic_load!$B$20*[1]Basic_load!G22)*0.85</f>
+        <v>4.4864725499999994E-2</v>
+      </c>
+      <c r="U21" s="7">
+        <f>([1]Basic_load!$B$21*[1]Basic_load!G22)*0.85</f>
+        <v>4.4864725499999994E-2</v>
+      </c>
+      <c r="V21" s="7">
+        <f>([1]Basic_load!$B$22*[1]Basic_load!G22)*0.85</f>
+        <v>4.4864725499999994E-2</v>
+      </c>
+      <c r="W21" s="7">
         <v>0</v>
       </c>
-      <c r="T21" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G22)*0.1</f>
-        <v>5.2782029999999995E-3</v>
-      </c>
-      <c r="U21" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G22)*0.1</f>
-        <v>5.2782029999999995E-3</v>
-      </c>
-      <c r="V21" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G22)*0.1</f>
-        <v>5.2782029999999995E-3</v>
-      </c>
-      <c r="W21" s="7">
-        <f>([1]Basic_load!$B$23*[1]Basic_load!G22)*0.1</f>
-        <v>5.2782029999999995E-3</v>
-      </c>
       <c r="X21" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G22)*0.1</f>
-        <v>5.2782029999999995E-3</v>
+        <f>([1]Basic_load!$B$24*[1]Basic_load!G22)*0.85</f>
+        <v>4.4864725499999994E-2</v>
       </c>
       <c r="Y21" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G22)*0.1</f>
-        <v>2.4631613999999996E-2</v>
+        <f>([1]Basic_load!$B$25*[1]Basic_load!G22)*0.85</f>
+        <v>0.20936871899999995</v>
       </c>
       <c r="Z21" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G22)*0.1</f>
-        <v>2.4631613999999996E-2</v>
+        <f>([1]Basic_load!$B$26*[1]Basic_load!G22)*0.85</f>
+        <v>0.20936871899999995</v>
       </c>
       <c r="AA21" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G22)*0.1</f>
-        <v>3.5188019999999997E-3</v>
+        <f>([1]Basic_load!$B$27*[1]Basic_load!G22)*0.85</f>
+        <v>2.9909816999999995E-2</v>
       </c>
       <c r="AB21" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G22)*0.1</f>
-        <v>3.5188019999999997E-3</v>
+        <f>([1]Basic_load!$B$28*[1]Basic_load!G22)*0.85</f>
+        <v>2.9909816999999995E-2</v>
       </c>
       <c r="AC21" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G22)*0.1</f>
-        <v>3.5188019999999997E-3</v>
+        <f>([1]Basic_load!$B$29*[1]Basic_load!G22)*0.85</f>
+        <v>2.9909816999999995E-2</v>
       </c>
       <c r="AD21" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G22)*0.1</f>
-        <v>7.0376039999999994E-3</v>
+        <f>([1]Basic_load!$B$30*[1]Basic_load!G22)*0.85</f>
+        <v>5.981963399999999E-2</v>
       </c>
       <c r="AE21" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G22)*0.1</f>
-        <v>1.172934E-2</v>
+        <f>([1]Basic_load!$B$31*[1]Basic_load!G22)*0.85</f>
+        <v>9.9699389999999985E-2</v>
       </c>
       <c r="AF21" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G22)*0.1</f>
-        <v>8.7970050000000001E-3</v>
+        <f>([1]Basic_load!$B$32*[1]Basic_load!G22)*0.85</f>
+        <v>7.4774542499999999E-2</v>
       </c>
       <c r="AG21" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G22)*0.1</f>
-        <v>1.2315806999999998E-2</v>
+        <f>([1]Basic_load!$B$33*[1]Basic_load!G22)*0.85</f>
+        <v>0.10468435949999998</v>
       </c>
       <c r="AH21" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G22)*0.1</f>
-        <v>3.5188019999999997E-3</v>
+        <f>([1]Basic_load!$B$34*[1]Basic_load!G22)*0.85</f>
+        <v>2.9909816999999995E-2</v>
       </c>
     </row>
     <row r="22" spans="1:34" x14ac:dyDescent="0.3">
@@ -3535,135 +4249,134 @@
         <v>0.83333333333333404</v>
       </c>
       <c r="B22" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G23)*0.1</f>
+        <f>([1]Basic_load!$B$2*[1]Basic_load!G23)*0.85</f>
         <v>0</v>
       </c>
       <c r="C22" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G23)*0.1</f>
-        <v>4.8171700000000008E-3</v>
+        <f>([1]Basic_load!$B$3*[1]Basic_load!G23)*0.85</f>
+        <v>4.0945945000000004E-2</v>
       </c>
       <c r="D22" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G23)*0.1</f>
-        <v>4.3354530000000004E-3</v>
+        <f>([1]Basic_load!$B$4*[1]Basic_load!G23)*0.85</f>
+        <v>3.6851350499999998E-2</v>
       </c>
       <c r="E22" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G23)*0.1</f>
-        <v>4.8171700000000008E-3</v>
+        <f>([1]Basic_load!$B$5*[1]Basic_load!G23)*0.85</f>
+        <v>4.0945945000000004E-2</v>
       </c>
       <c r="F22" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G23)*0.1</f>
-        <v>2.890302E-3</v>
+        <f>([1]Basic_load!$B$6*[1]Basic_load!G23)*0.85</f>
+        <v>2.4567566999999998E-2</v>
       </c>
       <c r="G22" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G23)*0.1</f>
-        <v>2.890302E-3</v>
+        <f>([1]Basic_load!$B$7*[1]Basic_load!G23)*0.85</f>
+        <v>2.4567566999999998E-2</v>
       </c>
       <c r="H22" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G23)*0.1</f>
-        <v>9.6343400000000017E-3</v>
+        <f>([1]Basic_load!$B$8*[1]Basic_load!G23)*0.85</f>
+        <v>8.1891890000000009E-2</v>
       </c>
       <c r="I22" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G23)*0.1</f>
-        <v>9.6343400000000017E-3</v>
+        <f>([1]Basic_load!$B$9*[1]Basic_load!G23)*0.85</f>
+        <v>8.1891890000000009E-2</v>
       </c>
       <c r="J22" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G23)*0.1</f>
-        <v>2.890302E-3</v>
+        <f>([1]Basic_load!$B$10*[1]Basic_load!G23)*0.85</f>
+        <v>2.4567566999999998E-2</v>
       </c>
       <c r="K22" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G23)*0.1</f>
-        <v>2.890302E-3</v>
+        <f>([1]Basic_load!$B$11*[1]Basic_load!G23)*0.85</f>
+        <v>2.4567566999999998E-2</v>
       </c>
       <c r="L22" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G23)*0.1</f>
-        <v>2.1677265000000002E-3</v>
+        <f>([1]Basic_load!$B$12*[1]Basic_load!G23)*0.85</f>
+        <v>1.8425675249999999E-2</v>
       </c>
       <c r="M22" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G23)*0.1</f>
-        <v>2.890302E-3</v>
+        <f>([1]Basic_load!$B$13*[1]Basic_load!G23)*0.85</f>
+        <v>2.4567566999999998E-2</v>
       </c>
       <c r="N22" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G23)*0.1</f>
-        <v>2.890302E-3</v>
+        <f>([1]Basic_load!$B$14*[1]Basic_load!G23)*0.85</f>
+        <v>2.4567566999999998E-2</v>
       </c>
       <c r="O22" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G23)*0.1</f>
-        <v>5.780604E-3</v>
+        <f>([1]Basic_load!$B$15*[1]Basic_load!G23)*0.85</f>
+        <v>4.9135133999999997E-2</v>
       </c>
       <c r="P22" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G23)*0.1</f>
-        <v>2.890302E-3</v>
+        <f>([1]Basic_load!$B$16*[1]Basic_load!G23)*0.85</f>
+        <v>2.4567566999999998E-2</v>
       </c>
       <c r="Q22" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G23)*0.1</f>
-        <v>2.890302E-3</v>
+        <f>([1]Basic_load!$B$17*[1]Basic_load!G23)*0.85</f>
+        <v>2.4567566999999998E-2</v>
       </c>
       <c r="R22" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G23)*0.1</f>
-        <v>2.890302E-3</v>
+        <f>([1]Basic_load!$B$18*[1]Basic_load!G23)*0.85</f>
+        <v>2.4567566999999998E-2</v>
       </c>
       <c r="S22" s="8">
+        <v>0.33319999999999994</v>
+      </c>
+      <c r="T22" s="7">
+        <f>([1]Basic_load!$B$20*[1]Basic_load!G23)*0.85</f>
+        <v>3.6851350499999998E-2</v>
+      </c>
+      <c r="U22" s="7">
+        <f>([1]Basic_load!$B$21*[1]Basic_load!G23)*0.85</f>
+        <v>3.6851350499999998E-2</v>
+      </c>
+      <c r="V22" s="7">
+        <f>([1]Basic_load!$B$22*[1]Basic_load!G23)*0.85</f>
+        <v>3.6851350499999998E-2</v>
+      </c>
+      <c r="W22" s="7">
         <v>0</v>
       </c>
-      <c r="T22" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G23)*0.1</f>
-        <v>4.3354530000000004E-3</v>
-      </c>
-      <c r="U22" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G23)*0.1</f>
-        <v>4.3354530000000004E-3</v>
-      </c>
-      <c r="V22" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G23)*0.1</f>
-        <v>4.3354530000000004E-3</v>
-      </c>
-      <c r="W22" s="7">
-        <f>([1]Basic_load!$B$23*[1]Basic_load!G23)*0.1</f>
-        <v>4.3354530000000004E-3</v>
-      </c>
       <c r="X22" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G23)*0.1</f>
-        <v>4.3354530000000004E-3</v>
+        <f>([1]Basic_load!$B$24*[1]Basic_load!G23)*0.85</f>
+        <v>3.6851350499999998E-2</v>
       </c>
       <c r="Y22" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G23)*0.1</f>
-        <v>2.0232113999999999E-2</v>
+        <f>([1]Basic_load!$B$25*[1]Basic_load!G23)*0.85</f>
+        <v>0.17197296899999998</v>
       </c>
       <c r="Z22" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G23)*0.1</f>
-        <v>2.0232113999999999E-2</v>
+        <f>([1]Basic_load!$B$26*[1]Basic_load!G23)*0.85</f>
+        <v>0.17197296899999998</v>
       </c>
       <c r="AA22" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G23)*0.1</f>
-        <v>2.890302E-3</v>
+        <f>([1]Basic_load!$B$27*[1]Basic_load!G23)*0.85</f>
+        <v>2.4567566999999998E-2</v>
       </c>
       <c r="AB22" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G23)*0.1</f>
-        <v>2.890302E-3</v>
+        <f>([1]Basic_load!$B$28*[1]Basic_load!G23)*0.85</f>
+        <v>2.4567566999999998E-2</v>
       </c>
       <c r="AC22" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G23)*0.1</f>
-        <v>2.890302E-3</v>
+        <f>([1]Basic_load!$B$29*[1]Basic_load!G23)*0.85</f>
+        <v>2.4567566999999998E-2</v>
       </c>
       <c r="AD22" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G23)*0.1</f>
-        <v>5.780604E-3</v>
+        <f>([1]Basic_load!$B$30*[1]Basic_load!G23)*0.85</f>
+        <v>4.9135133999999997E-2</v>
       </c>
       <c r="AE22" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G23)*0.1</f>
-        <v>9.6343400000000017E-3</v>
+        <f>([1]Basic_load!$B$31*[1]Basic_load!G23)*0.85</f>
+        <v>8.1891890000000009E-2</v>
       </c>
       <c r="AF22" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G23)*0.1</f>
-        <v>7.2257550000000004E-3</v>
+        <f>([1]Basic_load!$B$32*[1]Basic_load!G23)*0.85</f>
+        <v>6.1418917500000003E-2</v>
       </c>
       <c r="AG22" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G23)*0.1</f>
-        <v>1.0116056999999999E-2</v>
+        <f>([1]Basic_load!$B$33*[1]Basic_load!G23)*0.85</f>
+        <v>8.5986484499999988E-2</v>
       </c>
       <c r="AH22" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G23)*0.1</f>
-        <v>2.890302E-3</v>
+        <f>([1]Basic_load!$B$34*[1]Basic_load!G23)*0.85</f>
+        <v>2.4567566999999998E-2</v>
       </c>
     </row>
     <row r="23" spans="1:34" x14ac:dyDescent="0.3">
@@ -3671,135 +4384,134 @@
         <v>0.875000000000001</v>
       </c>
       <c r="B23" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G24)*0.1</f>
+        <f>([1]Basic_load!$B$2*[1]Basic_load!G24)*0.85</f>
         <v>0</v>
       </c>
       <c r="C23" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G24)*0.1</f>
-        <v>5.4343300000000011E-3</v>
+        <f>([1]Basic_load!$B$3*[1]Basic_load!G24)*0.85</f>
+        <v>4.6191805000000009E-2</v>
       </c>
       <c r="D23" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G24)*0.1</f>
-        <v>4.8908970000000008E-3</v>
+        <f>([1]Basic_load!$B$4*[1]Basic_load!G24)*0.85</f>
+        <v>4.1572624500000002E-2</v>
       </c>
       <c r="E23" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G24)*0.1</f>
-        <v>5.4343300000000011E-3</v>
+        <f>([1]Basic_load!$B$5*[1]Basic_load!G24)*0.85</f>
+        <v>4.6191805000000009E-2</v>
       </c>
       <c r="F23" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G24)*0.1</f>
-        <v>3.260598E-3</v>
+        <f>([1]Basic_load!$B$6*[1]Basic_load!G24)*0.85</f>
+        <v>2.7715082999999998E-2</v>
       </c>
       <c r="G23" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G24)*0.1</f>
-        <v>3.260598E-3</v>
+        <f>([1]Basic_load!$B$7*[1]Basic_load!G24)*0.85</f>
+        <v>2.7715082999999998E-2</v>
       </c>
       <c r="H23" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G24)*0.1</f>
-        <v>1.0868660000000002E-2</v>
+        <f>([1]Basic_load!$B$8*[1]Basic_load!G24)*0.85</f>
+        <v>9.2383610000000019E-2</v>
       </c>
       <c r="I23" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G24)*0.1</f>
-        <v>1.0868660000000002E-2</v>
+        <f>([1]Basic_load!$B$9*[1]Basic_load!G24)*0.85</f>
+        <v>9.2383610000000019E-2</v>
       </c>
       <c r="J23" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G24)*0.1</f>
-        <v>3.260598E-3</v>
+        <f>([1]Basic_load!$B$10*[1]Basic_load!G24)*0.85</f>
+        <v>2.7715082999999998E-2</v>
       </c>
       <c r="K23" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G24)*0.1</f>
-        <v>3.260598E-3</v>
+        <f>([1]Basic_load!$B$11*[1]Basic_load!G24)*0.85</f>
+        <v>2.7715082999999998E-2</v>
       </c>
       <c r="L23" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G24)*0.1</f>
-        <v>2.4454485000000004E-3</v>
+        <f>([1]Basic_load!$B$12*[1]Basic_load!G24)*0.85</f>
+        <v>2.0786312250000001E-2</v>
       </c>
       <c r="M23" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G24)*0.1</f>
-        <v>3.260598E-3</v>
+        <f>([1]Basic_load!$B$13*[1]Basic_load!G24)*0.85</f>
+        <v>2.7715082999999998E-2</v>
       </c>
       <c r="N23" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G24)*0.1</f>
-        <v>3.260598E-3</v>
+        <f>([1]Basic_load!$B$14*[1]Basic_load!G24)*0.85</f>
+        <v>2.7715082999999998E-2</v>
       </c>
       <c r="O23" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G24)*0.1</f>
-        <v>6.5211959999999999E-3</v>
+        <f>([1]Basic_load!$B$15*[1]Basic_load!G24)*0.85</f>
+        <v>5.5430165999999996E-2</v>
       </c>
       <c r="P23" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G24)*0.1</f>
-        <v>3.260598E-3</v>
+        <f>([1]Basic_load!$B$16*[1]Basic_load!G24)*0.85</f>
+        <v>2.7715082999999998E-2</v>
       </c>
       <c r="Q23" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G24)*0.1</f>
-        <v>3.260598E-3</v>
+        <f>([1]Basic_load!$B$17*[1]Basic_load!G24)*0.85</f>
+        <v>2.7715082999999998E-2</v>
       </c>
       <c r="R23" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G24)*0.1</f>
-        <v>3.260598E-3</v>
+        <f>([1]Basic_load!$B$18*[1]Basic_load!G24)*0.85</f>
+        <v>2.7715082999999998E-2</v>
       </c>
       <c r="S23" s="8">
+        <v>0.40879999999999994</v>
+      </c>
+      <c r="T23" s="7">
+        <f>([1]Basic_load!$B$20*[1]Basic_load!G24)*0.85</f>
+        <v>4.1572624500000002E-2</v>
+      </c>
+      <c r="U23" s="7">
+        <f>([1]Basic_load!$B$21*[1]Basic_load!G24)*0.85</f>
+        <v>4.1572624500000002E-2</v>
+      </c>
+      <c r="V23" s="7">
+        <f>([1]Basic_load!$B$22*[1]Basic_load!G24)*0.85</f>
+        <v>4.1572624500000002E-2</v>
+      </c>
+      <c r="W23" s="7">
         <v>0</v>
       </c>
-      <c r="T23" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G24)*0.1</f>
-        <v>4.8908970000000008E-3</v>
-      </c>
-      <c r="U23" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G24)*0.1</f>
-        <v>4.8908970000000008E-3</v>
-      </c>
-      <c r="V23" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G24)*0.1</f>
-        <v>4.8908970000000008E-3</v>
-      </c>
-      <c r="W23" s="7">
-        <f>([1]Basic_load!$B$23*[1]Basic_load!G24)*0.1</f>
-        <v>4.8908970000000008E-3</v>
-      </c>
       <c r="X23" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G24)*0.1</f>
-        <v>4.8908970000000008E-3</v>
+        <f>([1]Basic_load!$B$24*[1]Basic_load!G24)*0.85</f>
+        <v>4.1572624500000002E-2</v>
       </c>
       <c r="Y23" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G24)*0.1</f>
-        <v>2.2824186000000003E-2</v>
+        <f>([1]Basic_load!$B$25*[1]Basic_load!G24)*0.85</f>
+        <v>0.19400558100000001</v>
       </c>
       <c r="Z23" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G24)*0.1</f>
-        <v>2.2824186000000003E-2</v>
+        <f>([1]Basic_load!$B$26*[1]Basic_load!G24)*0.85</f>
+        <v>0.19400558100000001</v>
       </c>
       <c r="AA23" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G24)*0.1</f>
-        <v>3.260598E-3</v>
+        <f>([1]Basic_load!$B$27*[1]Basic_load!G24)*0.85</f>
+        <v>2.7715082999999998E-2</v>
       </c>
       <c r="AB23" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G24)*0.1</f>
-        <v>3.260598E-3</v>
+        <f>([1]Basic_load!$B$28*[1]Basic_load!G24)*0.85</f>
+        <v>2.7715082999999998E-2</v>
       </c>
       <c r="AC23" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G24)*0.1</f>
-        <v>3.260598E-3</v>
+        <f>([1]Basic_load!$B$29*[1]Basic_load!G24)*0.85</f>
+        <v>2.7715082999999998E-2</v>
       </c>
       <c r="AD23" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G24)*0.1</f>
-        <v>6.5211959999999999E-3</v>
+        <f>([1]Basic_load!$B$30*[1]Basic_load!G24)*0.85</f>
+        <v>5.5430165999999996E-2</v>
       </c>
       <c r="AE23" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G24)*0.1</f>
-        <v>1.0868660000000002E-2</v>
+        <f>([1]Basic_load!$B$31*[1]Basic_load!G24)*0.85</f>
+        <v>9.2383610000000019E-2</v>
       </c>
       <c r="AF23" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G24)*0.1</f>
-        <v>8.1514949999999999E-3</v>
+        <f>([1]Basic_load!$B$32*[1]Basic_load!G24)*0.85</f>
+        <v>6.9287707500000004E-2</v>
       </c>
       <c r="AG23" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G24)*0.1</f>
-        <v>1.1412093000000002E-2</v>
+        <f>([1]Basic_load!$B$33*[1]Basic_load!G24)*0.85</f>
+        <v>9.7002790500000005E-2</v>
       </c>
       <c r="AH23" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G24)*0.1</f>
-        <v>3.260598E-3</v>
+        <f>([1]Basic_load!$B$34*[1]Basic_load!G24)*0.85</f>
+        <v>2.7715082999999998E-2</v>
       </c>
     </row>
     <row r="24" spans="1:34" x14ac:dyDescent="0.3">
@@ -3807,135 +4519,134 @@
         <v>0.91666666666666696</v>
       </c>
       <c r="B24" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G25)*0.1</f>
+        <f>([1]Basic_load!$B$2*[1]Basic_load!G25)*0.85</f>
         <v>0</v>
       </c>
       <c r="C24" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G25)*0.1</f>
-        <v>6.8446700000000015E-3</v>
+        <f>([1]Basic_load!$B$3*[1]Basic_load!G25)*0.85</f>
+        <v>5.817969500000001E-2</v>
       </c>
       <c r="D24" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G25)*0.1</f>
-        <v>6.1602030000000004E-3</v>
+        <f>([1]Basic_load!$B$4*[1]Basic_load!G25)*0.85</f>
+        <v>5.2361725499999998E-2</v>
       </c>
       <c r="E24" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G25)*0.1</f>
-        <v>6.8446700000000015E-3</v>
+        <f>([1]Basic_load!$B$5*[1]Basic_load!G25)*0.85</f>
+        <v>5.817969500000001E-2</v>
       </c>
       <c r="F24" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G25)*0.1</f>
-        <v>4.1068020000000005E-3</v>
+        <f>([1]Basic_load!$B$6*[1]Basic_load!G25)*0.85</f>
+        <v>3.4907817000000001E-2</v>
       </c>
       <c r="G24" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G25)*0.1</f>
-        <v>4.1068020000000005E-3</v>
+        <f>([1]Basic_load!$B$7*[1]Basic_load!G25)*0.85</f>
+        <v>3.4907817000000001E-2</v>
       </c>
       <c r="H24" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G25)*0.1</f>
-        <v>1.3689340000000003E-2</v>
+        <f>([1]Basic_load!$B$8*[1]Basic_load!G25)*0.85</f>
+        <v>0.11635939000000002</v>
       </c>
       <c r="I24" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G25)*0.1</f>
-        <v>1.3689340000000003E-2</v>
+        <f>([1]Basic_load!$B$9*[1]Basic_load!G25)*0.85</f>
+        <v>0.11635939000000002</v>
       </c>
       <c r="J24" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G25)*0.1</f>
-        <v>4.1068020000000005E-3</v>
+        <f>([1]Basic_load!$B$10*[1]Basic_load!G25)*0.85</f>
+        <v>3.4907817000000001E-2</v>
       </c>
       <c r="K24" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G25)*0.1</f>
-        <v>4.1068020000000005E-3</v>
+        <f>([1]Basic_load!$B$11*[1]Basic_load!G25)*0.85</f>
+        <v>3.4907817000000001E-2</v>
       </c>
       <c r="L24" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G25)*0.1</f>
-        <v>3.0801015000000002E-3</v>
+        <f>([1]Basic_load!$B$12*[1]Basic_load!G25)*0.85</f>
+        <v>2.6180862749999999E-2</v>
       </c>
       <c r="M24" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G25)*0.1</f>
-        <v>4.1068020000000005E-3</v>
+        <f>([1]Basic_load!$B$13*[1]Basic_load!G25)*0.85</f>
+        <v>3.4907817000000001E-2</v>
       </c>
       <c r="N24" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G25)*0.1</f>
-        <v>4.1068020000000005E-3</v>
+        <f>([1]Basic_load!$B$14*[1]Basic_load!G25)*0.85</f>
+        <v>3.4907817000000001E-2</v>
       </c>
       <c r="O24" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G25)*0.1</f>
-        <v>8.2136040000000011E-3</v>
+        <f>([1]Basic_load!$B$15*[1]Basic_load!G25)*0.85</f>
+        <v>6.9815634000000001E-2</v>
       </c>
       <c r="P24" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G25)*0.1</f>
-        <v>4.1068020000000005E-3</v>
+        <f>([1]Basic_load!$B$16*[1]Basic_load!G25)*0.85</f>
+        <v>3.4907817000000001E-2</v>
       </c>
       <c r="Q24" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G25)*0.1</f>
-        <v>4.1068020000000005E-3</v>
+        <f>([1]Basic_load!$B$17*[1]Basic_load!G25)*0.85</f>
+        <v>3.4907817000000001E-2</v>
       </c>
       <c r="R24" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G25)*0.1</f>
-        <v>4.1068020000000005E-3</v>
+        <f>([1]Basic_load!$B$18*[1]Basic_load!G25)*0.85</f>
+        <v>3.4907817000000001E-2</v>
       </c>
       <c r="S24" s="8">
+        <v>0.40879999999999994</v>
+      </c>
+      <c r="T24" s="7">
+        <f>([1]Basic_load!$B$20*[1]Basic_load!G25)*0.85</f>
+        <v>5.2361725499999998E-2</v>
+      </c>
+      <c r="U24" s="7">
+        <f>([1]Basic_load!$B$21*[1]Basic_load!G25)*0.85</f>
+        <v>5.2361725499999998E-2</v>
+      </c>
+      <c r="V24" s="7">
+        <f>([1]Basic_load!$B$22*[1]Basic_load!G25)*0.85</f>
+        <v>5.2361725499999998E-2</v>
+      </c>
+      <c r="W24" s="7">
         <v>0</v>
       </c>
-      <c r="T24" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G25)*0.1</f>
-        <v>6.1602030000000004E-3</v>
-      </c>
-      <c r="U24" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G25)*0.1</f>
-        <v>6.1602030000000004E-3</v>
-      </c>
-      <c r="V24" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G25)*0.1</f>
-        <v>6.1602030000000004E-3</v>
-      </c>
-      <c r="W24" s="7">
-        <f>([1]Basic_load!$B$23*[1]Basic_load!G25)*0.1</f>
-        <v>6.1602030000000004E-3</v>
-      </c>
       <c r="X24" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G25)*0.1</f>
-        <v>6.1602030000000004E-3</v>
+        <f>([1]Basic_load!$B$24*[1]Basic_load!G25)*0.85</f>
+        <v>5.2361725499999998E-2</v>
       </c>
       <c r="Y24" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G25)*0.1</f>
-        <v>2.8747614000000001E-2</v>
+        <f>([1]Basic_load!$B$25*[1]Basic_load!G25)*0.85</f>
+        <v>0.244354719</v>
       </c>
       <c r="Z24" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G25)*0.1</f>
-        <v>2.8747614000000001E-2</v>
+        <f>([1]Basic_load!$B$26*[1]Basic_load!G25)*0.85</f>
+        <v>0.244354719</v>
       </c>
       <c r="AA24" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G25)*0.1</f>
-        <v>4.1068020000000005E-3</v>
+        <f>([1]Basic_load!$B$27*[1]Basic_load!G25)*0.85</f>
+        <v>3.4907817000000001E-2</v>
       </c>
       <c r="AB24" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G25)*0.1</f>
-        <v>4.1068020000000005E-3</v>
+        <f>([1]Basic_load!$B$28*[1]Basic_load!G25)*0.85</f>
+        <v>3.4907817000000001E-2</v>
       </c>
       <c r="AC24" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G25)*0.1</f>
-        <v>4.1068020000000005E-3</v>
+        <f>([1]Basic_load!$B$29*[1]Basic_load!G25)*0.85</f>
+        <v>3.4907817000000001E-2</v>
       </c>
       <c r="AD24" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G25)*0.1</f>
-        <v>8.2136040000000011E-3</v>
+        <f>([1]Basic_load!$B$30*[1]Basic_load!G25)*0.85</f>
+        <v>6.9815634000000001E-2</v>
       </c>
       <c r="AE24" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G25)*0.1</f>
-        <v>1.3689340000000003E-2</v>
+        <f>([1]Basic_load!$B$31*[1]Basic_load!G25)*0.85</f>
+        <v>0.11635939000000002</v>
       </c>
       <c r="AF24" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G25)*0.1</f>
-        <v>1.0267005000000001E-2</v>
+        <f>([1]Basic_load!$B$32*[1]Basic_load!G25)*0.85</f>
+        <v>8.7269542499999991E-2</v>
       </c>
       <c r="AG24" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G25)*0.1</f>
-        <v>1.4373807000000001E-2</v>
+        <f>([1]Basic_load!$B$33*[1]Basic_load!G25)*0.85</f>
+        <v>0.1221773595</v>
       </c>
       <c r="AH24" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G25)*0.1</f>
-        <v>4.1068020000000005E-3</v>
+        <f>([1]Basic_load!$B$34*[1]Basic_load!G25)*0.85</f>
+        <v>3.4907817000000001E-2</v>
       </c>
     </row>
     <row r="25" spans="1:34" x14ac:dyDescent="0.3">
@@ -3943,149 +4654,455 @@
         <v>0.95833333333333404</v>
       </c>
       <c r="B25" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G26)*0.1</f>
+        <f>([1]Basic_load!$B$2*[1]Basic_load!G26)*0.85</f>
         <v>0</v>
       </c>
       <c r="C25" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G26)*0.1</f>
-        <v>1.1882000000000002E-3</v>
+        <f>([1]Basic_load!$B$3*[1]Basic_load!G26)*0.85</f>
+        <v>1.00997E-2</v>
       </c>
       <c r="D25" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G26)*0.1</f>
-        <v>1.06938E-3</v>
+        <f>([1]Basic_load!$B$4*[1]Basic_load!G26)*0.85</f>
+        <v>9.089729999999999E-3</v>
       </c>
       <c r="E25" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G26)*0.1</f>
-        <v>1.1882000000000002E-3</v>
+        <f>([1]Basic_load!$B$5*[1]Basic_load!G26)*0.85</f>
+        <v>1.00997E-2</v>
       </c>
       <c r="F25" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G26)*0.1</f>
-        <v>7.1292000000000003E-4</v>
+        <f>([1]Basic_load!$B$6*[1]Basic_load!G26)*0.85</f>
+        <v>6.0598199999999996E-3</v>
       </c>
       <c r="G25" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G26)*0.1</f>
-        <v>7.1292000000000003E-4</v>
+        <f>([1]Basic_load!$B$7*[1]Basic_load!G26)*0.85</f>
+        <v>6.0598199999999996E-3</v>
       </c>
       <c r="H25" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G26)*0.1</f>
-        <v>2.3764000000000003E-3</v>
+        <f>([1]Basic_load!$B$8*[1]Basic_load!G26)*0.85</f>
+        <v>2.0199399999999999E-2</v>
       </c>
       <c r="I25" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G26)*0.1</f>
-        <v>2.3764000000000003E-3</v>
+        <f>([1]Basic_load!$B$9*[1]Basic_load!G26)*0.85</f>
+        <v>2.0199399999999999E-2</v>
       </c>
       <c r="J25" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G26)*0.1</f>
-        <v>7.1292000000000003E-4</v>
+        <f>([1]Basic_load!$B$10*[1]Basic_load!G26)*0.85</f>
+        <v>6.0598199999999996E-3</v>
       </c>
       <c r="K25" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G26)*0.1</f>
-        <v>7.1292000000000003E-4</v>
+        <f>([1]Basic_load!$B$11*[1]Basic_load!G26)*0.85</f>
+        <v>6.0598199999999996E-3</v>
       </c>
       <c r="L25" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G26)*0.1</f>
-        <v>5.3468999999999999E-4</v>
+        <f>([1]Basic_load!$B$12*[1]Basic_load!G26)*0.85</f>
+        <v>4.5448649999999995E-3</v>
       </c>
       <c r="M25" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G26)*0.1</f>
-        <v>7.1292000000000003E-4</v>
+        <f>([1]Basic_load!$B$13*[1]Basic_load!G26)*0.85</f>
+        <v>6.0598199999999996E-3</v>
       </c>
       <c r="N25" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G26)*0.1</f>
-        <v>7.1292000000000003E-4</v>
+        <f>([1]Basic_load!$B$14*[1]Basic_load!G26)*0.85</f>
+        <v>6.0598199999999996E-3</v>
       </c>
       <c r="O25" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G26)*0.1</f>
-        <v>1.4258400000000001E-3</v>
+        <f>([1]Basic_load!$B$15*[1]Basic_load!G26)*0.85</f>
+        <v>1.2119639999999999E-2</v>
       </c>
       <c r="P25" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G26)*0.1</f>
-        <v>7.1292000000000003E-4</v>
+        <f>([1]Basic_load!$B$16*[1]Basic_load!G26)*0.85</f>
+        <v>6.0598199999999996E-3</v>
       </c>
       <c r="Q25" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G26)*0.1</f>
-        <v>7.1292000000000003E-4</v>
+        <f>([1]Basic_load!$B$17*[1]Basic_load!G26)*0.85</f>
+        <v>6.0598199999999996E-3</v>
       </c>
       <c r="R25" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G26)*0.1</f>
-        <v>7.1292000000000003E-4</v>
+        <f>([1]Basic_load!$B$18*[1]Basic_load!G26)*0.85</f>
+        <v>6.0598199999999996E-3</v>
       </c>
       <c r="S25" s="8">
+        <v>0.30869999999999997</v>
+      </c>
+      <c r="T25" s="7">
+        <f>([1]Basic_load!$B$20*[1]Basic_load!G26)*0.85</f>
+        <v>9.089729999999999E-3</v>
+      </c>
+      <c r="U25" s="7">
+        <f>([1]Basic_load!$B$21*[1]Basic_load!G26)*0.85</f>
+        <v>9.089729999999999E-3</v>
+      </c>
+      <c r="V25" s="7">
+        <f>([1]Basic_load!$B$22*[1]Basic_load!G26)*0.85</f>
+        <v>9.089729999999999E-3</v>
+      </c>
+      <c r="W25" s="7">
         <v>0</v>
       </c>
-      <c r="T25" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G26)*0.1</f>
-        <v>1.06938E-3</v>
-      </c>
-      <c r="U25" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G26)*0.1</f>
-        <v>1.06938E-3</v>
-      </c>
-      <c r="V25" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G26)*0.1</f>
-        <v>1.06938E-3</v>
-      </c>
-      <c r="W25" s="7">
-        <f>([1]Basic_load!$B$23*[1]Basic_load!G26)*0.1</f>
-        <v>1.06938E-3</v>
-      </c>
       <c r="X25" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G26)*0.1</f>
-        <v>1.06938E-3</v>
+        <f>([1]Basic_load!$B$24*[1]Basic_load!G26)*0.85</f>
+        <v>9.089729999999999E-3</v>
       </c>
       <c r="Y25" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G26)*0.1</f>
-        <v>4.9904399999999996E-3</v>
+        <f>([1]Basic_load!$B$25*[1]Basic_load!G26)*0.85</f>
+        <v>4.2418739999999996E-2</v>
       </c>
       <c r="Z25" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G26)*0.1</f>
-        <v>4.9904399999999996E-3</v>
+        <f>([1]Basic_load!$B$26*[1]Basic_load!G26)*0.85</f>
+        <v>4.2418739999999996E-2</v>
       </c>
       <c r="AA25" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G26)*0.1</f>
-        <v>7.1292000000000003E-4</v>
+        <f>([1]Basic_load!$B$27*[1]Basic_load!G26)*0.85</f>
+        <v>6.0598199999999996E-3</v>
       </c>
       <c r="AB25" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G26)*0.1</f>
-        <v>7.1292000000000003E-4</v>
+        <f>([1]Basic_load!$B$28*[1]Basic_load!G26)*0.85</f>
+        <v>6.0598199999999996E-3</v>
       </c>
       <c r="AC25" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G26)*0.1</f>
-        <v>7.1292000000000003E-4</v>
+        <f>([1]Basic_load!$B$29*[1]Basic_load!G26)*0.85</f>
+        <v>6.0598199999999996E-3</v>
       </c>
       <c r="AD25" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G26)*0.1</f>
-        <v>1.4258400000000001E-3</v>
+        <f>([1]Basic_load!$B$30*[1]Basic_load!G26)*0.85</f>
+        <v>1.2119639999999999E-2</v>
       </c>
       <c r="AE25" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G26)*0.1</f>
-        <v>2.3764000000000003E-3</v>
+        <f>([1]Basic_load!$B$31*[1]Basic_load!G26)*0.85</f>
+        <v>2.0199399999999999E-2</v>
       </c>
       <c r="AF25" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G26)*0.1</f>
-        <v>1.7822999999999999E-3</v>
+        <f>([1]Basic_load!$B$32*[1]Basic_load!G26)*0.85</f>
+        <v>1.5149549999999998E-2</v>
       </c>
       <c r="AG25" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G26)*0.1</f>
-        <v>2.4952199999999998E-3</v>
+        <f>([1]Basic_load!$B$33*[1]Basic_load!G26)*0.85</f>
+        <v>2.1209369999999998E-2</v>
       </c>
       <c r="AH25" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G26)*0.1</f>
-        <v>7.1292000000000003E-4</v>
+        <f>([1]Basic_load!$B$34*[1]Basic_load!G26)*0.85</f>
+        <v>6.0598199999999996E-3</v>
       </c>
     </row>
     <row r="26" spans="1:34" x14ac:dyDescent="0.3">
       <c r="S26" s="8"/>
     </row>
     <row r="27" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="S27" s="8"/>
+      <c r="S27" s="8">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="28" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="C28" s="7">
+        <f>SUM(B2:AH2)</f>
+        <v>0.47601400000000005</v>
+      </c>
+      <c r="G28" s="7">
+        <v>0.85</v>
+      </c>
       <c r="S28" s="8"/>
+    </row>
+    <row r="29" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="C29" s="7">
+        <f>SUM(B3:AH3)</f>
+        <v>0.47601400000000005</v>
+      </c>
+      <c r="Y29" s="7">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="30" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="C30" s="7">
+        <f>SUM(B4:AH4)</f>
+        <v>0.47601400000000005</v>
+      </c>
+      <c r="Z30" s="7">
+        <v>18</v>
+      </c>
+      <c r="AA30" s="7">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="C31" s="7">
+        <f>SUM(B5:AH5)</f>
+        <v>0.48281400000000008</v>
+      </c>
+      <c r="Z31" s="8">
+        <v>0.441</v>
+      </c>
+      <c r="AA31" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="C32" s="7">
+        <f>SUM(B6:AH6)</f>
+        <v>0.63986399999999988</v>
+      </c>
+      <c r="Z32" s="8">
+        <v>0.441</v>
+      </c>
+      <c r="AA32" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="3:27" x14ac:dyDescent="0.3">
+      <c r="C33" s="7">
+        <f>SUM(B7:AH7)</f>
+        <v>0.72656399999999988</v>
+      </c>
+      <c r="Z33" s="8">
+        <v>0.441</v>
+      </c>
+      <c r="AA33" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="3:27" x14ac:dyDescent="0.3">
+      <c r="C34" s="7">
+        <f>SUM(B8:AH8)</f>
+        <v>0.81411399999999989</v>
+      </c>
+      <c r="Z34" s="8">
+        <v>0.441</v>
+      </c>
+      <c r="AA34" s="7">
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="3:27" x14ac:dyDescent="0.3">
+      <c r="C35" s="7">
+        <f>SUM(B9:AH9)</f>
+        <v>2.1036970292500001</v>
+      </c>
+      <c r="Z35" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="7">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="3:27" x14ac:dyDescent="0.3">
+      <c r="C36" s="7">
+        <f>SUM(B10:AH10)</f>
+        <v>3.6855196082499999</v>
+      </c>
+      <c r="Z36" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="7">
+        <v>0.17699999999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="3:27" x14ac:dyDescent="0.3">
+      <c r="C37" s="7">
+        <f>SUM(B11:AH11)</f>
+        <v>5.0920813375000025</v>
+      </c>
+      <c r="Z37" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="7">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="38" spans="3:27" x14ac:dyDescent="0.3">
+      <c r="C38" s="7">
+        <f>SUM(B12:AH12)</f>
+        <v>7.4582971000000011</v>
+      </c>
+      <c r="Z38" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="7">
+        <v>0.38600000000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="3:27" x14ac:dyDescent="0.3">
+      <c r="C39" s="7">
+        <f>SUM(B13:AH13)</f>
+        <v>1.2826433499999996</v>
+      </c>
+      <c r="Z39" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="7">
+        <v>0.47499999999999998</v>
+      </c>
+    </row>
+    <row r="40" spans="3:27" x14ac:dyDescent="0.3">
+      <c r="C40" s="7">
+        <f>SUM(B14:AH14)</f>
+        <v>1.0203896625</v>
+      </c>
+      <c r="Z40" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA40" s="7">
+        <v>0.52600000000000002</v>
+      </c>
+    </row>
+    <row r="41" spans="3:27" x14ac:dyDescent="0.3">
+      <c r="C41" s="7">
+        <f>SUM(B15:AH15)</f>
+        <v>0.94076399999999982</v>
+      </c>
+      <c r="Z41" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="7">
+        <v>0.53100000000000003</v>
+      </c>
+    </row>
+    <row r="42" spans="3:27" x14ac:dyDescent="0.3">
+      <c r="C42" s="7">
+        <f>SUM(B16:AH16)</f>
+        <v>0.88381399999999977</v>
+      </c>
+      <c r="Z42" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="7">
+        <v>0.52400000000000002</v>
+      </c>
+    </row>
+    <row r="43" spans="3:27" x14ac:dyDescent="0.3">
+      <c r="C43" s="7">
+        <f>SUM(B17:AH17)</f>
+        <v>0.82710050824999992</v>
+      </c>
+      <c r="Z43" s="8">
+        <v>0.58399999999999996</v>
+      </c>
+      <c r="AA43" s="7">
+        <v>0.48699999999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="3:27" x14ac:dyDescent="0.3">
+      <c r="C44" s="7">
+        <f>SUM(B18:AH18)</f>
+        <v>1.7234262124999999</v>
+      </c>
+      <c r="Z44" s="8">
+        <v>0.58399999999999996</v>
+      </c>
+      <c r="AA44" s="7">
+        <v>0.42899999999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="3:27" x14ac:dyDescent="0.3">
+      <c r="C45" s="7">
+        <f>SUM(B19:AH19)</f>
+        <v>2.9990951582499985</v>
+      </c>
+      <c r="Z45" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="7">
+        <v>0.36199999999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="3:27" x14ac:dyDescent="0.3">
+      <c r="C46" s="7">
+        <f>SUM(B20:AH20)</f>
+        <v>2.4540900417499998</v>
+      </c>
+      <c r="Z46" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="7">
+        <v>0.26300000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="3:27" x14ac:dyDescent="0.3">
+      <c r="C47" s="7">
+        <f>SUM(B21:AH21)</f>
+        <v>2.08541677925</v>
+      </c>
+      <c r="Z47" s="8">
+        <v>0.47599999999999998</v>
+      </c>
+      <c r="AA47" s="7">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="48" spans="3:27" x14ac:dyDescent="0.3">
+      <c r="C48" s="7">
+        <f>SUM(B22:AH22)</f>
+        <v>1.7724499667500004</v>
+      </c>
+      <c r="Z48" s="8">
+        <v>0.47599999999999998</v>
+      </c>
+      <c r="AA48" s="7">
+        <v>6.5000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.3">
+      <c r="C49" s="7">
+        <f>SUM(B23:AH23)</f>
+        <v>2.03244194575</v>
+      </c>
+      <c r="Z49" s="8">
+        <v>0.47599999999999998</v>
+      </c>
+      <c r="AA49" s="7">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.3">
+      <c r="C50" s="7">
+        <f>SUM(B24:AH24)</f>
+        <v>2.4538162792499998</v>
+      </c>
+      <c r="Z50" s="8">
+        <v>0.47599999999999998</v>
+      </c>
+      <c r="AA50" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.3">
+      <c r="C51" s="7">
+        <f>SUM(B25:AH25)</f>
+        <v>0.66370445500000008</v>
+      </c>
+      <c r="Z51" s="8">
+        <v>0.47599999999999998</v>
+      </c>
+      <c r="AA51" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.3">
+      <c r="Z52" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.3">
+      <c r="Z53" s="8">
+        <v>0.441</v>
+      </c>
+      <c r="AA53" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.3">
+      <c r="Z54" s="8">
+        <v>0.441</v>
+      </c>
+      <c r="AA54" s="7">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -4778,13 +5795,13 @@
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2">
+      <c r="A2" s="8">
         <v>1</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="8">
         <v>1</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="8">
         <v>2</v>
       </c>
       <c r="D2" s="8">
@@ -4794,7 +5811,7 @@
         <v>4.7699999999999999E-2</v>
       </c>
       <c r="F2" s="8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J2" s="12"/>
       <c r="K2" s="12"/>
@@ -4803,13 +5820,13 @@
       <c r="N2" s="12"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="A3" s="8">
         <v>2</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="8">
         <v>2</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="8">
         <v>3</v>
       </c>
       <c r="D3" s="8">
@@ -4819,7 +5836,7 @@
         <v>0.25109999999999999</v>
       </c>
       <c r="F3" s="8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J3" s="8"/>
       <c r="K3" s="8"/>
@@ -4828,13 +5845,13 @@
       <c r="N3" s="8"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4">
+      <c r="A4" s="8">
         <v>3</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="8">
         <v>3</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="8">
         <v>4</v>
       </c>
       <c r="D4" s="8">
@@ -4844,7 +5861,7 @@
         <v>0.18640000000000001</v>
       </c>
       <c r="F4" s="8">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="J4" s="8"/>
       <c r="K4" s="8"/>
@@ -4854,13 +5871,13 @@
       <c r="P4" s="8"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5">
+      <c r="A5" s="8">
         <v>4</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="8">
         <v>4</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="8">
         <v>5</v>
       </c>
       <c r="D5" s="8">
@@ -4870,7 +5887,7 @@
         <v>0.19409999999999999</v>
       </c>
       <c r="F5" s="8">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="J5" s="8"/>
       <c r="K5" s="8"/>
@@ -4880,13 +5897,13 @@
       <c r="O5" s="5"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6">
+      <c r="A6" s="8">
         <v>5</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="8">
         <v>5</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="8">
         <v>6</v>
       </c>
       <c r="D6" s="8">
@@ -4896,7 +5913,7 @@
         <v>0.70699999999999996</v>
       </c>
       <c r="F6" s="8">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="J6" s="8"/>
       <c r="K6" s="8"/>
@@ -4906,13 +5923,13 @@
       <c r="O6" s="5"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A7">
+      <c r="A7" s="8">
         <v>6</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="8">
         <v>6</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="8">
         <v>7</v>
       </c>
       <c r="D7" s="8">
@@ -4922,7 +5939,7 @@
         <v>0.61880000000000002</v>
       </c>
       <c r="F7" s="8">
-        <v>1.2</v>
+        <v>6</v>
       </c>
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
@@ -4932,14 +5949,13 @@
       <c r="O7" s="5"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <f>A7+1</f>
+      <c r="A8" s="8">
         <v>7</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="8">
         <v>7</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="8">
         <v>8</v>
       </c>
       <c r="D8" s="8">
@@ -4949,7 +5965,7 @@
         <v>0.2351</v>
       </c>
       <c r="F8" s="8">
-        <v>1.2</v>
+        <v>6</v>
       </c>
       <c r="J8" s="8"/>
       <c r="K8" s="8"/>
@@ -4959,14 +5975,13 @@
       <c r="O8" s="5"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A9" s="7">
-        <f t="shared" ref="A9:A33" si="0">A8+1</f>
+      <c r="A9" s="8">
         <v>8</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="8">
         <v>8</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="8">
         <v>9</v>
       </c>
       <c r="D9" s="8">
@@ -4976,7 +5991,7 @@
         <v>0.74</v>
       </c>
       <c r="F9" s="8">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J9" s="8"/>
       <c r="K9" s="8"/>
@@ -4986,14 +6001,13 @@
       <c r="O9" s="5"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A10" s="7">
-        <f t="shared" si="0"/>
+      <c r="A10" s="8">
         <v>9</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="8">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="8">
         <v>10</v>
       </c>
       <c r="D10" s="8">
@@ -5003,7 +6017,7 @@
         <v>0.74</v>
       </c>
       <c r="F10" s="8">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J10" s="8"/>
       <c r="K10" s="8"/>
@@ -5013,14 +6027,13 @@
       <c r="O10" s="5"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A11" s="7">
-        <f t="shared" si="0"/>
+      <c r="A11" s="8">
         <v>10</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="8">
         <v>10</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="8">
         <v>11</v>
       </c>
       <c r="D11" s="8">
@@ -5030,7 +6043,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="F11" s="8">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J11" s="8"/>
       <c r="K11" s="8"/>
@@ -5040,14 +6053,13 @@
       <c r="O11" s="5"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A12" s="7">
-        <f t="shared" si="0"/>
+      <c r="A12" s="8">
         <v>11</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="8">
         <v>11</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="8">
         <v>12</v>
       </c>
       <c r="D12" s="8">
@@ -5057,7 +6069,7 @@
         <v>0.12379999999999999</v>
       </c>
       <c r="F12" s="8">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J12" s="8"/>
       <c r="K12" s="8"/>
@@ -5067,14 +6079,13 @@
       <c r="O12" s="5"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A13" s="7">
-        <f t="shared" si="0"/>
+      <c r="A13" s="8">
         <v>12</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="8">
         <v>12</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="8">
         <v>13</v>
       </c>
       <c r="D13" s="8">
@@ -5084,7 +6095,7 @@
         <v>1.155</v>
       </c>
       <c r="F13" s="8">
-        <v>0.8</v>
+        <v>6</v>
       </c>
       <c r="J13" s="8"/>
       <c r="K13" s="8"/>
@@ -5094,14 +6105,13 @@
       <c r="O13" s="5"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A14" s="7">
-        <f t="shared" si="0"/>
+      <c r="A14" s="8">
         <v>13</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="8">
         <v>13</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="8">
         <v>14</v>
       </c>
       <c r="D14" s="8">
@@ -5111,7 +6121,7 @@
         <v>0.71289999999999998</v>
       </c>
       <c r="F14" s="8">
-        <v>0.8</v>
+        <v>6</v>
       </c>
       <c r="J14" s="8"/>
       <c r="K14" s="8"/>
@@ -5121,14 +6131,13 @@
       <c r="O14" s="5"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A15" s="7">
-        <f t="shared" si="0"/>
+      <c r="A15" s="8">
         <v>14</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="8">
         <v>14</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="8">
         <v>15</v>
       </c>
       <c r="D15" s="8">
@@ -5138,7 +6147,7 @@
         <v>0.52600000000000002</v>
       </c>
       <c r="F15" s="8">
-        <v>0.8</v>
+        <v>6</v>
       </c>
       <c r="J15" s="8"/>
       <c r="K15" s="8"/>
@@ -5148,14 +6157,13 @@
       <c r="O15" s="5"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A16" s="7">
-        <f t="shared" si="0"/>
+      <c r="A16" s="8">
         <v>15</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="8">
         <v>15</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="8">
         <v>16</v>
       </c>
       <c r="D16" s="8">
@@ -5165,7 +6173,7 @@
         <v>0.54500000000000004</v>
       </c>
       <c r="F16" s="8">
-        <v>0.8</v>
+        <v>6</v>
       </c>
       <c r="J16" s="8"/>
       <c r="K16" s="8"/>
@@ -5175,14 +6183,13 @@
       <c r="O16" s="5"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="7">
-        <f t="shared" si="0"/>
+      <c r="A17" s="8">
         <v>16</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="8">
         <v>16</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="8">
         <v>17</v>
       </c>
       <c r="D17" s="8">
@@ -5192,7 +6199,7 @@
         <v>1.7210000000000001</v>
       </c>
       <c r="F17" s="8">
-        <v>0.8</v>
+        <v>6</v>
       </c>
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
@@ -5202,14 +6209,13 @@
       <c r="O17" s="5"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" s="7">
-        <f t="shared" si="0"/>
+      <c r="A18" s="8">
         <v>17</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="8">
         <v>17</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="8">
         <v>18</v>
       </c>
       <c r="D18" s="8">
@@ -5219,7 +6225,7 @@
         <v>0.57399999999999995</v>
       </c>
       <c r="F18" s="8">
-        <v>0.8</v>
+        <v>6</v>
       </c>
       <c r="J18" s="8"/>
       <c r="K18" s="8"/>
@@ -5229,14 +6235,13 @@
       <c r="O18" s="5"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" s="7">
-        <f t="shared" si="0"/>
+      <c r="A19" s="8">
         <v>18</v>
       </c>
-      <c r="B19" s="6">
-        <v>2</v>
-      </c>
-      <c r="C19" s="6">
+      <c r="B19" s="8">
+        <v>18</v>
+      </c>
+      <c r="C19" s="8">
         <v>19</v>
       </c>
       <c r="D19" s="8">
@@ -5246,7 +6251,7 @@
         <v>0.1565</v>
       </c>
       <c r="F19" s="8">
-        <v>1.2</v>
+        <v>6</v>
       </c>
       <c r="J19" s="8"/>
       <c r="K19" s="8"/>
@@ -5256,14 +6261,13 @@
       <c r="O19" s="5"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20" s="7">
-        <f t="shared" si="0"/>
+      <c r="A20" s="8">
         <v>19</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20" s="8">
         <v>19</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="8">
         <v>20</v>
       </c>
       <c r="D20" s="8">
@@ -5273,7 +6277,7 @@
         <v>1.3553999999999999</v>
       </c>
       <c r="F20" s="8">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J20" s="8"/>
       <c r="K20" s="8"/>
@@ -5283,14 +6287,13 @@
       <c r="O20" s="5"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" s="7">
-        <f t="shared" si="0"/>
+      <c r="A21" s="8">
         <v>20</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21" s="8">
         <v>20</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="8">
         <v>21</v>
       </c>
       <c r="D21" s="8">
@@ -5300,7 +6303,7 @@
         <v>0.47839999999999999</v>
       </c>
       <c r="F21" s="8">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J21" s="8"/>
       <c r="K21" s="8"/>
@@ -5310,14 +6313,13 @@
       <c r="O21" s="5"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A22" s="7">
-        <f t="shared" si="0"/>
+      <c r="A22" s="8">
         <v>21</v>
       </c>
-      <c r="B22" s="6">
+      <c r="B22" s="8">
         <v>21</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="8">
         <v>22</v>
       </c>
       <c r="D22" s="8">
@@ -5327,7 +6329,7 @@
         <v>0.93730000000000002</v>
       </c>
       <c r="F22" s="8">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J22" s="8"/>
       <c r="K22" s="8"/>
@@ -5337,14 +6339,13 @@
       <c r="O22" s="5"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A23" s="7">
-        <f t="shared" si="0"/>
+      <c r="A23" s="8">
         <v>22</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B23" s="8">
         <v>3</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="8">
         <v>23</v>
       </c>
       <c r="D23" s="8">
@@ -5354,7 +6355,7 @@
         <v>0.30830000000000002</v>
       </c>
       <c r="F23" s="8">
-        <v>1.2</v>
+        <v>6</v>
       </c>
       <c r="J23" s="8"/>
       <c r="K23" s="8"/>
@@ -5364,14 +6365,13 @@
       <c r="O23" s="6"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A24" s="7">
-        <f t="shared" si="0"/>
+      <c r="A24" s="8">
         <v>23</v>
       </c>
-      <c r="B24" s="6">
+      <c r="B24" s="8">
         <v>23</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24" s="8">
         <v>24</v>
       </c>
       <c r="D24" s="8">
@@ -5381,7 +6381,7 @@
         <v>0.70909999999999995</v>
       </c>
       <c r="F24" s="8">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J24" s="8"/>
       <c r="K24" s="8"/>
@@ -5391,14 +6391,13 @@
       <c r="O24" s="6"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25" s="7">
-        <f t="shared" si="0"/>
+      <c r="A25" s="8">
         <v>24</v>
       </c>
-      <c r="B25" s="6">
+      <c r="B25" s="8">
         <v>24</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="8">
         <v>25</v>
       </c>
       <c r="D25" s="8">
@@ -5408,7 +6407,7 @@
         <v>0.70109999999999995</v>
       </c>
       <c r="F25" s="8">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J25" s="8"/>
       <c r="K25" s="8"/>
@@ -5418,14 +6417,13 @@
       <c r="O25" s="6"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A26" s="7">
-        <f t="shared" si="0"/>
+      <c r="A26" s="8">
         <v>25</v>
       </c>
-      <c r="B26" s="6">
+      <c r="B26" s="8">
         <v>6</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="8">
         <v>26</v>
       </c>
       <c r="D26" s="8">
@@ -5435,7 +6433,7 @@
         <v>0.10340000000000001</v>
       </c>
       <c r="F26" s="8">
-        <v>0.8</v>
+        <v>6</v>
       </c>
       <c r="H26" s="8"/>
       <c r="J26" s="8"/>
@@ -5446,14 +6444,13 @@
       <c r="O26" s="6"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A27" s="7">
-        <f t="shared" si="0"/>
+      <c r="A27" s="8">
         <v>26</v>
       </c>
-      <c r="B27" s="6">
+      <c r="B27" s="8">
         <v>26</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="8">
         <v>27</v>
       </c>
       <c r="D27" s="8">
@@ -5463,7 +6460,7 @@
         <v>0.1447</v>
       </c>
       <c r="F27" s="8">
-        <v>0.8</v>
+        <v>6</v>
       </c>
       <c r="J27" s="8"/>
       <c r="K27" s="8"/>
@@ -5473,14 +6470,13 @@
       <c r="O27" s="6"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A28" s="7">
-        <f t="shared" si="0"/>
+      <c r="A28" s="8">
         <v>27</v>
       </c>
-      <c r="B28" s="6">
+      <c r="B28" s="8">
         <v>27</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28" s="8">
         <v>28</v>
       </c>
       <c r="D28" s="8">
@@ -5490,7 +6486,7 @@
         <v>0.93369999999999997</v>
       </c>
       <c r="F28" s="8">
-        <v>0.6</v>
+        <v>6</v>
       </c>
       <c r="J28" s="8"/>
       <c r="K28" s="8"/>
@@ -5500,14 +6496,13 @@
       <c r="O28" s="6"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A29" s="7">
-        <f t="shared" si="0"/>
+      <c r="A29" s="8">
         <v>28</v>
       </c>
-      <c r="B29" s="6">
+      <c r="B29" s="8">
         <v>28</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="8">
         <v>29</v>
       </c>
       <c r="D29" s="8">
@@ -5517,7 +6512,7 @@
         <v>0.7006</v>
       </c>
       <c r="F29" s="8">
-        <v>0.6</v>
+        <v>6</v>
       </c>
       <c r="J29" s="8"/>
       <c r="K29" s="8"/>
@@ -5527,14 +6522,13 @@
       <c r="O29" s="6"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A30" s="7">
-        <f t="shared" si="0"/>
+      <c r="A30" s="8">
         <v>29</v>
       </c>
-      <c r="B30" s="6">
+      <c r="B30" s="8">
         <v>29</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C30" s="8">
         <v>30</v>
       </c>
       <c r="D30" s="8">
@@ -5544,7 +6538,7 @@
         <v>0.25850000000000001</v>
       </c>
       <c r="F30" s="8">
-        <v>0.6</v>
+        <v>6</v>
       </c>
       <c r="J30" s="8"/>
       <c r="K30" s="8"/>
@@ -5554,14 +6548,13 @@
       <c r="O30" s="6"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A31" s="7">
-        <f t="shared" si="0"/>
+      <c r="A31" s="8">
         <v>30</v>
       </c>
-      <c r="B31" s="6">
+      <c r="B31" s="8">
         <v>30</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31" s="8">
         <v>31</v>
       </c>
       <c r="D31" s="8">
@@ -5571,7 +6564,7 @@
         <v>0.96299999999999997</v>
       </c>
       <c r="F31" s="8">
-        <v>0.6</v>
+        <v>6</v>
       </c>
       <c r="J31" s="8"/>
       <c r="K31" s="8"/>
@@ -5581,14 +6574,13 @@
       <c r="O31" s="6"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A32" s="7">
-        <f t="shared" si="0"/>
+      <c r="A32" s="8">
         <v>31</v>
       </c>
-      <c r="B32" s="6">
+      <c r="B32" s="8">
         <v>31</v>
       </c>
-      <c r="C32" s="6">
+      <c r="C32" s="8">
         <v>32</v>
       </c>
       <c r="D32" s="8">
@@ -5598,7 +6590,7 @@
         <v>0.3619</v>
       </c>
       <c r="F32" s="8">
-        <v>0.6</v>
+        <v>6</v>
       </c>
       <c r="J32" s="8"/>
       <c r="K32" s="8"/>
@@ -5608,14 +6600,13 @@
       <c r="O32" s="6"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A33" s="7">
-        <f t="shared" si="0"/>
+      <c r="A33" s="8">
         <v>32</v>
       </c>
-      <c r="B33" s="6">
+      <c r="B33" s="8">
         <v>32</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="8">
         <v>33</v>
       </c>
       <c r="D33" s="8">
@@ -5625,7 +6616,7 @@
         <v>0.5302</v>
       </c>
       <c r="F33" s="8">
-        <v>0.6</v>
+        <v>6</v>
       </c>
       <c r="J33" s="8"/>
       <c r="K33" s="8"/>

--- a/Inputs/Time_Series.xlsx
+++ b/Inputs/Time_Series.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="3"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
   </bookViews>
   <sheets>
     <sheet name="load_profile" sheetId="1" r:id="rId1"/>
@@ -14,9 +14,6 @@
     <sheet name="slack_bus" sheetId="5" r:id="rId5"/>
     <sheet name="fleet_bus" sheetId="6" r:id="rId6"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId7"/>
-  </externalReferences>
   <calcPr calcId="145621"/>
 </workbook>
 </file>
@@ -122,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -142,6 +139,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -176,99 +174,6 @@
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:marker val="1"/>
-        <c:smooth val="0"/>
-        <c:axId val="151182336"/>
-        <c:axId val="151831296"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="151182336"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="151831296"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="151831296"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="151182336"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:layout/>
-      <c:overlay val="0"/>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="6.5113517060367457E-2"/>
-          <c:y val="7.4548702245552642E-2"/>
-          <c:w val="0.70903871391076112"/>
-          <c:h val="0.8326195683872849"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -277,81 +182,81 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>load_profile!$C$28:$C$51</c:f>
+              <c:f>load_profile!$A$28:$A$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
-                  <c:v>0.47601400000000005</c:v>
+                  <c:v>6.4599968265141319E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.47601400000000005</c:v>
+                  <c:v>9.9399951169582765E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.47601400000000005</c:v>
+                  <c:v>0.15349992459286682</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.48281400000000008</c:v>
+                  <c:v>0.27443286518432708</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.63986399999999988</c:v>
+                  <c:v>0.13006693610436743</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.72656399999999988</c:v>
+                  <c:v>7.0799965219380881E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.81411399999999989</c:v>
+                  <c:v>0.18533290895485199</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.1036970292500001</c:v>
+                  <c:v>1.3912823165298855</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.6855196082499999</c:v>
+                  <c:v>0.65203267968769163</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5.0920813375000025</c:v>
+                  <c:v>0.63463268823547114</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>7.4582971000000011</c:v>
+                  <c:v>0.58276671371473088</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.2826433499999996</c:v>
+                  <c:v>0.33769983410430698</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.0203896625</c:v>
+                  <c:v>9.3199954215343203E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.94076399999999982</c:v>
+                  <c:v>0.10719994733781968</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.88381399999999977</c:v>
+                  <c:v>0.1097999460605653</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.82710050824999992</c:v>
+                  <c:v>0.21759989310363387</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.7234262124999999</c:v>
+                  <c:v>0.44901677941964313</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2.9990951582499985</c:v>
+                  <c:v>1.0476994853156123</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2.4540900417499998</c:v>
+                  <c:v>1.1567324317529679</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2.08541677925</c:v>
+                  <c:v>0.65523267811568653</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.7724499667500004</c:v>
+                  <c:v>0.57831671590080069</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>2.03244194575</c:v>
+                  <c:v>0.54359973295558539</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>2.4538162792499998</c:v>
+                  <c:v>0.46329977240309561</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.66370445500000008</c:v>
+                  <c:v>0.22523288935390981</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -368,11 +273,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="152183552"/>
-        <c:axId val="152185088"/>
+        <c:axId val="145281792"/>
+        <c:axId val="145284096"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="152183552"/>
+        <c:axId val="145281792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -381,7 +286,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="152185088"/>
+        <c:crossAx val="145284096"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -389,7 +294,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="152185088"/>
+        <c:axId val="145284096"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -400,353 +305,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="152183552"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:layout/>
-      <c:overlay val="0"/>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:val>
-            <c:numRef>
-              <c:f>load_profile!$W$2:$W$25</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6.7999999999999996E-3</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>6.3750000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.15045</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.23800000000000002</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.3281</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.40375</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.4471</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.45135000000000003</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.44540000000000002</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.41394999999999998</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.36464999999999997</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.30769999999999997</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.22355</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.12834999999999999</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>5.525E-2</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>8.5000000000000006E-3</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:marker val="1"/>
-        <c:smooth val="0"/>
-        <c:axId val="152205184"/>
-        <c:axId val="152206720"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="152205184"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="152206720"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="152206720"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="152205184"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:layout/>
-      <c:overlay val="0"/>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:val>
-            <c:numRef>
-              <c:f>load_profile!$S$2:$S$25</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
-                <c:pt idx="0">
-                  <c:v>0.30869999999999997</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.30869999999999997</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.30869999999999997</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.30869999999999997</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.40879999999999994</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.40879999999999994</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.40879999999999994</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.40879999999999994</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.40879999999999994</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.40879999999999994</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.40879999999999994</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.40879999999999994</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.40879999999999994</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.40879999999999994</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.40879999999999994</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.40879999999999994</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.33319999999999994</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.33319999999999994</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.33319999999999994</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.33319999999999994</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.33319999999999994</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.40879999999999994</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.40879999999999994</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.30869999999999997</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:marker val="1"/>
-        <c:smooth val="0"/>
-        <c:axId val="152239104"/>
-        <c:axId val="152371968"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="152239104"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="152371968"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="152371968"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="152239104"/>
+        <c:crossAx val="145281792"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -772,20 +331,20 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>17929</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>94129</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>784860</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>466165</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>147918</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvPr id="6" name="Chart 5"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -800,346 +359,7 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>358140</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>160020</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>815340</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>160020</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>53340</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>617220</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>53340</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>617220</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>160020</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>502920</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>160020</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Chart 4"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="ActiveLoad"/>
-      <sheetName val="ReactiveLoad"/>
-      <sheetName val="Basic_load"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2">
-        <row r="2">
-          <cell r="B2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>0.1</v>
-          </cell>
-          <cell r="G3">
-            <v>5.6000000000000001E-2</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="B4">
-            <v>0.09</v>
-          </cell>
-          <cell r="G4">
-            <v>5.6000000000000001E-2</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="B5">
-            <v>0.1</v>
-          </cell>
-          <cell r="G5">
-            <v>5.6000000000000001E-2</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="B6">
-            <v>0.06</v>
-          </cell>
-          <cell r="G6">
-            <v>5.6000000000000001E-2</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="B7">
-            <v>0.06</v>
-          </cell>
-          <cell r="G7">
-            <v>5.6000000000000001E-2</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="B8">
-            <v>0.2</v>
-          </cell>
-          <cell r="G8">
-            <v>5.6000000000000001E-2</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="B9">
-            <v>0.2</v>
-          </cell>
-          <cell r="G9">
-            <v>5.6000000000000001E-2</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="B10">
-            <v>0.06</v>
-          </cell>
-          <cell r="G10">
-            <v>0.45746700000000001</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="B11">
-            <v>0.06</v>
-          </cell>
-          <cell r="G11">
-            <v>0.96158299999999997</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="B12">
-            <v>4.4999999999999998E-2</v>
-          </cell>
-          <cell r="G12">
-            <v>1.4178500000000001</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="B13">
-            <v>0.06</v>
-          </cell>
-          <cell r="G13">
-            <v>2.2084000000000001</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="B14">
-            <v>0.06</v>
-          </cell>
-          <cell r="G14">
-            <v>0.1434</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="B15">
-            <v>0.12</v>
-          </cell>
-          <cell r="G15">
-            <v>6.615E-2</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="B16">
-            <v>0.06</v>
-          </cell>
-          <cell r="G16">
-            <v>5.6000000000000001E-2</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="B17">
-            <v>0.06</v>
-          </cell>
-          <cell r="G17">
-            <v>5.6000000000000001E-2</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="B18">
-            <v>0.06</v>
-          </cell>
-          <cell r="G18">
-            <v>6.5183000000000005E-2</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="G19">
-            <v>0.42235</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="B20">
-            <v>0.09</v>
-          </cell>
-          <cell r="G20">
-            <v>0.87378299999999998</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="B21">
-            <v>0.09</v>
-          </cell>
-          <cell r="G21">
-            <v>0.70701700000000001</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="B22">
-            <v>0.09</v>
-          </cell>
-          <cell r="G22">
-            <v>0.58646699999999996</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="G23">
-            <v>0.48171700000000001</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="B24">
-            <v>0.09</v>
-          </cell>
-          <cell r="G24">
-            <v>0.54343300000000005</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="B25">
-            <v>0.42</v>
-          </cell>
-          <cell r="G25">
-            <v>0.68446700000000005</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="B26">
-            <v>0.42</v>
-          </cell>
-          <cell r="G26">
-            <v>0.11882</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="B27">
-            <v>0.06</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="B28">
-            <v>0.06</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="B29">
-            <v>0.06</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="B30">
-            <v>0.12</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="B31">
-            <v>0.2</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="B32">
-            <v>0.15</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="B33">
-            <v>0.21</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="B34">
-            <v>0.06</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1549,134 +769,103 @@
         <v>0</v>
       </c>
       <c r="B2" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G3)*0.85</f>
         <v>0</v>
       </c>
       <c r="C2" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G3)*0.85</f>
-        <v>4.7600000000000003E-3</v>
+        <v>1.7389028000000001E-3</v>
       </c>
       <c r="D2" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G3)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>1.5649996000000003E-3</v>
       </c>
       <c r="E2" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G3)*0.85</f>
-        <v>4.7600000000000003E-3</v>
+        <v>2.0866446000000006E-3</v>
       </c>
       <c r="F2" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G3)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.0433378196500673E-3</v>
       </c>
       <c r="G2" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G3)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.0433378196500673E-3</v>
       </c>
       <c r="H2" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G3)*0.85</f>
-        <v>9.5200000000000007E-3</v>
+        <v>3.4777927321668913E-3</v>
       </c>
       <c r="I2" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G3)*0.85</f>
-        <v>9.5200000000000007E-3</v>
+        <v>3.4777927321668913E-3</v>
       </c>
       <c r="J2" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G3)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.0433378196500673E-3</v>
       </c>
       <c r="K2" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G3)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.0433378196500673E-3</v>
       </c>
       <c r="L2" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G3)*0.85</f>
-        <v>2.1420000000000002E-3</v>
+        <v>7.8250336473755053E-4</v>
       </c>
       <c r="M2" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G3)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.0433378196500673E-3</v>
       </c>
       <c r="N2" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G3)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.0433378196500673E-3</v>
       </c>
       <c r="O2" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G3)*0.85</f>
-        <v>5.7120000000000001E-3</v>
+        <v>2.0866756393001346E-3</v>
       </c>
       <c r="P2" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G3)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.0433378196500673E-3</v>
       </c>
       <c r="Q2" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G3)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.0433378196500673E-3</v>
       </c>
       <c r="R2" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G3)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.0433378196500673E-3</v>
       </c>
       <c r="S2" s="8">
-        <v>0.30869999999999997</v>
+        <v>1.5650067294751011E-3</v>
       </c>
       <c r="T2" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G3)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>1.5650067294751011E-3</v>
       </c>
       <c r="U2" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G3)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>1.5650067294751011E-3</v>
       </c>
       <c r="V2" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G3)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>1.5650067294751011E-3</v>
       </c>
       <c r="W2" s="7">
-        <v>0</v>
+        <v>1.5650067294751011E-3</v>
       </c>
       <c r="X2" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G3)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>1.5650067294751011E-3</v>
       </c>
       <c r="Y2" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G3)*0.85</f>
-        <v>1.9991999999999999E-2</v>
+        <v>7.3033647375504709E-3</v>
       </c>
       <c r="Z2" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G3)*0.85</f>
-        <v>1.9991999999999999E-2</v>
+        <v>7.3033647375504709E-3</v>
       </c>
       <c r="AA2" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G3)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.0433378196500673E-3</v>
       </c>
       <c r="AB2" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G3)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.0433378196500673E-3</v>
       </c>
       <c r="AC2" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G3)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.0433378196500673E-3</v>
       </c>
       <c r="AD2" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G3)*0.85</f>
-        <v>5.7120000000000001E-3</v>
+        <v>2.0866756393001346E-3</v>
       </c>
       <c r="AE2" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G3)*0.85</f>
-        <v>9.5200000000000007E-3</v>
+        <v>3.4777927321668913E-3</v>
       </c>
       <c r="AF2" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G3)*0.85</f>
-        <v>7.1399999999999996E-3</v>
+        <v>2.6083445491251684E-3</v>
       </c>
       <c r="AG2" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G3)*0.85</f>
-        <v>9.9959999999999997E-3</v>
+        <v>3.6516823687752355E-3</v>
       </c>
       <c r="AH2" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G3)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.0433378196500673E-3</v>
       </c>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.3">
@@ -1684,134 +873,103 @@
         <v>4.1666666666666699E-2</v>
       </c>
       <c r="B3" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G4)*0.85</f>
         <v>0</v>
       </c>
       <c r="C3" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G4)*0.85</f>
-        <v>4.7600000000000003E-3</v>
+        <v>2.6756492000000001E-3</v>
       </c>
       <c r="D3" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G4)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>2.4080644000000003E-3</v>
       </c>
       <c r="E3" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G4)*0.85</f>
-        <v>4.7600000000000003E-3</v>
+        <v>3.2107194000000005E-3</v>
       </c>
       <c r="F3" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G4)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.6053835800807538E-3</v>
       </c>
       <c r="G3" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G4)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.6053835800807538E-3</v>
       </c>
       <c r="H3" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G4)*0.85</f>
-        <v>9.5200000000000007E-3</v>
+        <v>5.3512786002691791E-3</v>
       </c>
       <c r="I3" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G4)*0.85</f>
-        <v>9.5200000000000007E-3</v>
+        <v>5.3512786002691791E-3</v>
       </c>
       <c r="J3" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G4)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.6053835800807538E-3</v>
       </c>
       <c r="K3" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G4)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.6053835800807538E-3</v>
       </c>
       <c r="L3" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G4)*0.85</f>
-        <v>2.1420000000000002E-3</v>
+        <v>1.2040376850605654E-3</v>
       </c>
       <c r="M3" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G4)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.6053835800807538E-3</v>
       </c>
       <c r="N3" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G4)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.6053835800807538E-3</v>
       </c>
       <c r="O3" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G4)*0.85</f>
-        <v>5.7120000000000001E-3</v>
+        <v>3.2107671601615075E-3</v>
       </c>
       <c r="P3" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G4)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.6053835800807538E-3</v>
       </c>
       <c r="Q3" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G4)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.6053835800807538E-3</v>
       </c>
       <c r="R3" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G4)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.6053835800807538E-3</v>
       </c>
       <c r="S3" s="8">
-        <v>0.30869999999999997</v>
+        <v>2.4080753701211308E-3</v>
       </c>
       <c r="T3" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G4)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>2.4080753701211308E-3</v>
       </c>
       <c r="U3" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G4)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>2.4080753701211308E-3</v>
       </c>
       <c r="V3" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G4)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>2.4080753701211308E-3</v>
       </c>
       <c r="W3" s="7">
-        <v>0</v>
+        <v>2.4080753701211308E-3</v>
       </c>
       <c r="X3" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G4)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>2.4080753701211308E-3</v>
       </c>
       <c r="Y3" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G4)*0.85</f>
-        <v>1.9991999999999999E-2</v>
+        <v>1.1237685060565276E-2</v>
       </c>
       <c r="Z3" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G4)*0.85</f>
-        <v>1.9991999999999999E-2</v>
+        <v>1.1237685060565276E-2</v>
       </c>
       <c r="AA3" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G4)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.6053835800807538E-3</v>
       </c>
       <c r="AB3" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G4)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.6053835800807538E-3</v>
       </c>
       <c r="AC3" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G4)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.6053835800807538E-3</v>
       </c>
       <c r="AD3" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G4)*0.85</f>
-        <v>5.7120000000000001E-3</v>
+        <v>3.2107671601615075E-3</v>
       </c>
       <c r="AE3" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G4)*0.85</f>
-        <v>9.5200000000000007E-3</v>
+        <v>5.3512786002691791E-3</v>
       </c>
       <c r="AF3" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G4)*0.85</f>
-        <v>7.1399999999999996E-3</v>
+        <v>4.0134589502018843E-3</v>
       </c>
       <c r="AG3" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G4)*0.85</f>
-        <v>9.9959999999999997E-3</v>
+        <v>5.6188425302826379E-3</v>
       </c>
       <c r="AH3" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G4)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.6053835800807538E-3</v>
       </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.3">
@@ -1819,134 +977,103 @@
         <v>8.3333333333333301E-2</v>
       </c>
       <c r="B4" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G5)*0.85</f>
         <v>0</v>
       </c>
       <c r="C4" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G5)*0.85</f>
-        <v>4.7600000000000003E-3</v>
+        <v>4.1319130000000001E-3</v>
       </c>
       <c r="D4" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G5)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>3.7186910000000001E-3</v>
       </c>
       <c r="E4" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G5)*0.85</f>
-        <v>4.7600000000000003E-3</v>
+        <v>4.9582035000000002E-3</v>
       </c>
       <c r="F4" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G5)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.4791386271870793E-3</v>
       </c>
       <c r="G4" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G5)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.4791386271870793E-3</v>
       </c>
       <c r="H4" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G5)*0.85</f>
-        <v>9.5200000000000007E-3</v>
+        <v>8.2637954239569312E-3</v>
       </c>
       <c r="I4" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G5)*0.85</f>
-        <v>9.5200000000000007E-3</v>
+        <v>8.2637954239569312E-3</v>
       </c>
       <c r="J4" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G5)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.4791386271870793E-3</v>
       </c>
       <c r="K4" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G5)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.4791386271870793E-3</v>
       </c>
       <c r="L4" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G5)*0.85</f>
-        <v>2.1420000000000002E-3</v>
+        <v>1.8593539703903096E-3</v>
       </c>
       <c r="M4" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G5)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.4791386271870793E-3</v>
       </c>
       <c r="N4" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G5)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.4791386271870793E-3</v>
       </c>
       <c r="O4" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G5)*0.85</f>
-        <v>5.7120000000000001E-3</v>
+        <v>4.9582772543741585E-3</v>
       </c>
       <c r="P4" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G5)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.4791386271870793E-3</v>
       </c>
       <c r="Q4" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G5)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.4791386271870793E-3</v>
       </c>
       <c r="R4" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G5)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.4791386271870793E-3</v>
       </c>
       <c r="S4" s="8">
-        <v>0.30869999999999997</v>
+        <v>3.7187079407806191E-3</v>
       </c>
       <c r="T4" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G5)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>3.7187079407806191E-3</v>
       </c>
       <c r="U4" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G5)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>3.7187079407806191E-3</v>
       </c>
       <c r="V4" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G5)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>3.7187079407806191E-3</v>
       </c>
       <c r="W4" s="7">
-        <v>0</v>
+        <v>3.7187079407806191E-3</v>
       </c>
       <c r="X4" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G5)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>3.7187079407806191E-3</v>
       </c>
       <c r="Y4" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G5)*0.85</f>
-        <v>1.9991999999999999E-2</v>
+        <v>1.7353970390309555E-2</v>
       </c>
       <c r="Z4" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G5)*0.85</f>
-        <v>1.9991999999999999E-2</v>
+        <v>1.7353970390309555E-2</v>
       </c>
       <c r="AA4" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G5)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.4791386271870793E-3</v>
       </c>
       <c r="AB4" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G5)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.4791386271870793E-3</v>
       </c>
       <c r="AC4" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G5)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.4791386271870793E-3</v>
       </c>
       <c r="AD4" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G5)*0.85</f>
-        <v>5.7120000000000001E-3</v>
+        <v>4.9582772543741585E-3</v>
       </c>
       <c r="AE4" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G5)*0.85</f>
-        <v>9.5200000000000007E-3</v>
+        <v>8.2637954239569312E-3</v>
       </c>
       <c r="AF4" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G5)*0.85</f>
-        <v>7.1399999999999996E-3</v>
+        <v>6.197846567967698E-3</v>
       </c>
       <c r="AG4" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G5)*0.85</f>
-        <v>9.9959999999999997E-3</v>
+        <v>8.6769851951547777E-3</v>
       </c>
       <c r="AH4" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G5)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.4791386271870793E-3</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.3">
@@ -1954,134 +1081,103 @@
         <v>0.125</v>
       </c>
       <c r="B5" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G6)*0.85</f>
         <v>0</v>
       </c>
       <c r="C5" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G6)*0.85</f>
-        <v>4.7600000000000003E-3</v>
+        <v>7.3871874939999997E-3</v>
       </c>
       <c r="D5" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G6)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>6.6484138579999998E-3</v>
       </c>
       <c r="E5" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G6)*0.85</f>
-        <v>4.7600000000000003E-3</v>
+        <v>8.8644603330000002E-3</v>
       </c>
       <c r="F5" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G6)*0.85</f>
-        <v>2.856E-3</v>
+        <v>4.4322960969044416E-3</v>
       </c>
       <c r="G5" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G6)*0.85</f>
-        <v>2.856E-3</v>
+        <v>4.4322960969044416E-3</v>
       </c>
       <c r="H5" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G6)*0.85</f>
-        <v>9.5200000000000007E-3</v>
+        <v>1.4774320323014805E-2</v>
       </c>
       <c r="I5" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G6)*0.85</f>
-        <v>9.5200000000000007E-3</v>
+        <v>1.4774320323014805E-2</v>
       </c>
       <c r="J5" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G6)*0.85</f>
-        <v>2.856E-3</v>
+        <v>4.4322960969044416E-3</v>
       </c>
       <c r="K5" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G6)*0.85</f>
-        <v>2.856E-3</v>
+        <v>4.4322960969044416E-3</v>
       </c>
       <c r="L5" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G6)*0.85</f>
-        <v>2.1420000000000002E-3</v>
+        <v>3.3242220726783307E-3</v>
       </c>
       <c r="M5" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G6)*0.85</f>
-        <v>2.856E-3</v>
+        <v>4.4322960969044416E-3</v>
       </c>
       <c r="N5" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G6)*0.85</f>
-        <v>2.856E-3</v>
+        <v>4.4322960969044416E-3</v>
       </c>
       <c r="O5" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G6)*0.85</f>
-        <v>5.7120000000000001E-3</v>
+        <v>8.8645921938088831E-3</v>
       </c>
       <c r="P5" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G6)*0.85</f>
-        <v>2.856E-3</v>
+        <v>4.4322960969044416E-3</v>
       </c>
       <c r="Q5" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G6)*0.85</f>
-        <v>2.856E-3</v>
+        <v>4.4322960969044416E-3</v>
       </c>
       <c r="R5" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G6)*0.85</f>
-        <v>2.856E-3</v>
+        <v>4.4322960969044416E-3</v>
       </c>
       <c r="S5" s="8">
-        <v>0.30869999999999997</v>
+        <v>6.6484441453566615E-3</v>
       </c>
       <c r="T5" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G6)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>6.6484441453566615E-3</v>
       </c>
       <c r="U5" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G6)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>6.6484441453566615E-3</v>
       </c>
       <c r="V5" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G6)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>6.6484441453566615E-3</v>
       </c>
       <c r="W5" s="7">
-        <v>6.7999999999999996E-3</v>
+        <v>6.6484441453566615E-3</v>
       </c>
       <c r="X5" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G6)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>6.6484441453566615E-3</v>
       </c>
       <c r="Y5" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G6)*0.85</f>
-        <v>1.9991999999999999E-2</v>
+        <v>3.1026072678331088E-2</v>
       </c>
       <c r="Z5" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G6)*0.85</f>
-        <v>1.9991999999999999E-2</v>
+        <v>3.1026072678331088E-2</v>
       </c>
       <c r="AA5" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G6)*0.85</f>
-        <v>2.856E-3</v>
+        <v>4.4322960969044416E-3</v>
       </c>
       <c r="AB5" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G6)*0.85</f>
-        <v>2.856E-3</v>
+        <v>4.4322960969044416E-3</v>
       </c>
       <c r="AC5" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G6)*0.85</f>
-        <v>2.856E-3</v>
+        <v>4.4322960969044416E-3</v>
       </c>
       <c r="AD5" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G6)*0.85</f>
-        <v>5.7120000000000001E-3</v>
+        <v>8.8645921938088831E-3</v>
       </c>
       <c r="AE5" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G6)*0.85</f>
-        <v>9.5200000000000007E-3</v>
+        <v>1.4774320323014805E-2</v>
       </c>
       <c r="AF5" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G6)*0.85</f>
-        <v>7.1399999999999996E-3</v>
+        <v>1.1080740242261102E-2</v>
       </c>
       <c r="AG5" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G6)*0.85</f>
-        <v>9.9959999999999997E-3</v>
+        <v>1.5513036339165544E-2</v>
       </c>
       <c r="AH5" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G6)*0.85</f>
-        <v>2.856E-3</v>
+        <v>4.4322960969044416E-3</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.3">
@@ -2089,134 +1185,103 @@
         <v>0.16666666666666699</v>
       </c>
       <c r="B6" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G7)*0.85</f>
         <v>0</v>
       </c>
       <c r="C6" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G7)*0.85</f>
-        <v>4.7600000000000003E-3</v>
+        <v>3.5011435059999997E-3</v>
       </c>
       <c r="D6" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G7)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>3.1510031419999997E-3</v>
       </c>
       <c r="E6" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G7)*0.85</f>
-        <v>4.7600000000000003E-3</v>
+        <v>4.2012941670000001E-3</v>
       </c>
       <c r="F6" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G7)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.1006783310901747E-3</v>
       </c>
       <c r="G6" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G7)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.1006783310901747E-3</v>
       </c>
       <c r="H6" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G7)*0.85</f>
-        <v>9.5200000000000007E-3</v>
+        <v>7.0022611036339158E-3</v>
       </c>
       <c r="I6" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G7)*0.85</f>
-        <v>9.5200000000000007E-3</v>
+        <v>7.0022611036339158E-3</v>
       </c>
       <c r="J6" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G7)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.1006783310901747E-3</v>
       </c>
       <c r="K6" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G7)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.1006783310901747E-3</v>
       </c>
       <c r="L6" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G7)*0.85</f>
-        <v>2.1420000000000002E-3</v>
+        <v>1.5755087483176312E-3</v>
       </c>
       <c r="M6" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G7)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.1006783310901747E-3</v>
       </c>
       <c r="N6" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G7)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.1006783310901747E-3</v>
       </c>
       <c r="O6" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G7)*0.85</f>
-        <v>5.7120000000000001E-3</v>
+        <v>4.2013566621803495E-3</v>
       </c>
       <c r="P6" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G7)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.1006783310901747E-3</v>
       </c>
       <c r="Q6" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G7)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.1006783310901747E-3</v>
       </c>
       <c r="R6" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G7)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.1006783310901747E-3</v>
       </c>
       <c r="S6" s="8">
-        <v>0.40879999999999994</v>
+        <v>3.1510174966352623E-3</v>
       </c>
       <c r="T6" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G7)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>3.1510174966352623E-3</v>
       </c>
       <c r="U6" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G7)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>3.1510174966352623E-3</v>
       </c>
       <c r="V6" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G7)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>3.1510174966352623E-3</v>
       </c>
       <c r="W6" s="7">
-        <v>6.3750000000000001E-2</v>
+        <v>3.1510174966352623E-3</v>
       </c>
       <c r="X6" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G7)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>3.1510174966352623E-3</v>
       </c>
       <c r="Y6" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G7)*0.85</f>
-        <v>1.9991999999999999E-2</v>
+        <v>1.4704748317631222E-2</v>
       </c>
       <c r="Z6" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G7)*0.85</f>
-        <v>1.9991999999999999E-2</v>
+        <v>1.4704748317631222E-2</v>
       </c>
       <c r="AA6" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G7)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.1006783310901747E-3</v>
       </c>
       <c r="AB6" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G7)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.1006783310901747E-3</v>
       </c>
       <c r="AC6" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G7)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.1006783310901747E-3</v>
       </c>
       <c r="AD6" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G7)*0.85</f>
-        <v>5.7120000000000001E-3</v>
+        <v>4.2013566621803495E-3</v>
       </c>
       <c r="AE6" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G7)*0.85</f>
-        <v>9.5200000000000007E-3</v>
+        <v>7.0022611036339158E-3</v>
       </c>
       <c r="AF6" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G7)*0.85</f>
-        <v>7.1399999999999996E-3</v>
+        <v>5.2516958277254366E-3</v>
       </c>
       <c r="AG6" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G7)*0.85</f>
-        <v>9.9959999999999997E-3</v>
+        <v>7.3523741588156109E-3</v>
       </c>
       <c r="AH6" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G7)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.1006783310901747E-3</v>
       </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.3">
@@ -2224,134 +1289,103 @@
         <v>0.20833333333333301</v>
       </c>
       <c r="B7" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G8)*0.85</f>
         <v>0</v>
       </c>
       <c r="C7" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G8)*0.85</f>
-        <v>4.7600000000000003E-3</v>
+        <v>1.9057944000000001E-3</v>
       </c>
       <c r="D7" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G8)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>1.7152008000000001E-3</v>
       </c>
       <c r="E7" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G8)*0.85</f>
-        <v>4.7600000000000003E-3</v>
+        <v>2.2869108000000003E-3</v>
       </c>
       <c r="F7" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G8)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.1434724091520861E-3</v>
       </c>
       <c r="G7" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G8)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.1434724091520861E-3</v>
       </c>
       <c r="H7" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G8)*0.85</f>
-        <v>9.5200000000000007E-3</v>
+        <v>3.8115746971736208E-3</v>
       </c>
       <c r="I7" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G8)*0.85</f>
-        <v>9.5200000000000007E-3</v>
+        <v>3.8115746971736208E-3</v>
       </c>
       <c r="J7" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G8)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.1434724091520861E-3</v>
       </c>
       <c r="K7" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G8)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.1434724091520861E-3</v>
       </c>
       <c r="L7" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G8)*0.85</f>
-        <v>2.1420000000000002E-3</v>
+        <v>8.5760430686406463E-4</v>
       </c>
       <c r="M7" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G8)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.1434724091520861E-3</v>
       </c>
       <c r="N7" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G8)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.1434724091520861E-3</v>
       </c>
       <c r="O7" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G8)*0.85</f>
-        <v>5.7120000000000001E-3</v>
+        <v>2.2869448183041722E-3</v>
       </c>
       <c r="P7" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G8)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.1434724091520861E-3</v>
       </c>
       <c r="Q7" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G8)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.1434724091520861E-3</v>
       </c>
       <c r="R7" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G8)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.1434724091520861E-3</v>
       </c>
       <c r="S7" s="8">
-        <v>0.40879999999999994</v>
+        <v>1.7152086137281293E-3</v>
       </c>
       <c r="T7" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G8)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>1.7152086137281293E-3</v>
       </c>
       <c r="U7" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G8)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>1.7152086137281293E-3</v>
       </c>
       <c r="V7" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G8)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>1.7152086137281293E-3</v>
       </c>
       <c r="W7" s="7">
-        <v>0.15045</v>
+        <v>1.7152086137281293E-3</v>
       </c>
       <c r="X7" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G8)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>1.7152086137281293E-3</v>
       </c>
       <c r="Y7" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G8)*0.85</f>
-        <v>1.9991999999999999E-2</v>
+        <v>8.0043068640646021E-3</v>
       </c>
       <c r="Z7" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G8)*0.85</f>
-        <v>1.9991999999999999E-2</v>
+        <v>8.0043068640646021E-3</v>
       </c>
       <c r="AA7" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G8)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.1434724091520861E-3</v>
       </c>
       <c r="AB7" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G8)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.1434724091520861E-3</v>
       </c>
       <c r="AC7" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G8)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.1434724091520861E-3</v>
       </c>
       <c r="AD7" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G8)*0.85</f>
-        <v>5.7120000000000001E-3</v>
+        <v>2.2869448183041722E-3</v>
       </c>
       <c r="AE7" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G8)*0.85</f>
-        <v>9.5200000000000007E-3</v>
+        <v>3.8115746971736208E-3</v>
       </c>
       <c r="AF7" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G8)*0.85</f>
-        <v>7.1399999999999996E-3</v>
+        <v>2.8586810228802152E-3</v>
       </c>
       <c r="AG7" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G8)*0.85</f>
-        <v>9.9959999999999997E-3</v>
+        <v>4.002153432032301E-3</v>
       </c>
       <c r="AH7" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G8)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.1434724091520861E-3</v>
       </c>
     </row>
     <row r="8" spans="1:34" x14ac:dyDescent="0.3">
@@ -2359,134 +1393,103 @@
         <v>0.25</v>
       </c>
       <c r="B8" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G9)*0.85</f>
         <v>0</v>
       </c>
       <c r="C8" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G9)*0.85</f>
-        <v>4.7600000000000003E-3</v>
+        <v>4.9887936939999999E-3</v>
       </c>
       <c r="D8" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G9)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>4.4898772580000005E-3</v>
       </c>
       <c r="E8" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G9)*0.85</f>
-        <v>4.7600000000000003E-3</v>
+        <v>5.9864412330000007E-3</v>
       </c>
       <c r="F8" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G9)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.9932651413189771E-3</v>
       </c>
       <c r="G8" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G9)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.9932651413189771E-3</v>
       </c>
       <c r="H8" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G9)*0.85</f>
-        <v>9.5200000000000007E-3</v>
+        <v>9.9775504710632578E-3</v>
       </c>
       <c r="I8" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G9)*0.85</f>
-        <v>9.5200000000000007E-3</v>
+        <v>9.9775504710632578E-3</v>
       </c>
       <c r="J8" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G9)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.9932651413189771E-3</v>
       </c>
       <c r="K8" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G9)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.9932651413189771E-3</v>
       </c>
       <c r="L8" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G9)*0.85</f>
-        <v>2.1420000000000002E-3</v>
+        <v>2.2449488559892327E-3</v>
       </c>
       <c r="M8" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G9)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.9932651413189771E-3</v>
       </c>
       <c r="N8" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G9)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.9932651413189771E-3</v>
       </c>
       <c r="O8" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G9)*0.85</f>
-        <v>5.7120000000000001E-3</v>
+        <v>5.9865302826379542E-3</v>
       </c>
       <c r="P8" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G9)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.9932651413189771E-3</v>
       </c>
       <c r="Q8" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G9)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.9932651413189771E-3</v>
       </c>
       <c r="R8" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G9)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.9932651413189771E-3</v>
       </c>
       <c r="S8" s="8">
-        <v>0.40879999999999994</v>
+        <v>4.4898977119784654E-3</v>
       </c>
       <c r="T8" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G9)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>4.4898977119784654E-3</v>
       </c>
       <c r="U8" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G9)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>4.4898977119784654E-3</v>
       </c>
       <c r="V8" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G9)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>4.4898977119784654E-3</v>
       </c>
       <c r="W8" s="7">
-        <v>0.23800000000000002</v>
+        <v>4.4898977119784654E-3</v>
       </c>
       <c r="X8" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G9)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>4.4898977119784654E-3</v>
       </c>
       <c r="Y8" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G9)*0.85</f>
-        <v>1.9991999999999999E-2</v>
+        <v>2.0952855989232837E-2</v>
       </c>
       <c r="Z8" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G9)*0.85</f>
-        <v>1.9991999999999999E-2</v>
+        <v>2.0952855989232837E-2</v>
       </c>
       <c r="AA8" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G9)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.9932651413189771E-3</v>
       </c>
       <c r="AB8" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G9)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.9932651413189771E-3</v>
       </c>
       <c r="AC8" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G9)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.9932651413189771E-3</v>
       </c>
       <c r="AD8" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G9)*0.85</f>
-        <v>5.7120000000000001E-3</v>
+        <v>5.9865302826379542E-3</v>
       </c>
       <c r="AE8" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G9)*0.85</f>
-        <v>9.5200000000000007E-3</v>
+        <v>9.9775504710632578E-3</v>
       </c>
       <c r="AF8" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G9)*0.85</f>
-        <v>7.1399999999999996E-3</v>
+        <v>7.4831628532974421E-3</v>
       </c>
       <c r="AG8" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G9)*0.85</f>
-        <v>9.9959999999999997E-3</v>
+        <v>1.0476427994616419E-2</v>
       </c>
       <c r="AH8" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G9)*0.85</f>
-        <v>2.856E-3</v>
+        <v>2.9932651413189771E-3</v>
       </c>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.3">
@@ -2494,134 +1497,103 @@
         <v>0.29166666666666702</v>
       </c>
       <c r="B9" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G10)*0.85</f>
         <v>0</v>
       </c>
       <c r="C9" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G10)*0.85</f>
-        <v>3.8884694999999997E-2</v>
+        <v>3.7450555794000001E-2</v>
       </c>
       <c r="D9" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G10)*0.85</f>
-        <v>3.4996225499999999E-2</v>
+        <v>3.3705221957999999E-2</v>
       </c>
       <c r="E9" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G10)*0.85</f>
-        <v>3.8884694999999997E-2</v>
+        <v>4.4939832183000003E-2</v>
       </c>
       <c r="F9" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G10)*0.85</f>
-        <v>2.3330817E-2</v>
+        <v>2.2470250336473756E-2</v>
       </c>
       <c r="G9" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G10)*0.85</f>
-        <v>2.3330817E-2</v>
+        <v>2.2470250336473756E-2</v>
       </c>
       <c r="H9" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G10)*0.85</f>
-        <v>7.7769389999999994E-2</v>
+        <v>7.4900834454912524E-2</v>
       </c>
       <c r="I9" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G10)*0.85</f>
-        <v>7.7769389999999994E-2</v>
+        <v>7.4900834454912524E-2</v>
       </c>
       <c r="J9" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G10)*0.85</f>
-        <v>2.3330817E-2</v>
+        <v>2.2470250336473756E-2</v>
       </c>
       <c r="K9" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G10)*0.85</f>
-        <v>2.3330817E-2</v>
+        <v>2.2470250336473756E-2</v>
       </c>
       <c r="L9" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G10)*0.85</f>
-        <v>1.7498112749999999E-2</v>
+        <v>1.6852687752355319E-2</v>
       </c>
       <c r="M9" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G10)*0.85</f>
-        <v>2.3330817E-2</v>
+        <v>2.2470250336473756E-2</v>
       </c>
       <c r="N9" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G10)*0.85</f>
-        <v>2.3330817E-2</v>
+        <v>2.2470250336473756E-2</v>
       </c>
       <c r="O9" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G10)*0.85</f>
-        <v>4.6661634E-2</v>
+        <v>4.4940500672947511E-2</v>
       </c>
       <c r="P9" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G10)*0.85</f>
-        <v>2.3330817E-2</v>
+        <v>2.2470250336473756E-2</v>
       </c>
       <c r="Q9" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G10)*0.85</f>
-        <v>2.3330817E-2</v>
+        <v>2.2470250336473756E-2</v>
       </c>
       <c r="R9" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G10)*0.85</f>
-        <v>2.3330817E-2</v>
+        <v>2.2470250336473756E-2</v>
       </c>
       <c r="S9" s="8">
-        <v>0.40879999999999994</v>
+        <v>3.3705375504710637E-2</v>
       </c>
       <c r="T9" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G10)*0.85</f>
-        <v>3.4996225499999999E-2</v>
+        <v>3.3705375504710637E-2</v>
       </c>
       <c r="U9" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G10)*0.85</f>
-        <v>3.4996225499999999E-2</v>
+        <v>3.3705375504710637E-2</v>
       </c>
       <c r="V9" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G10)*0.85</f>
-        <v>3.4996225499999999E-2</v>
+        <v>3.3705375504710637E-2</v>
       </c>
       <c r="W9" s="7">
-        <v>0.3281</v>
+        <v>3.3705375504710637E-2</v>
       </c>
       <c r="X9" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G10)*0.85</f>
-        <v>3.4996225499999999E-2</v>
+        <v>3.3705375504710637E-2</v>
       </c>
       <c r="Y9" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G10)*0.85</f>
-        <v>0.163315719</v>
+        <v>0.15729175235531628</v>
       </c>
       <c r="Z9" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G10)*0.85</f>
-        <v>0.163315719</v>
+        <v>0.15729175235531628</v>
       </c>
       <c r="AA9" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G10)*0.85</f>
-        <v>2.3330817E-2</v>
+        <v>2.2470250336473756E-2</v>
       </c>
       <c r="AB9" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G10)*0.85</f>
-        <v>2.3330817E-2</v>
+        <v>2.2470250336473756E-2</v>
       </c>
       <c r="AC9" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G10)*0.85</f>
-        <v>2.3330817E-2</v>
+        <v>2.2470250336473756E-2</v>
       </c>
       <c r="AD9" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G10)*0.85</f>
-        <v>4.6661634E-2</v>
+        <v>4.4940500672947511E-2</v>
       </c>
       <c r="AE9" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G10)*0.85</f>
-        <v>7.7769389999999994E-2</v>
+        <v>7.4900834454912524E-2</v>
       </c>
       <c r="AF9" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G10)*0.85</f>
-        <v>5.8327042500000002E-2</v>
+        <v>5.6175625841184386E-2</v>
       </c>
       <c r="AG9" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G10)*0.85</f>
-        <v>8.1657859499999999E-2</v>
+        <v>7.8645876177658142E-2</v>
       </c>
       <c r="AH9" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G10)*0.85</f>
-        <v>2.3330817E-2</v>
+        <v>2.2470250336473756E-2</v>
       </c>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.3">
@@ -2629,134 +1601,103 @@
         <v>0.33333333333333398</v>
       </c>
       <c r="B10" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G11)*0.85</f>
         <v>0</v>
       </c>
       <c r="C10" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G11)*0.85</f>
-        <v>8.1734555E-2</v>
+        <v>1.7551424294000001E-2</v>
       </c>
       <c r="D10" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G11)*0.85</f>
-        <v>7.3561099499999991E-2</v>
+        <v>1.5796151458E-2</v>
       </c>
       <c r="E10" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G11)*0.85</f>
-        <v>8.1734555E-2</v>
+        <v>2.1061317933E-2</v>
       </c>
       <c r="F10" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G11)*0.85</f>
-        <v>4.9040732999999996E-2</v>
+        <v>1.0530815612382234E-2</v>
       </c>
       <c r="G10" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G11)*0.85</f>
-        <v>4.9040732999999996E-2</v>
+        <v>1.0530815612382234E-2</v>
       </c>
       <c r="H10" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G11)*0.85</f>
-        <v>0.16346911</v>
+        <v>3.510271870794078E-2</v>
       </c>
       <c r="I10" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G11)*0.85</f>
-        <v>0.16346911</v>
+        <v>3.510271870794078E-2</v>
       </c>
       <c r="J10" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G11)*0.85</f>
-        <v>4.9040732999999996E-2</v>
+        <v>1.0530815612382234E-2</v>
       </c>
       <c r="K10" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G11)*0.85</f>
-        <v>4.9040732999999996E-2</v>
+        <v>1.0530815612382234E-2</v>
       </c>
       <c r="L10" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G11)*0.85</f>
-        <v>3.6780549749999995E-2</v>
+        <v>7.8981117092866756E-3</v>
       </c>
       <c r="M10" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G11)*0.85</f>
-        <v>4.9040732999999996E-2</v>
+        <v>1.0530815612382234E-2</v>
       </c>
       <c r="N10" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G11)*0.85</f>
-        <v>4.9040732999999996E-2</v>
+        <v>1.0530815612382234E-2</v>
       </c>
       <c r="O10" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G11)*0.85</f>
-        <v>9.8081465999999992E-2</v>
+        <v>2.1061631224764468E-2</v>
       </c>
       <c r="P10" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G11)*0.85</f>
-        <v>4.9040732999999996E-2</v>
+        <v>1.0530815612382234E-2</v>
       </c>
       <c r="Q10" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G11)*0.85</f>
-        <v>4.9040732999999996E-2</v>
+        <v>1.0530815612382234E-2</v>
       </c>
       <c r="R10" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G11)*0.85</f>
-        <v>4.9040732999999996E-2</v>
+        <v>1.0530815612382234E-2</v>
       </c>
       <c r="S10" s="8">
-        <v>0.40879999999999994</v>
+        <v>1.5796223418573351E-2</v>
       </c>
       <c r="T10" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G11)*0.85</f>
-        <v>7.3561099499999991E-2</v>
+        <v>1.5796223418573351E-2</v>
       </c>
       <c r="U10" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G11)*0.85</f>
-        <v>7.3561099499999991E-2</v>
+        <v>1.5796223418573351E-2</v>
       </c>
       <c r="V10" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G11)*0.85</f>
-        <v>7.3561099499999991E-2</v>
+        <v>1.5796223418573351E-2</v>
       </c>
       <c r="W10" s="7">
-        <v>0.40375</v>
+        <v>1.5796223418573351E-2</v>
       </c>
       <c r="X10" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G11)*0.85</f>
-        <v>7.3561099499999991E-2</v>
+        <v>1.5796223418573351E-2</v>
       </c>
       <c r="Y10" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G11)*0.85</f>
-        <v>0.34328513099999997</v>
+        <v>7.3715709286675632E-2</v>
       </c>
       <c r="Z10" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G11)*0.85</f>
-        <v>0.34328513099999997</v>
+        <v>7.3715709286675632E-2</v>
       </c>
       <c r="AA10" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G11)*0.85</f>
-        <v>4.9040732999999996E-2</v>
+        <v>1.0530815612382234E-2</v>
       </c>
       <c r="AB10" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G11)*0.85</f>
-        <v>4.9040732999999996E-2</v>
+        <v>1.0530815612382234E-2</v>
       </c>
       <c r="AC10" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G11)*0.85</f>
-        <v>4.9040732999999996E-2</v>
+        <v>1.0530815612382234E-2</v>
       </c>
       <c r="AD10" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G11)*0.85</f>
-        <v>9.8081465999999992E-2</v>
+        <v>2.1061631224764468E-2</v>
       </c>
       <c r="AE10" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G11)*0.85</f>
-        <v>0.16346911</v>
+        <v>3.510271870794078E-2</v>
       </c>
       <c r="AF10" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G11)*0.85</f>
-        <v>0.12260183249999999</v>
+        <v>2.6327039030955582E-2</v>
       </c>
       <c r="AG10" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G11)*0.85</f>
-        <v>0.17164256549999998</v>
+        <v>3.6857854643337816E-2</v>
       </c>
       <c r="AH10" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G11)*0.85</f>
-        <v>4.9040732999999996E-2</v>
+        <v>1.0530815612382234E-2</v>
       </c>
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.3">
@@ -2764,134 +1705,103 @@
         <v>0.375</v>
       </c>
       <c r="B11" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G12)*0.85</f>
         <v>0</v>
       </c>
       <c r="C11" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G12)*0.85</f>
-        <v>0.12051725000000002</v>
+        <v>1.7083051094000001E-2</v>
       </c>
       <c r="D11" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G12)*0.85</f>
-        <v>0.10846552500000001</v>
+        <v>1.5374619058000001E-2</v>
       </c>
       <c r="E11" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G12)*0.85</f>
-        <v>0.12051725000000002</v>
+        <v>2.0499280533000003E-2</v>
       </c>
       <c r="F11" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G12)*0.85</f>
-        <v>7.2310349999999995E-2</v>
+        <v>1.0249792732166892E-2</v>
       </c>
       <c r="G11" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G12)*0.85</f>
-        <v>7.2310349999999995E-2</v>
+        <v>1.0249792732166892E-2</v>
       </c>
       <c r="H11" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G12)*0.85</f>
-        <v>0.24103450000000004</v>
+        <v>3.4165975773889634E-2</v>
       </c>
       <c r="I11" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G12)*0.85</f>
-        <v>0.24103450000000004</v>
+        <v>3.4165975773889634E-2</v>
       </c>
       <c r="J11" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G12)*0.85</f>
-        <v>7.2310349999999995E-2</v>
+        <v>1.0249792732166892E-2</v>
       </c>
       <c r="K11" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G12)*0.85</f>
-        <v>7.2310349999999995E-2</v>
+        <v>1.0249792732166892E-2</v>
       </c>
       <c r="L11" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G12)*0.85</f>
-        <v>5.4232762500000004E-2</v>
+        <v>7.6873445491251685E-3</v>
       </c>
       <c r="M11" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G12)*0.85</f>
-        <v>7.2310349999999995E-2</v>
+        <v>1.0249792732166892E-2</v>
       </c>
       <c r="N11" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G12)*0.85</f>
-        <v>7.2310349999999995E-2</v>
+        <v>1.0249792732166892E-2</v>
       </c>
       <c r="O11" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G12)*0.85</f>
-        <v>0.14462069999999999</v>
+        <v>2.0499585464333784E-2</v>
       </c>
       <c r="P11" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G12)*0.85</f>
-        <v>7.2310349999999995E-2</v>
+        <v>1.0249792732166892E-2</v>
       </c>
       <c r="Q11" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G12)*0.85</f>
-        <v>7.2310349999999995E-2</v>
+        <v>1.0249792732166892E-2</v>
       </c>
       <c r="R11" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G12)*0.85</f>
-        <v>7.2310349999999995E-2</v>
+        <v>1.0249792732166892E-2</v>
       </c>
       <c r="S11" s="8">
-        <v>0.40879999999999994</v>
+        <v>1.5374689098250337E-2</v>
       </c>
       <c r="T11" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G12)*0.85</f>
-        <v>0.10846552500000001</v>
+        <v>1.5374689098250337E-2</v>
       </c>
       <c r="U11" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G12)*0.85</f>
-        <v>0.10846552500000001</v>
+        <v>1.5374689098250337E-2</v>
       </c>
       <c r="V11" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G12)*0.85</f>
-        <v>0.10846552500000001</v>
+        <v>1.5374689098250337E-2</v>
       </c>
       <c r="W11" s="7">
-        <v>0.4471</v>
+        <v>1.5374689098250337E-2</v>
       </c>
       <c r="X11" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G12)*0.85</f>
-        <v>0.10846552500000001</v>
+        <v>1.5374689098250337E-2</v>
       </c>
       <c r="Y11" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G12)*0.85</f>
-        <v>0.50617245</v>
+        <v>7.1748549125168232E-2</v>
       </c>
       <c r="Z11" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G12)*0.85</f>
-        <v>0.50617245</v>
+        <v>7.1748549125168232E-2</v>
       </c>
       <c r="AA11" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G12)*0.85</f>
-        <v>7.2310349999999995E-2</v>
+        <v>1.0249792732166892E-2</v>
       </c>
       <c r="AB11" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G12)*0.85</f>
-        <v>7.2310349999999995E-2</v>
+        <v>1.0249792732166892E-2</v>
       </c>
       <c r="AC11" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G12)*0.85</f>
-        <v>7.2310349999999995E-2</v>
+        <v>1.0249792732166892E-2</v>
       </c>
       <c r="AD11" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G12)*0.85</f>
-        <v>0.14462069999999999</v>
+        <v>2.0499585464333784E-2</v>
       </c>
       <c r="AE11" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G12)*0.85</f>
-        <v>0.24103450000000004</v>
+        <v>3.4165975773889634E-2</v>
       </c>
       <c r="AF11" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G12)*0.85</f>
-        <v>0.18077587499999997</v>
+        <v>2.5624481830417226E-2</v>
       </c>
       <c r="AG11" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G12)*0.85</f>
-        <v>0.253086225</v>
+        <v>3.5874274562584116E-2</v>
       </c>
       <c r="AH11" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G12)*0.85</f>
-        <v>7.2310349999999995E-2</v>
+        <v>1.0249792732166892E-2</v>
       </c>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.3">
@@ -2899,134 +1809,103 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B12" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G13)*0.85</f>
         <v>0</v>
       </c>
       <c r="C12" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G13)*0.85</f>
-        <v>0.18771400000000002</v>
+        <v>1.5686922106000003E-2</v>
       </c>
       <c r="D12" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G13)*0.85</f>
-        <v>0.1689426</v>
+        <v>1.4118113342000001E-2</v>
       </c>
       <c r="E12" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G13)*0.85</f>
-        <v>0.18771400000000002</v>
+        <v>1.8823956867000002E-2</v>
       </c>
       <c r="F12" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G13)*0.85</f>
-        <v>0.1126284</v>
+        <v>9.4121184387617775E-3</v>
       </c>
       <c r="G12" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G13)*0.85</f>
-        <v>0.1126284</v>
+        <v>9.4121184387617775E-3</v>
       </c>
       <c r="H12" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G13)*0.85</f>
-        <v>0.37542800000000004</v>
+        <v>3.1373728129205927E-2</v>
       </c>
       <c r="I12" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G13)*0.85</f>
-        <v>0.37542800000000004</v>
+        <v>3.1373728129205927E-2</v>
       </c>
       <c r="J12" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G13)*0.85</f>
-        <v>0.1126284</v>
+        <v>9.4121184387617775E-3</v>
       </c>
       <c r="K12" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G13)*0.85</f>
-        <v>0.1126284</v>
+        <v>9.4121184387617775E-3</v>
       </c>
       <c r="L12" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G13)*0.85</f>
-        <v>8.4471299999999999E-2</v>
+        <v>7.0590888290713331E-3</v>
       </c>
       <c r="M12" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G13)*0.85</f>
-        <v>0.1126284</v>
+        <v>9.4121184387617775E-3</v>
       </c>
       <c r="N12" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G13)*0.85</f>
-        <v>0.1126284</v>
+        <v>9.4121184387617775E-3</v>
       </c>
       <c r="O12" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G13)*0.85</f>
-        <v>0.22525680000000001</v>
+        <v>1.8824236877523555E-2</v>
       </c>
       <c r="P12" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G13)*0.85</f>
-        <v>0.1126284</v>
+        <v>9.4121184387617775E-3</v>
       </c>
       <c r="Q12" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G13)*0.85</f>
-        <v>0.1126284</v>
+        <v>9.4121184387617775E-3</v>
       </c>
       <c r="R12" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G13)*0.85</f>
-        <v>0.1126284</v>
+        <v>9.4121184387617775E-3</v>
       </c>
       <c r="S12" s="8">
-        <v>0.40879999999999994</v>
+        <v>1.4118177658142666E-2</v>
       </c>
       <c r="T12" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G13)*0.85</f>
-        <v>0.1689426</v>
+        <v>1.4118177658142666E-2</v>
       </c>
       <c r="U12" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G13)*0.85</f>
-        <v>0.1689426</v>
+        <v>1.4118177658142666E-2</v>
       </c>
       <c r="V12" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G13)*0.85</f>
-        <v>0.1689426</v>
+        <v>1.4118177658142666E-2</v>
       </c>
       <c r="W12" s="7">
-        <v>0.45135000000000003</v>
+        <v>1.4118177658142666E-2</v>
       </c>
       <c r="X12" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G13)*0.85</f>
-        <v>0.1689426</v>
+        <v>1.4118177658142666E-2</v>
       </c>
       <c r="Y12" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G13)*0.85</f>
-        <v>0.78839879999999996</v>
+        <v>6.5884829071332432E-2</v>
       </c>
       <c r="Z12" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G13)*0.85</f>
-        <v>0.78839879999999996</v>
+        <v>6.5884829071332432E-2</v>
       </c>
       <c r="AA12" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G13)*0.85</f>
-        <v>0.1126284</v>
+        <v>9.4121184387617775E-3</v>
       </c>
       <c r="AB12" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G13)*0.85</f>
-        <v>0.1126284</v>
+        <v>9.4121184387617775E-3</v>
       </c>
       <c r="AC12" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G13)*0.85</f>
-        <v>0.1126284</v>
+        <v>9.4121184387617775E-3</v>
       </c>
       <c r="AD12" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G13)*0.85</f>
-        <v>0.22525680000000001</v>
+        <v>1.8824236877523555E-2</v>
       </c>
       <c r="AE12" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G13)*0.85</f>
-        <v>0.37542800000000004</v>
+        <v>3.1373728129205927E-2</v>
       </c>
       <c r="AF12" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G13)*0.85</f>
-        <v>0.28157100000000002</v>
+        <v>2.3530296096904442E-2</v>
       </c>
       <c r="AG12" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G13)*0.85</f>
-        <v>0.39419939999999998</v>
+        <v>3.2942414535666216E-2</v>
       </c>
       <c r="AH12" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G13)*0.85</f>
-        <v>0.1126284</v>
+        <v>9.4121184387617775E-3</v>
       </c>
     </row>
     <row r="13" spans="1:34" x14ac:dyDescent="0.3">
@@ -3034,134 +1913,103 @@
         <v>0.45833333333333398</v>
       </c>
       <c r="B13" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G14)*0.85</f>
         <v>0</v>
       </c>
       <c r="C13" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G14)*0.85</f>
-        <v>1.2189E-2</v>
+        <v>9.0902086E-3</v>
       </c>
       <c r="D13" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G14)*0.85</f>
-        <v>1.0970099999999998E-2</v>
+        <v>8.181120200000001E-3</v>
       </c>
       <c r="E13" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G14)*0.85</f>
-        <v>1.2189E-2</v>
+        <v>1.0908047700000001E-2</v>
       </c>
       <c r="F13" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G14)*0.85</f>
-        <v>7.3133999999999985E-3</v>
+        <v>5.4541049798115752E-3</v>
       </c>
       <c r="G13" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G14)*0.85</f>
-        <v>7.3133999999999985E-3</v>
+        <v>5.4541049798115752E-3</v>
       </c>
       <c r="H13" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G14)*0.85</f>
-        <v>2.4378E-2</v>
+        <v>1.8180349932705248E-2</v>
       </c>
       <c r="I13" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G14)*0.85</f>
-        <v>2.4378E-2</v>
+        <v>1.8180349932705248E-2</v>
       </c>
       <c r="J13" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G14)*0.85</f>
-        <v>7.3133999999999985E-3</v>
+        <v>5.4541049798115752E-3</v>
       </c>
       <c r="K13" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G14)*0.85</f>
-        <v>7.3133999999999985E-3</v>
+        <v>5.4541049798115752E-3</v>
       </c>
       <c r="L13" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G14)*0.85</f>
-        <v>5.4850499999999991E-3</v>
+        <v>4.0905787348586809E-3</v>
       </c>
       <c r="M13" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G14)*0.85</f>
-        <v>7.3133999999999985E-3</v>
+        <v>5.4541049798115752E-3</v>
       </c>
       <c r="N13" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G14)*0.85</f>
-        <v>7.3133999999999985E-3</v>
+        <v>5.4541049798115752E-3</v>
       </c>
       <c r="O13" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G14)*0.85</f>
-        <v>1.4626799999999997E-2</v>
+        <v>1.090820995962315E-2</v>
       </c>
       <c r="P13" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G14)*0.85</f>
-        <v>7.3133999999999985E-3</v>
+        <v>5.4541049798115752E-3</v>
       </c>
       <c r="Q13" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G14)*0.85</f>
-        <v>7.3133999999999985E-3</v>
+        <v>5.4541049798115752E-3</v>
       </c>
       <c r="R13" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G14)*0.85</f>
-        <v>7.3133999999999985E-3</v>
+        <v>5.4541049798115752E-3</v>
       </c>
       <c r="S13" s="8">
-        <v>0.40879999999999994</v>
+        <v>8.1811574697173619E-3</v>
       </c>
       <c r="T13" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G14)*0.85</f>
-        <v>1.0970099999999998E-2</v>
+        <v>8.1811574697173619E-3</v>
       </c>
       <c r="U13" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G14)*0.85</f>
-        <v>1.0970099999999998E-2</v>
+        <v>8.1811574697173619E-3</v>
       </c>
       <c r="V13" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G14)*0.85</f>
-        <v>1.0970099999999998E-2</v>
+        <v>8.1811574697173619E-3</v>
       </c>
       <c r="W13" s="7">
-        <v>0.44540000000000002</v>
+        <v>8.1811574697173619E-3</v>
       </c>
       <c r="X13" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G14)*0.85</f>
-        <v>1.0970099999999998E-2</v>
+        <v>8.1811574697173619E-3</v>
       </c>
       <c r="Y13" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G14)*0.85</f>
-        <v>5.1193799999999998E-2</v>
+        <v>3.8178734858681021E-2</v>
       </c>
       <c r="Z13" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G14)*0.85</f>
-        <v>5.1193799999999998E-2</v>
+        <v>3.8178734858681021E-2</v>
       </c>
       <c r="AA13" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G14)*0.85</f>
-        <v>7.3133999999999985E-3</v>
+        <v>5.4541049798115752E-3</v>
       </c>
       <c r="AB13" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G14)*0.85</f>
-        <v>7.3133999999999985E-3</v>
+        <v>5.4541049798115752E-3</v>
       </c>
       <c r="AC13" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G14)*0.85</f>
-        <v>7.3133999999999985E-3</v>
+        <v>5.4541049798115752E-3</v>
       </c>
       <c r="AD13" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G14)*0.85</f>
-        <v>1.4626799999999997E-2</v>
+        <v>1.090820995962315E-2</v>
       </c>
       <c r="AE13" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G14)*0.85</f>
-        <v>2.4378E-2</v>
+        <v>1.8180349932705248E-2</v>
       </c>
       <c r="AF13" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G14)*0.85</f>
-        <v>1.8283499999999998E-2</v>
+        <v>1.3635262449528935E-2</v>
       </c>
       <c r="AG13" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G14)*0.85</f>
-        <v>2.5596899999999999E-2</v>
+        <v>1.9089367429340511E-2</v>
       </c>
       <c r="AH13" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G14)*0.85</f>
-        <v>7.3133999999999985E-3</v>
+        <v>5.4541049798115752E-3</v>
       </c>
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.3">
@@ -3169,134 +2017,103 @@
         <v>0.5</v>
       </c>
       <c r="B14" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G15)*0.85</f>
         <v>0</v>
       </c>
       <c r="C14" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G15)*0.85</f>
-        <v>5.6227500000000001E-3</v>
+        <v>2.5087576000000001E-3</v>
       </c>
       <c r="D14" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G15)*0.85</f>
-        <v>5.0604749999999992E-3</v>
+        <v>2.2578632000000002E-3</v>
       </c>
       <c r="E14" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G15)*0.85</f>
-        <v>5.6227500000000001E-3</v>
+        <v>3.0104532000000007E-3</v>
       </c>
       <c r="F14" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G15)*0.85</f>
-        <v>3.3736500000000002E-3</v>
+        <v>1.505248990578735E-3</v>
       </c>
       <c r="G14" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G15)*0.85</f>
-        <v>3.3736500000000002E-3</v>
+        <v>1.505248990578735E-3</v>
       </c>
       <c r="H14" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G15)*0.85</f>
-        <v>1.12455E-2</v>
+        <v>5.01749663526245E-3</v>
       </c>
       <c r="I14" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G15)*0.85</f>
-        <v>1.12455E-2</v>
+        <v>5.01749663526245E-3</v>
       </c>
       <c r="J14" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G15)*0.85</f>
-        <v>3.3736500000000002E-3</v>
+        <v>1.505248990578735E-3</v>
       </c>
       <c r="K14" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G15)*0.85</f>
-        <v>3.3736500000000002E-3</v>
+        <v>1.505248990578735E-3</v>
       </c>
       <c r="L14" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G15)*0.85</f>
-        <v>2.5302374999999996E-3</v>
+        <v>1.1289367429340512E-3</v>
       </c>
       <c r="M14" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G15)*0.85</f>
-        <v>3.3736500000000002E-3</v>
+        <v>1.505248990578735E-3</v>
       </c>
       <c r="N14" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G15)*0.85</f>
-        <v>3.3736500000000002E-3</v>
+        <v>1.505248990578735E-3</v>
       </c>
       <c r="O14" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G15)*0.85</f>
-        <v>6.7473000000000003E-3</v>
+        <v>3.0104979811574699E-3</v>
       </c>
       <c r="P14" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G15)*0.85</f>
-        <v>3.3736500000000002E-3</v>
+        <v>1.505248990578735E-3</v>
       </c>
       <c r="Q14" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G15)*0.85</f>
-        <v>3.3736500000000002E-3</v>
+        <v>1.505248990578735E-3</v>
       </c>
       <c r="R14" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G15)*0.85</f>
-        <v>3.3736500000000002E-3</v>
+        <v>1.505248990578735E-3</v>
       </c>
       <c r="S14" s="8">
-        <v>0.40879999999999994</v>
+        <v>2.2578734858681023E-3</v>
       </c>
       <c r="T14" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G15)*0.85</f>
-        <v>5.0604749999999992E-3</v>
+        <v>2.2578734858681023E-3</v>
       </c>
       <c r="U14" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G15)*0.85</f>
-        <v>5.0604749999999992E-3</v>
+        <v>2.2578734858681023E-3</v>
       </c>
       <c r="V14" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G15)*0.85</f>
-        <v>5.0604749999999992E-3</v>
+        <v>2.2578734858681023E-3</v>
       </c>
       <c r="W14" s="7">
-        <v>0.41394999999999998</v>
+        <v>2.2578734858681023E-3</v>
       </c>
       <c r="X14" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G15)*0.85</f>
-        <v>5.0604749999999992E-3</v>
+        <v>2.2578734858681023E-3</v>
       </c>
       <c r="Y14" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G15)*0.85</f>
-        <v>2.3615549999999999E-2</v>
+        <v>1.0536742934051144E-2</v>
       </c>
       <c r="Z14" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G15)*0.85</f>
-        <v>2.3615549999999999E-2</v>
+        <v>1.0536742934051144E-2</v>
       </c>
       <c r="AA14" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G15)*0.85</f>
-        <v>3.3736500000000002E-3</v>
+        <v>1.505248990578735E-3</v>
       </c>
       <c r="AB14" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G15)*0.85</f>
-        <v>3.3736500000000002E-3</v>
+        <v>1.505248990578735E-3</v>
       </c>
       <c r="AC14" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G15)*0.85</f>
-        <v>3.3736500000000002E-3</v>
+        <v>1.505248990578735E-3</v>
       </c>
       <c r="AD14" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G15)*0.85</f>
-        <v>6.7473000000000003E-3</v>
+        <v>3.0104979811574699E-3</v>
       </c>
       <c r="AE14" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G15)*0.85</f>
-        <v>1.12455E-2</v>
+        <v>5.01749663526245E-3</v>
       </c>
       <c r="AF14" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G15)*0.85</f>
-        <v>8.4341249999999989E-3</v>
+        <v>3.7631224764468371E-3</v>
       </c>
       <c r="AG14" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G15)*0.85</f>
-        <v>1.1807775E-2</v>
+        <v>5.2683714670255719E-3</v>
       </c>
       <c r="AH14" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G15)*0.85</f>
-        <v>3.3736500000000002E-3</v>
+        <v>1.505248990578735E-3</v>
       </c>
     </row>
     <row r="15" spans="1:34" x14ac:dyDescent="0.3">
@@ -3304,134 +2121,103 @@
         <v>0.54166666666666696</v>
       </c>
       <c r="B15" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G16)*0.85</f>
         <v>0</v>
       </c>
       <c r="C15" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G16)*0.85</f>
-        <v>4.7600000000000003E-3</v>
+        <v>2.8856096000000001E-3</v>
       </c>
       <c r="D15" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G16)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>2.5970272000000001E-3</v>
       </c>
       <c r="E15" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G16)*0.85</f>
-        <v>4.7600000000000003E-3</v>
+        <v>3.4626672000000005E-3</v>
       </c>
       <c r="F15" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G16)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.7313593539703903E-3</v>
       </c>
       <c r="G15" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G16)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.7313593539703903E-3</v>
       </c>
       <c r="H15" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G16)*0.85</f>
-        <v>9.5200000000000007E-3</v>
+        <v>5.7711978465679681E-3</v>
       </c>
       <c r="I15" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G16)*0.85</f>
-        <v>9.5200000000000007E-3</v>
+        <v>5.7711978465679681E-3</v>
       </c>
       <c r="J15" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G16)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.7313593539703903E-3</v>
       </c>
       <c r="K15" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G16)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.7313593539703903E-3</v>
       </c>
       <c r="L15" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G16)*0.85</f>
-        <v>2.1420000000000002E-3</v>
+        <v>1.2985195154777928E-3</v>
       </c>
       <c r="M15" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G16)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.7313593539703903E-3</v>
       </c>
       <c r="N15" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G16)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.7313593539703903E-3</v>
       </c>
       <c r="O15" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G16)*0.85</f>
-        <v>5.7120000000000001E-3</v>
+        <v>3.4627187079407807E-3</v>
       </c>
       <c r="P15" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G16)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.7313593539703903E-3</v>
       </c>
       <c r="Q15" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G16)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.7313593539703903E-3</v>
       </c>
       <c r="R15" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G16)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.7313593539703903E-3</v>
       </c>
       <c r="S15" s="8">
-        <v>0.40879999999999994</v>
+        <v>2.5970390309555855E-3</v>
       </c>
       <c r="T15" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G16)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>2.5970390309555855E-3</v>
       </c>
       <c r="U15" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G16)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>2.5970390309555855E-3</v>
       </c>
       <c r="V15" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G16)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>2.5970390309555855E-3</v>
       </c>
       <c r="W15" s="7">
-        <v>0.36464999999999997</v>
+        <v>2.5970390309555855E-3</v>
       </c>
       <c r="X15" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G16)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>2.5970390309555855E-3</v>
       </c>
       <c r="Y15" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G16)*0.85</f>
-        <v>1.9991999999999999E-2</v>
+        <v>1.2119515477792732E-2</v>
       </c>
       <c r="Z15" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G16)*0.85</f>
-        <v>1.9991999999999999E-2</v>
+        <v>1.2119515477792732E-2</v>
       </c>
       <c r="AA15" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G16)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.7313593539703903E-3</v>
       </c>
       <c r="AB15" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G16)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.7313593539703903E-3</v>
       </c>
       <c r="AC15" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G16)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.7313593539703903E-3</v>
       </c>
       <c r="AD15" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G16)*0.85</f>
-        <v>5.7120000000000001E-3</v>
+        <v>3.4627187079407807E-3</v>
       </c>
       <c r="AE15" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G16)*0.85</f>
-        <v>9.5200000000000007E-3</v>
+        <v>5.7711978465679681E-3</v>
       </c>
       <c r="AF15" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G16)*0.85</f>
-        <v>7.1399999999999996E-3</v>
+        <v>4.3283983849259754E-3</v>
       </c>
       <c r="AG15" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G16)*0.85</f>
-        <v>9.9959999999999997E-3</v>
+        <v>6.0597577388963658E-3</v>
       </c>
       <c r="AH15" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G16)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.7313593539703903E-3</v>
       </c>
     </row>
     <row r="16" spans="1:34" x14ac:dyDescent="0.3">
@@ -3439,134 +2225,103 @@
         <v>0.58333333333333404</v>
       </c>
       <c r="B16" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G17)*0.85</f>
         <v>0</v>
       </c>
       <c r="C16" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G17)*0.85</f>
-        <v>4.7600000000000003E-3</v>
+        <v>2.9555964000000001E-3</v>
       </c>
       <c r="D16" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G17)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>2.6600147999999999E-3</v>
       </c>
       <c r="E16" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G17)*0.85</f>
-        <v>4.7600000000000003E-3</v>
+        <v>3.5466498000000001E-3</v>
       </c>
       <c r="F16" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G17)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.7733512786002692E-3</v>
       </c>
       <c r="G16" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G17)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.7733512786002692E-3</v>
       </c>
       <c r="H16" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G17)*0.85</f>
-        <v>9.5200000000000007E-3</v>
+        <v>5.9111709286675633E-3</v>
       </c>
       <c r="I16" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G17)*0.85</f>
-        <v>9.5200000000000007E-3</v>
+        <v>5.9111709286675633E-3</v>
       </c>
       <c r="J16" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G17)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.7733512786002692E-3</v>
       </c>
       <c r="K16" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G17)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.7733512786002692E-3</v>
       </c>
       <c r="L16" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G17)*0.85</f>
-        <v>2.1420000000000002E-3</v>
+        <v>1.3300134589502017E-3</v>
       </c>
       <c r="M16" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G17)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.7733512786002692E-3</v>
       </c>
       <c r="N16" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G17)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.7733512786002692E-3</v>
       </c>
       <c r="O16" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G17)*0.85</f>
-        <v>5.7120000000000001E-3</v>
+        <v>3.5467025572005384E-3</v>
       </c>
       <c r="P16" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G17)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.7733512786002692E-3</v>
       </c>
       <c r="Q16" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G17)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.7733512786002692E-3</v>
       </c>
       <c r="R16" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G17)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.7733512786002692E-3</v>
       </c>
       <c r="S16" s="8">
-        <v>0.40879999999999994</v>
+        <v>2.6600269179004035E-3</v>
       </c>
       <c r="T16" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G17)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>2.6600269179004035E-3</v>
       </c>
       <c r="U16" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G17)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>2.6600269179004035E-3</v>
       </c>
       <c r="V16" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G17)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>2.6600269179004035E-3</v>
       </c>
       <c r="W16" s="7">
-        <v>0.30769999999999997</v>
+        <v>2.6600269179004035E-3</v>
       </c>
       <c r="X16" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G17)*0.85</f>
-        <v>4.2840000000000005E-3</v>
+        <v>2.6600269179004035E-3</v>
       </c>
       <c r="Y16" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G17)*0.85</f>
-        <v>1.9991999999999999E-2</v>
+        <v>1.2413458950201883E-2</v>
       </c>
       <c r="Z16" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G17)*0.85</f>
-        <v>1.9991999999999999E-2</v>
+        <v>1.2413458950201883E-2</v>
       </c>
       <c r="AA16" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G17)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.7733512786002692E-3</v>
       </c>
       <c r="AB16" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G17)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.7733512786002692E-3</v>
       </c>
       <c r="AC16" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G17)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.7733512786002692E-3</v>
       </c>
       <c r="AD16" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G17)*0.85</f>
-        <v>5.7120000000000001E-3</v>
+        <v>3.5467025572005384E-3</v>
       </c>
       <c r="AE16" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G17)*0.85</f>
-        <v>9.5200000000000007E-3</v>
+        <v>5.9111709286675633E-3</v>
       </c>
       <c r="AF16" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G17)*0.85</f>
-        <v>7.1399999999999996E-3</v>
+        <v>4.4333781965006725E-3</v>
       </c>
       <c r="AG16" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G17)*0.85</f>
-        <v>9.9959999999999997E-3</v>
+        <v>6.2067294751009415E-3</v>
       </c>
       <c r="AH16" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G17)*0.85</f>
-        <v>2.856E-3</v>
+        <v>1.7733512786002692E-3</v>
       </c>
     </row>
     <row r="17" spans="1:34" x14ac:dyDescent="0.3">
@@ -3574,134 +2329,103 @@
         <v>0.625</v>
       </c>
       <c r="B17" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G18)*0.85</f>
         <v>0</v>
       </c>
       <c r="C17" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G18)*0.85</f>
-        <v>5.5405550000000008E-3</v>
+        <v>5.8573567999999996E-3</v>
       </c>
       <c r="D17" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G18)*0.85</f>
-        <v>4.9864994999999999E-3</v>
+        <v>5.2715775999999997E-3</v>
       </c>
       <c r="E17" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G18)*0.85</f>
-        <v>5.5405550000000008E-3</v>
+        <v>7.0286976000000006E-3</v>
       </c>
       <c r="F17" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G18)*0.85</f>
-        <v>3.3243330000000005E-3</v>
+        <v>3.5144010767160158E-3</v>
       </c>
       <c r="G17" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G18)*0.85</f>
-        <v>3.3243330000000005E-3</v>
+        <v>3.5144010767160158E-3</v>
       </c>
       <c r="H17" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G18)*0.85</f>
-        <v>1.1081110000000002E-2</v>
+        <v>1.1714670255720053E-2</v>
       </c>
       <c r="I17" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G18)*0.85</f>
-        <v>1.1081110000000002E-2</v>
+        <v>1.1714670255720053E-2</v>
       </c>
       <c r="J17" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G18)*0.85</f>
-        <v>3.3243330000000005E-3</v>
+        <v>3.5144010767160158E-3</v>
       </c>
       <c r="K17" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G18)*0.85</f>
-        <v>3.3243330000000005E-3</v>
+        <v>3.5144010767160158E-3</v>
       </c>
       <c r="L17" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G18)*0.85</f>
-        <v>2.4932497499999999E-3</v>
+        <v>2.6358008075370119E-3</v>
       </c>
       <c r="M17" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G18)*0.85</f>
-        <v>3.3243330000000005E-3</v>
+        <v>3.5144010767160158E-3</v>
       </c>
       <c r="N17" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G18)*0.85</f>
-        <v>3.3243330000000005E-3</v>
+        <v>3.5144010767160158E-3</v>
       </c>
       <c r="O17" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G18)*0.85</f>
-        <v>6.648666000000001E-3</v>
+        <v>7.0288021534320316E-3</v>
       </c>
       <c r="P17" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G18)*0.85</f>
-        <v>3.3243330000000005E-3</v>
+        <v>3.5144010767160158E-3</v>
       </c>
       <c r="Q17" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G18)*0.85</f>
-        <v>3.3243330000000005E-3</v>
+        <v>3.5144010767160158E-3</v>
       </c>
       <c r="R17" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G18)*0.85</f>
-        <v>3.3243330000000005E-3</v>
+        <v>3.5144010767160158E-3</v>
       </c>
       <c r="S17" s="8">
-        <v>0.40879999999999994</v>
+        <v>5.2716016150740237E-3</v>
       </c>
       <c r="T17" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G18)*0.85</f>
-        <v>4.9864994999999999E-3</v>
+        <v>5.2716016150740237E-3</v>
       </c>
       <c r="U17" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G18)*0.85</f>
-        <v>4.9864994999999999E-3</v>
+        <v>5.2716016150740237E-3</v>
       </c>
       <c r="V17" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G18)*0.85</f>
-        <v>4.9864994999999999E-3</v>
+        <v>5.2716016150740237E-3</v>
       </c>
       <c r="W17" s="7">
-        <v>0.22355</v>
+        <v>5.2716016150740237E-3</v>
       </c>
       <c r="X17" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G18)*0.85</f>
-        <v>4.9864994999999999E-3</v>
+        <v>5.2716016150740237E-3</v>
       </c>
       <c r="Y17" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G18)*0.85</f>
-        <v>2.3270330999999998E-2</v>
+        <v>2.4600807537012111E-2</v>
       </c>
       <c r="Z17" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G18)*0.85</f>
-        <v>2.3270330999999998E-2</v>
+        <v>2.4600807537012111E-2</v>
       </c>
       <c r="AA17" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G18)*0.85</f>
-        <v>3.3243330000000005E-3</v>
+        <v>3.5144010767160158E-3</v>
       </c>
       <c r="AB17" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G18)*0.85</f>
-        <v>3.3243330000000005E-3</v>
+        <v>3.5144010767160158E-3</v>
       </c>
       <c r="AC17" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G18)*0.85</f>
-        <v>3.3243330000000005E-3</v>
+        <v>3.5144010767160158E-3</v>
       </c>
       <c r="AD17" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G18)*0.85</f>
-        <v>6.648666000000001E-3</v>
+        <v>7.0288021534320316E-3</v>
       </c>
       <c r="AE17" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G18)*0.85</f>
-        <v>1.1081110000000002E-2</v>
+        <v>1.1714670255720053E-2</v>
       </c>
       <c r="AF17" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G18)*0.85</f>
-        <v>8.3108325000000004E-3</v>
+        <v>8.7860026917900395E-3</v>
       </c>
       <c r="AG17" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G18)*0.85</f>
-        <v>1.1635165499999999E-2</v>
+        <v>1.2300403768506055E-2</v>
       </c>
       <c r="AH17" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G18)*0.85</f>
-        <v>3.3243330000000005E-3</v>
+        <v>3.5144010767160158E-3</v>
       </c>
     </row>
     <row r="18" spans="1:34" x14ac:dyDescent="0.3">
@@ -3709,134 +2433,103 @@
         <v>0.66666666666666696</v>
       </c>
       <c r="B18" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G19)*0.85</f>
         <v>0</v>
       </c>
       <c r="C18" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G19)*0.85</f>
-        <v>3.5899750000000001E-2</v>
+        <v>1.2086639606E-2</v>
       </c>
       <c r="D18" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G19)*0.85</f>
-        <v>3.2309774999999999E-2</v>
+        <v>1.0877885842000001E-2</v>
       </c>
       <c r="E18" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G19)*0.85</f>
-        <v>3.5899750000000001E-2</v>
+        <v>1.4503698117000002E-2</v>
       </c>
       <c r="F18" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G19)*0.85</f>
-        <v>2.1539849999999999E-2</v>
+        <v>7.2519569313593537E-3</v>
       </c>
       <c r="G18" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G19)*0.85</f>
-        <v>2.1539849999999999E-2</v>
+        <v>7.2519569313593537E-3</v>
       </c>
       <c r="H18" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G19)*0.85</f>
-        <v>7.1799500000000002E-2</v>
+        <v>2.4173189771197846E-2</v>
       </c>
       <c r="I18" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G19)*0.85</f>
-        <v>7.1799500000000002E-2</v>
+        <v>2.4173189771197846E-2</v>
       </c>
       <c r="J18" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G19)*0.85</f>
-        <v>2.1539849999999999E-2</v>
+        <v>7.2519569313593537E-3</v>
       </c>
       <c r="K18" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G19)*0.85</f>
-        <v>2.1539849999999999E-2</v>
+        <v>7.2519569313593537E-3</v>
       </c>
       <c r="L18" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G19)*0.85</f>
-        <v>1.6154887499999999E-2</v>
+        <v>5.4389676985195159E-3</v>
       </c>
       <c r="M18" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G19)*0.85</f>
-        <v>2.1539849999999999E-2</v>
+        <v>7.2519569313593537E-3</v>
       </c>
       <c r="N18" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G19)*0.85</f>
-        <v>2.1539849999999999E-2</v>
+        <v>7.2519569313593537E-3</v>
       </c>
       <c r="O18" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G19)*0.85</f>
-        <v>4.3079699999999999E-2</v>
+        <v>1.4503913862718707E-2</v>
       </c>
       <c r="P18" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G19)*0.85</f>
-        <v>2.1539849999999999E-2</v>
+        <v>7.2519569313593537E-3</v>
       </c>
       <c r="Q18" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G19)*0.85</f>
-        <v>2.1539849999999999E-2</v>
+        <v>7.2519569313593537E-3</v>
       </c>
       <c r="R18" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G19)*0.85</f>
-        <v>2.1539849999999999E-2</v>
+        <v>7.2519569313593537E-3</v>
       </c>
       <c r="S18" s="8">
-        <v>0.33319999999999994</v>
+        <v>1.0877935397039032E-2</v>
       </c>
       <c r="T18" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G19)*0.85</f>
-        <v>3.2309774999999999E-2</v>
+        <v>1.0877935397039032E-2</v>
       </c>
       <c r="U18" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G19)*0.85</f>
-        <v>3.2309774999999999E-2</v>
+        <v>1.0877935397039032E-2</v>
       </c>
       <c r="V18" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G19)*0.85</f>
-        <v>3.2309774999999999E-2</v>
+        <v>1.0877935397039032E-2</v>
       </c>
       <c r="W18" s="7">
-        <v>0.12834999999999999</v>
+        <v>1.0877935397039032E-2</v>
       </c>
       <c r="X18" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G19)*0.85</f>
-        <v>3.2309774999999999E-2</v>
+        <v>1.0877935397039032E-2</v>
       </c>
       <c r="Y18" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G19)*0.85</f>
-        <v>0.15077894999999999</v>
+        <v>5.0763698519515475E-2</v>
       </c>
       <c r="Z18" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G19)*0.85</f>
-        <v>0.15077894999999999</v>
+        <v>5.0763698519515475E-2</v>
       </c>
       <c r="AA18" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G19)*0.85</f>
-        <v>2.1539849999999999E-2</v>
+        <v>7.2519569313593537E-3</v>
       </c>
       <c r="AB18" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G19)*0.85</f>
-        <v>2.1539849999999999E-2</v>
+        <v>7.2519569313593537E-3</v>
       </c>
       <c r="AC18" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G19)*0.85</f>
-        <v>2.1539849999999999E-2</v>
+        <v>7.2519569313593537E-3</v>
       </c>
       <c r="AD18" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G19)*0.85</f>
-        <v>4.3079699999999999E-2</v>
+        <v>1.4503913862718707E-2</v>
       </c>
       <c r="AE18" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G19)*0.85</f>
-        <v>7.1799500000000002E-2</v>
+        <v>2.4173189771197846E-2</v>
       </c>
       <c r="AF18" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G19)*0.85</f>
-        <v>5.3849624999999991E-2</v>
+        <v>1.8129892328398383E-2</v>
       </c>
       <c r="AG18" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G19)*0.85</f>
-        <v>7.5389474999999997E-2</v>
+        <v>2.5381849259757738E-2</v>
       </c>
       <c r="AH18" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G19)*0.85</f>
-        <v>2.1539849999999999E-2</v>
+        <v>7.2519569313593537E-3</v>
       </c>
     </row>
     <row r="19" spans="1:34" x14ac:dyDescent="0.3">
@@ -3844,134 +2537,103 @@
         <v>0.70833333333333404</v>
       </c>
       <c r="B19" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G20)*0.85</f>
         <v>0</v>
       </c>
       <c r="C19" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G20)*0.85</f>
-        <v>7.4271555000000003E-2</v>
+        <v>2.8201988600000002E-2</v>
       </c>
       <c r="D19" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G20)*0.85</f>
-        <v>6.6844399499999985E-2</v>
+        <v>2.5381580200000003E-2</v>
       </c>
       <c r="E19" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G20)*0.85</f>
-        <v>7.4271555000000003E-2</v>
+        <v>3.3841757700000002E-2</v>
       </c>
       <c r="F19" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G20)*0.85</f>
-        <v>4.4562932999999999E-2</v>
+        <v>1.692113055181696E-2</v>
       </c>
       <c r="G19" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G20)*0.85</f>
-        <v>4.4562932999999999E-2</v>
+        <v>1.692113055181696E-2</v>
       </c>
       <c r="H19" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G20)*0.85</f>
-        <v>0.14854311000000001</v>
+        <v>5.640376850605653E-2</v>
       </c>
       <c r="I19" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G20)*0.85</f>
-        <v>0.14854311000000001</v>
+        <v>5.640376850605653E-2</v>
       </c>
       <c r="J19" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G20)*0.85</f>
-        <v>4.4562932999999999E-2</v>
+        <v>1.692113055181696E-2</v>
       </c>
       <c r="K19" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G20)*0.85</f>
-        <v>4.4562932999999999E-2</v>
+        <v>1.692113055181696E-2</v>
       </c>
       <c r="L19" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G20)*0.85</f>
-        <v>3.3422199749999992E-2</v>
+        <v>1.269084791386272E-2</v>
       </c>
       <c r="M19" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G20)*0.85</f>
-        <v>4.4562932999999999E-2</v>
+        <v>1.692113055181696E-2</v>
       </c>
       <c r="N19" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G20)*0.85</f>
-        <v>4.4562932999999999E-2</v>
+        <v>1.692113055181696E-2</v>
       </c>
       <c r="O19" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G20)*0.85</f>
-        <v>8.9125865999999998E-2</v>
+        <v>3.3842261103633919E-2</v>
       </c>
       <c r="P19" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G20)*0.85</f>
-        <v>4.4562932999999999E-2</v>
+        <v>1.692113055181696E-2</v>
       </c>
       <c r="Q19" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G20)*0.85</f>
-        <v>4.4562932999999999E-2</v>
+        <v>1.692113055181696E-2</v>
       </c>
       <c r="R19" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G20)*0.85</f>
-        <v>4.4562932999999999E-2</v>
+        <v>1.692113055181696E-2</v>
       </c>
       <c r="S19" s="8">
-        <v>0.33319999999999994</v>
+        <v>2.538169582772544E-2</v>
       </c>
       <c r="T19" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G20)*0.85</f>
-        <v>6.6844399499999985E-2</v>
+        <v>2.538169582772544E-2</v>
       </c>
       <c r="U19" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G20)*0.85</f>
-        <v>6.6844399499999985E-2</v>
+        <v>2.538169582772544E-2</v>
       </c>
       <c r="V19" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G20)*0.85</f>
-        <v>6.6844399499999985E-2</v>
+        <v>2.538169582772544E-2</v>
       </c>
       <c r="W19" s="7">
-        <v>5.525E-2</v>
+        <v>2.538169582772544E-2</v>
       </c>
       <c r="X19" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G20)*0.85</f>
-        <v>6.6844399499999985E-2</v>
+        <v>2.538169582772544E-2</v>
       </c>
       <c r="Y19" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G20)*0.85</f>
-        <v>0.31194053099999997</v>
+        <v>0.1184479138627187</v>
       </c>
       <c r="Z19" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G20)*0.85</f>
-        <v>0.31194053099999997</v>
+        <v>0.1184479138627187</v>
       </c>
       <c r="AA19" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G20)*0.85</f>
-        <v>4.4562932999999999E-2</v>
+        <v>1.692113055181696E-2</v>
       </c>
       <c r="AB19" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G20)*0.85</f>
-        <v>4.4562932999999999E-2</v>
+        <v>1.692113055181696E-2</v>
       </c>
       <c r="AC19" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G20)*0.85</f>
-        <v>4.4562932999999999E-2</v>
+        <v>1.692113055181696E-2</v>
       </c>
       <c r="AD19" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G20)*0.85</f>
-        <v>8.9125865999999998E-2</v>
+        <v>3.3842261103633919E-2</v>
       </c>
       <c r="AE19" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G20)*0.85</f>
-        <v>0.14854311000000001</v>
+        <v>5.640376850605653E-2</v>
       </c>
       <c r="AF19" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G20)*0.85</f>
-        <v>0.1114073325</v>
+        <v>4.2302826379542392E-2</v>
       </c>
       <c r="AG19" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G20)*0.85</f>
-        <v>0.15597026549999998</v>
+        <v>5.9223956931359352E-2</v>
       </c>
       <c r="AH19" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G20)*0.85</f>
-        <v>4.4562932999999999E-2</v>
+        <v>1.692113055181696E-2</v>
       </c>
     </row>
     <row r="20" spans="1:34" x14ac:dyDescent="0.3">
@@ -3979,134 +2641,103 @@
         <v>0.750000000000001</v>
       </c>
       <c r="B20" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G21)*0.85</f>
         <v>0</v>
       </c>
       <c r="C20" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G21)*0.85</f>
-        <v>6.0096445000000005E-2</v>
+        <v>3.1136938894000002E-2</v>
       </c>
       <c r="D20" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G21)*0.85</f>
-        <v>5.408680049999999E-2</v>
+        <v>2.8023013658000001E-2</v>
       </c>
       <c r="E20" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G21)*0.85</f>
-        <v>6.0096445000000005E-2</v>
+        <v>3.7363632633000007E-2</v>
       </c>
       <c r="F20" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G21)*0.85</f>
-        <v>3.6057866999999993E-2</v>
+        <v>1.8682094212651414E-2</v>
       </c>
       <c r="G20" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G21)*0.85</f>
-        <v>3.6057866999999993E-2</v>
+        <v>1.8682094212651414E-2</v>
       </c>
       <c r="H20" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G21)*0.85</f>
-        <v>0.12019289000000001</v>
+        <v>6.2273647375504712E-2</v>
       </c>
       <c r="I20" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G21)*0.85</f>
-        <v>0.12019289000000001</v>
+        <v>6.2273647375504712E-2</v>
       </c>
       <c r="J20" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G21)*0.85</f>
-        <v>3.6057866999999993E-2</v>
+        <v>1.8682094212651414E-2</v>
       </c>
       <c r="K20" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G21)*0.85</f>
-        <v>3.6057866999999993E-2</v>
+        <v>1.8682094212651414E-2</v>
       </c>
       <c r="L20" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G21)*0.85</f>
-        <v>2.7043400249999995E-2</v>
+        <v>1.401157065948856E-2</v>
       </c>
       <c r="M20" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G21)*0.85</f>
-        <v>3.6057866999999993E-2</v>
+        <v>1.8682094212651414E-2</v>
       </c>
       <c r="N20" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G21)*0.85</f>
-        <v>3.6057866999999993E-2</v>
+        <v>1.8682094212651414E-2</v>
       </c>
       <c r="O20" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G21)*0.85</f>
-        <v>7.2115733999999987E-2</v>
+        <v>3.7364188425302827E-2</v>
       </c>
       <c r="P20" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G21)*0.85</f>
-        <v>3.6057866999999993E-2</v>
+        <v>1.8682094212651414E-2</v>
       </c>
       <c r="Q20" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G21)*0.85</f>
-        <v>3.6057866999999993E-2</v>
+        <v>1.8682094212651414E-2</v>
       </c>
       <c r="R20" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G21)*0.85</f>
-        <v>3.6057866999999993E-2</v>
+        <v>1.8682094212651414E-2</v>
       </c>
       <c r="S20" s="8">
-        <v>0.33319999999999994</v>
+        <v>2.802314131897712E-2</v>
       </c>
       <c r="T20" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G21)*0.85</f>
-        <v>5.408680049999999E-2</v>
+        <v>2.802314131897712E-2</v>
       </c>
       <c r="U20" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G21)*0.85</f>
-        <v>5.408680049999999E-2</v>
+        <v>2.802314131897712E-2</v>
       </c>
       <c r="V20" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G21)*0.85</f>
-        <v>5.408680049999999E-2</v>
+        <v>2.802314131897712E-2</v>
       </c>
       <c r="W20" s="7">
-        <v>8.5000000000000006E-3</v>
+        <v>2.802314131897712E-2</v>
       </c>
       <c r="X20" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G21)*0.85</f>
-        <v>5.408680049999999E-2</v>
+        <v>2.802314131897712E-2</v>
       </c>
       <c r="Y20" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G21)*0.85</f>
-        <v>0.25240506899999998</v>
+        <v>0.13077465948855987</v>
       </c>
       <c r="Z20" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G21)*0.85</f>
-        <v>0.25240506899999998</v>
+        <v>0.13077465948855987</v>
       </c>
       <c r="AA20" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G21)*0.85</f>
-        <v>3.6057866999999993E-2</v>
+        <v>1.8682094212651414E-2</v>
       </c>
       <c r="AB20" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G21)*0.85</f>
-        <v>3.6057866999999993E-2</v>
+        <v>1.8682094212651414E-2</v>
       </c>
       <c r="AC20" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G21)*0.85</f>
-        <v>3.6057866999999993E-2</v>
+        <v>1.8682094212651414E-2</v>
       </c>
       <c r="AD20" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G21)*0.85</f>
-        <v>7.2115733999999987E-2</v>
+        <v>3.7364188425302827E-2</v>
       </c>
       <c r="AE20" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G21)*0.85</f>
-        <v>0.12019289000000001</v>
+        <v>6.2273647375504712E-2</v>
       </c>
       <c r="AF20" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G21)*0.85</f>
-        <v>9.0144667499999998E-2</v>
+        <v>4.6705235531628531E-2</v>
       </c>
       <c r="AG20" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G21)*0.85</f>
-        <v>0.12620253449999999</v>
+        <v>6.5387329744279937E-2</v>
       </c>
       <c r="AH20" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G21)*0.85</f>
-        <v>3.6057866999999993E-2</v>
+        <v>1.8682094212651414E-2</v>
       </c>
     </row>
     <row r="21" spans="1:34" x14ac:dyDescent="0.3">
@@ -4114,134 +2745,103 @@
         <v>0.79166666666666696</v>
       </c>
       <c r="B21" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G22)*0.85</f>
         <v>0</v>
       </c>
       <c r="C21" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G22)*0.85</f>
-        <v>4.9849694999999992E-2</v>
+        <v>1.7637561893999999E-2</v>
       </c>
       <c r="D21" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G22)*0.85</f>
-        <v>4.4864725499999994E-2</v>
+        <v>1.5873674657999999E-2</v>
       </c>
       <c r="E21" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G22)*0.85</f>
-        <v>4.9849694999999992E-2</v>
+        <v>2.1164681133000001E-2</v>
       </c>
       <c r="F21" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G22)*0.85</f>
-        <v>2.9909816999999995E-2</v>
+        <v>1.0582497981157469E-2</v>
       </c>
       <c r="G21" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G22)*0.85</f>
-        <v>2.9909816999999995E-2</v>
+        <v>1.0582497981157469E-2</v>
       </c>
       <c r="H21" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G22)*0.85</f>
-        <v>9.9699389999999985E-2</v>
+        <v>3.5274993270524899E-2</v>
       </c>
       <c r="I21" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G22)*0.85</f>
-        <v>9.9699389999999985E-2</v>
+        <v>3.5274993270524899E-2</v>
       </c>
       <c r="J21" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G22)*0.85</f>
-        <v>2.9909816999999995E-2</v>
+        <v>1.0582497981157469E-2</v>
       </c>
       <c r="K21" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G22)*0.85</f>
-        <v>2.9909816999999995E-2</v>
+        <v>1.0582497981157469E-2</v>
       </c>
       <c r="L21" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G22)*0.85</f>
-        <v>2.2432362749999997E-2</v>
+        <v>7.9368734858681015E-3</v>
       </c>
       <c r="M21" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G22)*0.85</f>
-        <v>2.9909816999999995E-2</v>
+        <v>1.0582497981157469E-2</v>
       </c>
       <c r="N21" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G22)*0.85</f>
-        <v>2.9909816999999995E-2</v>
+        <v>1.0582497981157469E-2</v>
       </c>
       <c r="O21" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G22)*0.85</f>
-        <v>5.981963399999999E-2</v>
+        <v>2.1164995962314938E-2</v>
       </c>
       <c r="P21" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G22)*0.85</f>
-        <v>2.9909816999999995E-2</v>
+        <v>1.0582497981157469E-2</v>
       </c>
       <c r="Q21" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G22)*0.85</f>
-        <v>2.9909816999999995E-2</v>
+        <v>1.0582497981157469E-2</v>
       </c>
       <c r="R21" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G22)*0.85</f>
-        <v>2.9909816999999995E-2</v>
+        <v>1.0582497981157469E-2</v>
       </c>
       <c r="S21" s="8">
-        <v>0.33319999999999994</v>
+        <v>1.5873746971736203E-2</v>
       </c>
       <c r="T21" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G22)*0.85</f>
-        <v>4.4864725499999994E-2</v>
+        <v>1.5873746971736203E-2</v>
       </c>
       <c r="U21" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G22)*0.85</f>
-        <v>4.4864725499999994E-2</v>
+        <v>1.5873746971736203E-2</v>
       </c>
       <c r="V21" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G22)*0.85</f>
-        <v>4.4864725499999994E-2</v>
+        <v>1.5873746971736203E-2</v>
       </c>
       <c r="W21" s="7">
-        <v>0</v>
+        <v>1.5873746971736203E-2</v>
       </c>
       <c r="X21" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G22)*0.85</f>
-        <v>4.4864725499999994E-2</v>
+        <v>1.5873746971736203E-2</v>
       </c>
       <c r="Y21" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G22)*0.85</f>
-        <v>0.20936871899999995</v>
+        <v>7.4077485868102283E-2</v>
       </c>
       <c r="Z21" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G22)*0.85</f>
-        <v>0.20936871899999995</v>
+        <v>7.4077485868102283E-2</v>
       </c>
       <c r="AA21" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G22)*0.85</f>
-        <v>2.9909816999999995E-2</v>
+        <v>1.0582497981157469E-2</v>
       </c>
       <c r="AB21" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G22)*0.85</f>
-        <v>2.9909816999999995E-2</v>
+        <v>1.0582497981157469E-2</v>
       </c>
       <c r="AC21" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G22)*0.85</f>
-        <v>2.9909816999999995E-2</v>
+        <v>1.0582497981157469E-2</v>
       </c>
       <c r="AD21" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G22)*0.85</f>
-        <v>5.981963399999999E-2</v>
+        <v>2.1164995962314938E-2</v>
       </c>
       <c r="AE21" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G22)*0.85</f>
-        <v>9.9699389999999985E-2</v>
+        <v>3.5274993270524899E-2</v>
       </c>
       <c r="AF21" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G22)*0.85</f>
-        <v>7.4774542499999999E-2</v>
+        <v>2.6456244952893671E-2</v>
       </c>
       <c r="AG21" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G22)*0.85</f>
-        <v>0.10468435949999998</v>
+        <v>3.7038742934051141E-2</v>
       </c>
       <c r="AH21" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G22)*0.85</f>
-        <v>2.9909816999999995E-2</v>
+        <v>1.0582497981157469E-2</v>
       </c>
     </row>
     <row r="22" spans="1:34" x14ac:dyDescent="0.3">
@@ -4249,134 +2849,103 @@
         <v>0.83333333333333404</v>
       </c>
       <c r="B22" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G23)*0.85</f>
         <v>0</v>
       </c>
       <c r="C22" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G23)*0.85</f>
-        <v>4.0945945000000004E-2</v>
+        <v>1.5567137005999999E-2</v>
       </c>
       <c r="D22" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G23)*0.85</f>
-        <v>3.6851350499999998E-2</v>
+        <v>1.4010307642E-2</v>
       </c>
       <c r="E22" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G23)*0.85</f>
-        <v>4.0945945000000004E-2</v>
+        <v>1.8680217416999999E-2</v>
       </c>
       <c r="F22" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G23)*0.85</f>
-        <v>2.4567566999999998E-2</v>
+        <v>9.3402476446837138E-3</v>
       </c>
       <c r="G22" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G23)*0.85</f>
-        <v>2.4567566999999998E-2</v>
+        <v>9.3402476446837138E-3</v>
       </c>
       <c r="H22" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G23)*0.85</f>
-        <v>8.1891890000000009E-2</v>
+        <v>3.1134158815612382E-2</v>
       </c>
       <c r="I22" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G23)*0.85</f>
-        <v>8.1891890000000009E-2</v>
+        <v>3.1134158815612382E-2</v>
       </c>
       <c r="J22" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G23)*0.85</f>
-        <v>2.4567566999999998E-2</v>
+        <v>9.3402476446837138E-3</v>
       </c>
       <c r="K22" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G23)*0.85</f>
-        <v>2.4567566999999998E-2</v>
+        <v>9.3402476446837138E-3</v>
       </c>
       <c r="L22" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G23)*0.85</f>
-        <v>1.8425675249999999E-2</v>
+        <v>7.0051857335127858E-3</v>
       </c>
       <c r="M22" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G23)*0.85</f>
-        <v>2.4567566999999998E-2</v>
+        <v>9.3402476446837138E-3</v>
       </c>
       <c r="N22" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G23)*0.85</f>
-        <v>2.4567566999999998E-2</v>
+        <v>9.3402476446837138E-3</v>
       </c>
       <c r="O22" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G23)*0.85</f>
-        <v>4.9135133999999997E-2</v>
+        <v>1.8680495289367428E-2</v>
       </c>
       <c r="P22" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G23)*0.85</f>
-        <v>2.4567566999999998E-2</v>
+        <v>9.3402476446837138E-3</v>
       </c>
       <c r="Q22" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G23)*0.85</f>
-        <v>2.4567566999999998E-2</v>
+        <v>9.3402476446837138E-3</v>
       </c>
       <c r="R22" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G23)*0.85</f>
-        <v>2.4567566999999998E-2</v>
+        <v>9.3402476446837138E-3</v>
       </c>
       <c r="S22" s="8">
-        <v>0.33319999999999994</v>
+        <v>1.4010371467025572E-2</v>
       </c>
       <c r="T22" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G23)*0.85</f>
-        <v>3.6851350499999998E-2</v>
+        <v>1.4010371467025572E-2</v>
       </c>
       <c r="U22" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G23)*0.85</f>
-        <v>3.6851350499999998E-2</v>
+        <v>1.4010371467025572E-2</v>
       </c>
       <c r="V22" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G23)*0.85</f>
-        <v>3.6851350499999998E-2</v>
+        <v>1.4010371467025572E-2</v>
       </c>
       <c r="W22" s="7">
-        <v>0</v>
+        <v>1.4010371467025572E-2</v>
       </c>
       <c r="X22" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G23)*0.85</f>
-        <v>3.6851350499999998E-2</v>
+        <v>1.4010371467025572E-2</v>
       </c>
       <c r="Y22" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G23)*0.85</f>
-        <v>0.17197296899999998</v>
+        <v>6.5381733512785992E-2</v>
       </c>
       <c r="Z22" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G23)*0.85</f>
-        <v>0.17197296899999998</v>
+        <v>6.5381733512785992E-2</v>
       </c>
       <c r="AA22" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G23)*0.85</f>
-        <v>2.4567566999999998E-2</v>
+        <v>9.3402476446837138E-3</v>
       </c>
       <c r="AB22" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G23)*0.85</f>
-        <v>2.4567566999999998E-2</v>
+        <v>9.3402476446837138E-3</v>
       </c>
       <c r="AC22" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G23)*0.85</f>
-        <v>2.4567566999999998E-2</v>
+        <v>9.3402476446837138E-3</v>
       </c>
       <c r="AD22" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G23)*0.85</f>
-        <v>4.9135133999999997E-2</v>
+        <v>1.8680495289367428E-2</v>
       </c>
       <c r="AE22" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G23)*0.85</f>
-        <v>8.1891890000000009E-2</v>
+        <v>3.1134158815612382E-2</v>
       </c>
       <c r="AF22" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G23)*0.85</f>
-        <v>6.1418917500000003E-2</v>
+        <v>2.3350619111709284E-2</v>
       </c>
       <c r="AG22" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G23)*0.85</f>
-        <v>8.5986484499999988E-2</v>
+        <v>3.2690866756392996E-2</v>
       </c>
       <c r="AH22" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G23)*0.85</f>
-        <v>2.4567566999999998E-2</v>
+        <v>9.3402476446837138E-3</v>
       </c>
     </row>
     <row r="23" spans="1:34" x14ac:dyDescent="0.3">
@@ -4384,134 +2953,103 @@
         <v>0.875000000000001</v>
       </c>
       <c r="B23" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G24)*0.85</f>
         <v>0</v>
       </c>
       <c r="C23" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G24)*0.85</f>
-        <v>4.6191805000000009E-2</v>
+        <v>1.4632624800000001E-2</v>
       </c>
       <c r="D23" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G24)*0.85</f>
-        <v>4.1572624500000002E-2</v>
+        <v>1.31692536E-2</v>
       </c>
       <c r="E23" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G24)*0.85</f>
-        <v>4.6191805000000009E-2</v>
+        <v>1.7558823600000002E-2</v>
       </c>
       <c r="F23" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G24)*0.85</f>
-        <v>2.7715082999999998E-2</v>
+        <v>8.7795423956931358E-3</v>
       </c>
       <c r="G23" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G24)*0.85</f>
-        <v>2.7715082999999998E-2</v>
+        <v>8.7795423956931358E-3</v>
       </c>
       <c r="H23" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G24)*0.85</f>
-        <v>9.2383610000000019E-2</v>
+        <v>2.9265141318977117E-2</v>
       </c>
       <c r="I23" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G24)*0.85</f>
-        <v>9.2383610000000019E-2</v>
+        <v>2.9265141318977117E-2</v>
       </c>
       <c r="J23" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G24)*0.85</f>
-        <v>2.7715082999999998E-2</v>
+        <v>8.7795423956931358E-3</v>
       </c>
       <c r="K23" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G24)*0.85</f>
-        <v>2.7715082999999998E-2</v>
+        <v>8.7795423956931358E-3</v>
       </c>
       <c r="L23" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G24)*0.85</f>
-        <v>2.0786312250000001E-2</v>
+        <v>6.5846567967698518E-3</v>
       </c>
       <c r="M23" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G24)*0.85</f>
-        <v>2.7715082999999998E-2</v>
+        <v>8.7795423956931358E-3</v>
       </c>
       <c r="N23" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G24)*0.85</f>
-        <v>2.7715082999999998E-2</v>
+        <v>8.7795423956931358E-3</v>
       </c>
       <c r="O23" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G24)*0.85</f>
-        <v>5.5430165999999996E-2</v>
+        <v>1.7559084791386272E-2</v>
       </c>
       <c r="P23" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G24)*0.85</f>
-        <v>2.7715082999999998E-2</v>
+        <v>8.7795423956931358E-3</v>
       </c>
       <c r="Q23" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G24)*0.85</f>
-        <v>2.7715082999999998E-2</v>
+        <v>8.7795423956931358E-3</v>
       </c>
       <c r="R23" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G24)*0.85</f>
-        <v>2.7715082999999998E-2</v>
+        <v>8.7795423956931358E-3</v>
       </c>
       <c r="S23" s="8">
-        <v>0.40879999999999994</v>
+        <v>1.3169313593539704E-2</v>
       </c>
       <c r="T23" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G24)*0.85</f>
-        <v>4.1572624500000002E-2</v>
+        <v>1.3169313593539704E-2</v>
       </c>
       <c r="U23" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G24)*0.85</f>
-        <v>4.1572624500000002E-2</v>
+        <v>1.3169313593539704E-2</v>
       </c>
       <c r="V23" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G24)*0.85</f>
-        <v>4.1572624500000002E-2</v>
+        <v>1.3169313593539704E-2</v>
       </c>
       <c r="W23" s="7">
-        <v>0</v>
+        <v>1.3169313593539704E-2</v>
       </c>
       <c r="X23" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G24)*0.85</f>
-        <v>4.1572624500000002E-2</v>
+        <v>1.3169313593539704E-2</v>
       </c>
       <c r="Y23" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G24)*0.85</f>
-        <v>0.19400558100000001</v>
+        <v>6.1456796769851947E-2</v>
       </c>
       <c r="Z23" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G24)*0.85</f>
-        <v>0.19400558100000001</v>
+        <v>6.1456796769851947E-2</v>
       </c>
       <c r="AA23" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G24)*0.85</f>
-        <v>2.7715082999999998E-2</v>
+        <v>8.7795423956931358E-3</v>
       </c>
       <c r="AB23" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G24)*0.85</f>
-        <v>2.7715082999999998E-2</v>
+        <v>8.7795423956931358E-3</v>
       </c>
       <c r="AC23" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G24)*0.85</f>
-        <v>2.7715082999999998E-2</v>
+        <v>8.7795423956931358E-3</v>
       </c>
       <c r="AD23" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G24)*0.85</f>
-        <v>5.5430165999999996E-2</v>
+        <v>1.7559084791386272E-2</v>
       </c>
       <c r="AE23" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G24)*0.85</f>
-        <v>9.2383610000000019E-2</v>
+        <v>2.9265141318977117E-2</v>
       </c>
       <c r="AF23" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G24)*0.85</f>
-        <v>6.9287707500000004E-2</v>
+        <v>2.1948855989232838E-2</v>
       </c>
       <c r="AG23" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G24)*0.85</f>
-        <v>9.7002790500000005E-2</v>
+        <v>3.0728398384925974E-2</v>
       </c>
       <c r="AH23" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G24)*0.85</f>
-        <v>2.7715082999999998E-2</v>
+        <v>8.7795423956931358E-3</v>
       </c>
     </row>
     <row r="24" spans="1:34" x14ac:dyDescent="0.3">
@@ -4519,134 +3057,103 @@
         <v>0.91666666666666696</v>
       </c>
       <c r="B24" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G25)*0.85</f>
         <v>0</v>
       </c>
       <c r="C24" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G25)*0.85</f>
-        <v>5.817969500000001E-2</v>
+        <v>1.2471109399999999E-2</v>
       </c>
       <c r="D24" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G25)*0.85</f>
-        <v>5.2361725499999998E-2</v>
+        <v>1.12239058E-2</v>
       </c>
       <c r="E24" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G25)*0.85</f>
-        <v>5.817969500000001E-2</v>
+        <v>1.4965053300000001E-2</v>
       </c>
       <c r="F24" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G25)*0.85</f>
-        <v>3.4907817000000001E-2</v>
+        <v>7.4826379542395696E-3</v>
       </c>
       <c r="G24" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G25)*0.85</f>
-        <v>3.4907817000000001E-2</v>
+        <v>7.4826379542395696E-3</v>
       </c>
       <c r="H24" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G25)*0.85</f>
-        <v>0.11635939000000002</v>
+        <v>2.4942126514131899E-2</v>
       </c>
       <c r="I24" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G25)*0.85</f>
-        <v>0.11635939000000002</v>
+        <v>2.4942126514131899E-2</v>
       </c>
       <c r="J24" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G25)*0.85</f>
-        <v>3.4907817000000001E-2</v>
+        <v>7.4826379542395696E-3</v>
       </c>
       <c r="K24" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G25)*0.85</f>
-        <v>3.4907817000000001E-2</v>
+        <v>7.4826379542395696E-3</v>
       </c>
       <c r="L24" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G25)*0.85</f>
-        <v>2.6180862749999999E-2</v>
+        <v>5.6119784656796772E-3</v>
       </c>
       <c r="M24" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G25)*0.85</f>
-        <v>3.4907817000000001E-2</v>
+        <v>7.4826379542395696E-3</v>
       </c>
       <c r="N24" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G25)*0.85</f>
-        <v>3.4907817000000001E-2</v>
+        <v>7.4826379542395696E-3</v>
       </c>
       <c r="O24" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G25)*0.85</f>
-        <v>6.9815634000000001E-2</v>
+        <v>1.4965275908479139E-2</v>
       </c>
       <c r="P24" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G25)*0.85</f>
-        <v>3.4907817000000001E-2</v>
+        <v>7.4826379542395696E-3</v>
       </c>
       <c r="Q24" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G25)*0.85</f>
-        <v>3.4907817000000001E-2</v>
+        <v>7.4826379542395696E-3</v>
       </c>
       <c r="R24" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G25)*0.85</f>
-        <v>3.4907817000000001E-2</v>
+        <v>7.4826379542395696E-3</v>
       </c>
       <c r="S24" s="8">
-        <v>0.40879999999999994</v>
+        <v>1.1223956931359354E-2</v>
       </c>
       <c r="T24" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G25)*0.85</f>
-        <v>5.2361725499999998E-2</v>
+        <v>1.1223956931359354E-2</v>
       </c>
       <c r="U24" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G25)*0.85</f>
-        <v>5.2361725499999998E-2</v>
+        <v>1.1223956931359354E-2</v>
       </c>
       <c r="V24" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G25)*0.85</f>
-        <v>5.2361725499999998E-2</v>
+        <v>1.1223956931359354E-2</v>
       </c>
       <c r="W24" s="7">
-        <v>0</v>
+        <v>1.1223956931359354E-2</v>
       </c>
       <c r="X24" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G25)*0.85</f>
-        <v>5.2361725499999998E-2</v>
+        <v>1.1223956931359354E-2</v>
       </c>
       <c r="Y24" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G25)*0.85</f>
-        <v>0.244354719</v>
+        <v>5.237846567967698E-2</v>
       </c>
       <c r="Z24" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G25)*0.85</f>
-        <v>0.244354719</v>
+        <v>5.237846567967698E-2</v>
       </c>
       <c r="AA24" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G25)*0.85</f>
-        <v>3.4907817000000001E-2</v>
+        <v>7.4826379542395696E-3</v>
       </c>
       <c r="AB24" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G25)*0.85</f>
-        <v>3.4907817000000001E-2</v>
+        <v>7.4826379542395696E-3</v>
       </c>
       <c r="AC24" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G25)*0.85</f>
-        <v>3.4907817000000001E-2</v>
+        <v>7.4826379542395696E-3</v>
       </c>
       <c r="AD24" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G25)*0.85</f>
-        <v>6.9815634000000001E-2</v>
+        <v>1.4965275908479139E-2</v>
       </c>
       <c r="AE24" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G25)*0.85</f>
-        <v>0.11635939000000002</v>
+        <v>2.4942126514131899E-2</v>
       </c>
       <c r="AF24" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G25)*0.85</f>
-        <v>8.7269542499999991E-2</v>
+        <v>1.8706594885598921E-2</v>
       </c>
       <c r="AG24" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G25)*0.85</f>
-        <v>0.1221773595</v>
+        <v>2.618923283983849E-2</v>
       </c>
       <c r="AH24" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G25)*0.85</f>
-        <v>3.4907817000000001E-2</v>
+        <v>7.4826379542395696E-3</v>
       </c>
     </row>
     <row r="25" spans="1:34" x14ac:dyDescent="0.3">
@@ -4654,450 +3161,286 @@
         <v>0.95833333333333404</v>
       </c>
       <c r="B25" s="7">
-        <f>([1]Basic_load!$B$2*[1]Basic_load!G26)*0.85</f>
         <v>0</v>
       </c>
       <c r="C25" s="7">
-        <f>([1]Basic_load!$B$3*[1]Basic_load!G26)*0.85</f>
-        <v>1.00997E-2</v>
+        <v>6.0628218940000003E-3</v>
       </c>
       <c r="D25" s="7">
-        <f>([1]Basic_load!$B$4*[1]Basic_load!G26)*0.85</f>
-        <v>9.089729999999999E-3</v>
+        <v>5.4564946580000001E-3</v>
       </c>
       <c r="E25" s="7">
-        <f>([1]Basic_load!$B$5*[1]Basic_load!G26)*0.85</f>
-        <v>1.00997E-2</v>
+        <v>7.2752511330000007E-3</v>
       </c>
       <c r="F25" s="7">
-        <f>([1]Basic_load!$B$6*[1]Basic_load!G26)*0.85</f>
-        <v>6.0598199999999996E-3</v>
+        <v>3.6376796769851949E-3</v>
       </c>
       <c r="G25" s="7">
-        <f>([1]Basic_load!$B$7*[1]Basic_load!G26)*0.85</f>
-        <v>6.0598199999999996E-3</v>
+        <v>3.6376796769851949E-3</v>
       </c>
       <c r="H25" s="7">
-        <f>([1]Basic_load!$B$8*[1]Basic_load!G26)*0.85</f>
-        <v>2.0199399999999999E-2</v>
+        <v>1.2125598923283984E-2</v>
       </c>
       <c r="I25" s="7">
-        <f>([1]Basic_load!$B$9*[1]Basic_load!G26)*0.85</f>
-        <v>2.0199399999999999E-2</v>
+        <v>1.2125598923283984E-2</v>
       </c>
       <c r="J25" s="7">
-        <f>([1]Basic_load!$B$10*[1]Basic_load!G26)*0.85</f>
-        <v>6.0598199999999996E-3</v>
+        <v>3.6376796769851949E-3</v>
       </c>
       <c r="K25" s="7">
-        <f>([1]Basic_load!$B$11*[1]Basic_load!G26)*0.85</f>
-        <v>6.0598199999999996E-3</v>
+        <v>3.6376796769851949E-3</v>
       </c>
       <c r="L25" s="7">
-        <f>([1]Basic_load!$B$12*[1]Basic_load!G26)*0.85</f>
-        <v>4.5448649999999995E-3</v>
+        <v>2.7282597577388962E-3</v>
       </c>
       <c r="M25" s="7">
-        <f>([1]Basic_load!$B$13*[1]Basic_load!G26)*0.85</f>
-        <v>6.0598199999999996E-3</v>
+        <v>3.6376796769851949E-3</v>
       </c>
       <c r="N25" s="7">
-        <f>([1]Basic_load!$B$14*[1]Basic_load!G26)*0.85</f>
-        <v>6.0598199999999996E-3</v>
+        <v>3.6376796769851949E-3</v>
       </c>
       <c r="O25" s="7">
-        <f>([1]Basic_load!$B$15*[1]Basic_load!G26)*0.85</f>
-        <v>1.2119639999999999E-2</v>
+        <v>7.2753593539703898E-3</v>
       </c>
       <c r="P25" s="7">
-        <f>([1]Basic_load!$B$16*[1]Basic_load!G26)*0.85</f>
-        <v>6.0598199999999996E-3</v>
+        <v>3.6376796769851949E-3</v>
       </c>
       <c r="Q25" s="7">
-        <f>([1]Basic_load!$B$17*[1]Basic_load!G26)*0.85</f>
-        <v>6.0598199999999996E-3</v>
+        <v>3.6376796769851949E-3</v>
       </c>
       <c r="R25" s="7">
-        <f>([1]Basic_load!$B$18*[1]Basic_load!G26)*0.85</f>
-        <v>6.0598199999999996E-3</v>
+        <v>3.6376796769851949E-3</v>
       </c>
       <c r="S25" s="8">
-        <v>0.30869999999999997</v>
+        <v>5.4565195154777923E-3</v>
       </c>
       <c r="T25" s="7">
-        <f>([1]Basic_load!$B$20*[1]Basic_load!G26)*0.85</f>
-        <v>9.089729999999999E-3</v>
+        <v>5.4565195154777923E-3</v>
       </c>
       <c r="U25" s="7">
-        <f>([1]Basic_load!$B$21*[1]Basic_load!G26)*0.85</f>
-        <v>9.089729999999999E-3</v>
+        <v>5.4565195154777923E-3</v>
       </c>
       <c r="V25" s="7">
-        <f>([1]Basic_load!$B$22*[1]Basic_load!G26)*0.85</f>
-        <v>9.089729999999999E-3</v>
+        <v>5.4565195154777923E-3</v>
       </c>
       <c r="W25" s="7">
-        <v>0</v>
+        <v>5.4565195154777923E-3</v>
       </c>
       <c r="X25" s="7">
-        <f>([1]Basic_load!$B$24*[1]Basic_load!G26)*0.85</f>
-        <v>9.089729999999999E-3</v>
+        <v>5.4565195154777923E-3</v>
       </c>
       <c r="Y25" s="7">
-        <f>([1]Basic_load!$B$25*[1]Basic_load!G26)*0.85</f>
-        <v>4.2418739999999996E-2</v>
+        <v>2.5463757738896364E-2</v>
       </c>
       <c r="Z25" s="7">
-        <f>([1]Basic_load!$B$26*[1]Basic_load!G26)*0.85</f>
-        <v>4.2418739999999996E-2</v>
+        <v>2.5463757738896364E-2</v>
       </c>
       <c r="AA25" s="7">
-        <f>([1]Basic_load!$B$27*[1]Basic_load!G26)*0.85</f>
-        <v>6.0598199999999996E-3</v>
+        <v>3.6376796769851949E-3</v>
       </c>
       <c r="AB25" s="7">
-        <f>([1]Basic_load!$B$28*[1]Basic_load!G26)*0.85</f>
-        <v>6.0598199999999996E-3</v>
+        <v>3.6376796769851949E-3</v>
       </c>
       <c r="AC25" s="7">
-        <f>([1]Basic_load!$B$29*[1]Basic_load!G26)*0.85</f>
-        <v>6.0598199999999996E-3</v>
+        <v>3.6376796769851949E-3</v>
       </c>
       <c r="AD25" s="7">
-        <f>([1]Basic_load!$B$30*[1]Basic_load!G26)*0.85</f>
-        <v>1.2119639999999999E-2</v>
+        <v>7.2753593539703898E-3</v>
       </c>
       <c r="AE25" s="7">
-        <f>([1]Basic_load!$B$31*[1]Basic_load!G26)*0.85</f>
-        <v>2.0199399999999999E-2</v>
+        <v>1.2125598923283984E-2</v>
       </c>
       <c r="AF25" s="7">
-        <f>([1]Basic_load!$B$32*[1]Basic_load!G26)*0.85</f>
-        <v>1.5149549999999998E-2</v>
+        <v>9.0941991924629872E-3</v>
       </c>
       <c r="AG25" s="7">
-        <f>([1]Basic_load!$B$33*[1]Basic_load!G26)*0.85</f>
-        <v>2.1209369999999998E-2</v>
+        <v>1.2731878869448182E-2</v>
       </c>
       <c r="AH25" s="7">
-        <f>([1]Basic_load!$B$34*[1]Basic_load!G26)*0.85</f>
-        <v>6.0598199999999996E-3</v>
+        <v>3.6376796769851949E-3</v>
       </c>
     </row>
     <row r="26" spans="1:34" x14ac:dyDescent="0.3">
       <c r="S26" s="8"/>
     </row>
     <row r="27" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="S27" s="8">
-        <v>0.85</v>
-      </c>
+      <c r="S27" s="8"/>
     </row>
     <row r="28" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="C28" s="7">
+      <c r="A28" s="7">
         <f>SUM(B2:AH2)</f>
-        <v>0.47601400000000005</v>
-      </c>
-      <c r="G28" s="7">
-        <v>0.85</v>
+        <v>6.4599968265141319E-2</v>
       </c>
       <c r="S28" s="8"/>
     </row>
     <row r="29" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="C29" s="7">
-        <f>SUM(B3:AH3)</f>
-        <v>0.47601400000000005</v>
-      </c>
-      <c r="Y29" s="7">
-        <v>0.85</v>
+      <c r="A29" s="7">
+        <f t="shared" ref="A29:A52" si="0">SUM(B3:AH3)</f>
+        <v>9.9399951169582765E-2</v>
       </c>
     </row>
     <row r="30" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="C30" s="7">
-        <f>SUM(B4:AH4)</f>
-        <v>0.47601400000000005</v>
-      </c>
-      <c r="Z30" s="7">
-        <v>18</v>
-      </c>
-      <c r="AA30" s="7">
-        <v>22</v>
+      <c r="A30" s="7">
+        <f t="shared" si="0"/>
+        <v>0.15349992459286682</v>
       </c>
     </row>
     <row r="31" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="C31" s="7">
-        <f>SUM(B5:AH5)</f>
-        <v>0.48281400000000008</v>
-      </c>
-      <c r="Z31" s="8">
-        <v>0.441</v>
-      </c>
-      <c r="AA31" s="7">
-        <v>0</v>
-      </c>
+      <c r="A31" s="7">
+        <f t="shared" si="0"/>
+        <v>0.27443286518432708</v>
+      </c>
+      <c r="Z31" s="8"/>
     </row>
     <row r="32" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="C32" s="7">
-        <f>SUM(B6:AH6)</f>
-        <v>0.63986399999999988</v>
-      </c>
-      <c r="Z32" s="8">
-        <v>0.441</v>
-      </c>
-      <c r="AA32" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="3:27" x14ac:dyDescent="0.3">
-      <c r="C33" s="7">
-        <f>SUM(B7:AH7)</f>
-        <v>0.72656399999999988</v>
-      </c>
-      <c r="Z33" s="8">
-        <v>0.441</v>
-      </c>
-      <c r="AA33" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="3:27" x14ac:dyDescent="0.3">
-      <c r="C34" s="7">
-        <f>SUM(B8:AH8)</f>
-        <v>0.81411399999999989</v>
-      </c>
-      <c r="Z34" s="8">
-        <v>0.441</v>
-      </c>
-      <c r="AA34" s="7">
-        <v>8.0000000000000002E-3</v>
-      </c>
-    </row>
-    <row r="35" spans="3:27" x14ac:dyDescent="0.3">
-      <c r="C35" s="7">
-        <f>SUM(B9:AH9)</f>
-        <v>2.1036970292500001</v>
-      </c>
-      <c r="Z35" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA35" s="7">
-        <v>7.4999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="3:27" x14ac:dyDescent="0.3">
-      <c r="C36" s="7">
-        <f>SUM(B10:AH10)</f>
-        <v>3.6855196082499999</v>
-      </c>
-      <c r="Z36" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA36" s="7">
-        <v>0.17699999999999999</v>
-      </c>
-    </row>
-    <row r="37" spans="3:27" x14ac:dyDescent="0.3">
-      <c r="C37" s="7">
-        <f>SUM(B11:AH11)</f>
-        <v>5.0920813375000025</v>
-      </c>
-      <c r="Z37" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA37" s="7">
-        <v>0.28000000000000003</v>
-      </c>
-    </row>
-    <row r="38" spans="3:27" x14ac:dyDescent="0.3">
-      <c r="C38" s="7">
-        <f>SUM(B12:AH12)</f>
-        <v>7.4582971000000011</v>
-      </c>
-      <c r="Z38" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA38" s="7">
-        <v>0.38600000000000001</v>
-      </c>
-    </row>
-    <row r="39" spans="3:27" x14ac:dyDescent="0.3">
-      <c r="C39" s="7">
-        <f>SUM(B13:AH13)</f>
-        <v>1.2826433499999996</v>
-      </c>
-      <c r="Z39" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA39" s="7">
-        <v>0.47499999999999998</v>
-      </c>
-    </row>
-    <row r="40" spans="3:27" x14ac:dyDescent="0.3">
-      <c r="C40" s="7">
-        <f>SUM(B14:AH14)</f>
-        <v>1.0203896625</v>
-      </c>
-      <c r="Z40" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA40" s="7">
-        <v>0.52600000000000002</v>
-      </c>
-    </row>
-    <row r="41" spans="3:27" x14ac:dyDescent="0.3">
-      <c r="C41" s="7">
-        <f>SUM(B15:AH15)</f>
-        <v>0.94076399999999982</v>
-      </c>
-      <c r="Z41" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA41" s="7">
-        <v>0.53100000000000003</v>
-      </c>
-    </row>
-    <row r="42" spans="3:27" x14ac:dyDescent="0.3">
-      <c r="C42" s="7">
-        <f>SUM(B16:AH16)</f>
-        <v>0.88381399999999977</v>
-      </c>
-      <c r="Z42" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA42" s="7">
-        <v>0.52400000000000002</v>
-      </c>
-    </row>
-    <row r="43" spans="3:27" x14ac:dyDescent="0.3">
-      <c r="C43" s="7">
-        <f>SUM(B17:AH17)</f>
-        <v>0.82710050824999992</v>
-      </c>
-      <c r="Z43" s="8">
-        <v>0.58399999999999996</v>
-      </c>
-      <c r="AA43" s="7">
-        <v>0.48699999999999999</v>
-      </c>
-    </row>
-    <row r="44" spans="3:27" x14ac:dyDescent="0.3">
-      <c r="C44" s="7">
-        <f>SUM(B18:AH18)</f>
-        <v>1.7234262124999999</v>
-      </c>
-      <c r="Z44" s="8">
-        <v>0.58399999999999996</v>
-      </c>
-      <c r="AA44" s="7">
-        <v>0.42899999999999999</v>
-      </c>
-    </row>
-    <row r="45" spans="3:27" x14ac:dyDescent="0.3">
-      <c r="C45" s="7">
-        <f>SUM(B19:AH19)</f>
-        <v>2.9990951582499985</v>
-      </c>
-      <c r="Z45" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA45" s="7">
-        <v>0.36199999999999999</v>
-      </c>
-    </row>
-    <row r="46" spans="3:27" x14ac:dyDescent="0.3">
-      <c r="C46" s="7">
+      <c r="A32" s="7">
+        <f t="shared" si="0"/>
+        <v>0.13006693610436743</v>
+      </c>
+      <c r="Z32" s="8"/>
+    </row>
+    <row r="33" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A33" s="7">
+        <f t="shared" si="0"/>
+        <v>7.0799965219380881E-2</v>
+      </c>
+      <c r="Z33" s="8"/>
+    </row>
+    <row r="34" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A34" s="7">
+        <f t="shared" si="0"/>
+        <v>0.18533290895485199</v>
+      </c>
+      <c r="Z34" s="8"/>
+    </row>
+    <row r="35" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A35" s="7">
+        <f t="shared" si="0"/>
+        <v>1.3912823165298855</v>
+      </c>
+      <c r="C35" s="13"/>
+      <c r="Z35" s="8"/>
+    </row>
+    <row r="36" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A36" s="7">
+        <f t="shared" si="0"/>
+        <v>0.65203267968769163</v>
+      </c>
+      <c r="Z36" s="8"/>
+    </row>
+    <row r="37" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A37" s="7">
+        <f t="shared" si="0"/>
+        <v>0.63463268823547114</v>
+      </c>
+      <c r="Z37" s="8"/>
+    </row>
+    <row r="38" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A38" s="7">
+        <f t="shared" si="0"/>
+        <v>0.58276671371473088</v>
+      </c>
+      <c r="Z38" s="8"/>
+    </row>
+    <row r="39" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A39" s="7">
+        <f t="shared" si="0"/>
+        <v>0.33769983410430698</v>
+      </c>
+      <c r="Z39" s="8"/>
+    </row>
+    <row r="40" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A40" s="7">
+        <f t="shared" si="0"/>
+        <v>9.3199954215343203E-2</v>
+      </c>
+      <c r="Z40" s="8"/>
+    </row>
+    <row r="41" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A41" s="7">
+        <f t="shared" si="0"/>
+        <v>0.10719994733781968</v>
+      </c>
+      <c r="Z41" s="8"/>
+    </row>
+    <row r="42" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A42" s="7">
+        <f t="shared" si="0"/>
+        <v>0.1097999460605653</v>
+      </c>
+      <c r="Z42" s="8"/>
+    </row>
+    <row r="43" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A43" s="7">
+        <f t="shared" si="0"/>
+        <v>0.21759989310363387</v>
+      </c>
+      <c r="Z43" s="8"/>
+    </row>
+    <row r="44" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A44" s="7">
+        <f t="shared" si="0"/>
+        <v>0.44901677941964313</v>
+      </c>
+      <c r="Z44" s="8"/>
+    </row>
+    <row r="45" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A45" s="7">
+        <f t="shared" si="0"/>
+        <v>1.0476994853156123</v>
+      </c>
+      <c r="Z45" s="8"/>
+    </row>
+    <row r="46" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A46" s="7">
         <f>SUM(B20:AH20)</f>
-        <v>2.4540900417499998</v>
-      </c>
-      <c r="Z46" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA46" s="7">
-        <v>0.26300000000000001</v>
-      </c>
-    </row>
-    <row r="47" spans="3:27" x14ac:dyDescent="0.3">
-      <c r="C47" s="7">
-        <f>SUM(B21:AH21)</f>
-        <v>2.08541677925</v>
-      </c>
-      <c r="Z47" s="8">
-        <v>0.47599999999999998</v>
-      </c>
-      <c r="AA47" s="7">
-        <v>0.151</v>
-      </c>
-    </row>
-    <row r="48" spans="3:27" x14ac:dyDescent="0.3">
-      <c r="C48" s="7">
-        <f>SUM(B22:AH22)</f>
-        <v>1.7724499667500004</v>
-      </c>
-      <c r="Z48" s="8">
-        <v>0.47599999999999998</v>
-      </c>
-      <c r="AA48" s="7">
-        <v>6.5000000000000002E-2</v>
-      </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.3">
-      <c r="C49" s="7">
-        <f>SUM(B23:AH23)</f>
-        <v>2.03244194575</v>
-      </c>
-      <c r="Z49" s="8">
-        <v>0.47599999999999998</v>
-      </c>
-      <c r="AA49" s="7">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.3">
-      <c r="C50" s="7">
-        <f>SUM(B24:AH24)</f>
-        <v>2.4538162792499998</v>
-      </c>
-      <c r="Z50" s="8">
-        <v>0.47599999999999998</v>
-      </c>
-      <c r="AA50" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.3">
-      <c r="C51" s="7">
-        <f>SUM(B25:AH25)</f>
-        <v>0.66370445500000008</v>
-      </c>
-      <c r="Z51" s="8">
-        <v>0.47599999999999998</v>
-      </c>
-      <c r="AA51" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.3">
-      <c r="Z52" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA52" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.3">
-      <c r="Z53" s="8">
-        <v>0.441</v>
-      </c>
-      <c r="AA53" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.3">
-      <c r="Z54" s="8">
-        <v>0.441</v>
-      </c>
-      <c r="AA54" s="7">
-        <v>0</v>
-      </c>
+        <v>1.1567324317529679</v>
+      </c>
+      <c r="Z46" s="8"/>
+    </row>
+    <row r="47" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A47" s="7">
+        <f t="shared" si="0"/>
+        <v>0.65523267811568653</v>
+      </c>
+      <c r="Z47" s="8"/>
+    </row>
+    <row r="48" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A48" s="7">
+        <f t="shared" si="0"/>
+        <v>0.57831671590080069</v>
+      </c>
+      <c r="Z48" s="8"/>
+    </row>
+    <row r="49" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A49" s="7">
+        <f t="shared" si="0"/>
+        <v>0.54359973295558539</v>
+      </c>
+      <c r="Z49" s="8"/>
+    </row>
+    <row r="50" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A50" s="7">
+        <f t="shared" si="0"/>
+        <v>0.46329977240309561</v>
+      </c>
+      <c r="Z50" s="8"/>
+    </row>
+    <row r="51" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A51" s="7">
+        <f t="shared" si="0"/>
+        <v>0.22523288935390981</v>
+      </c>
+      <c r="Z51" s="8"/>
+    </row>
+    <row r="52" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="Z52" s="8"/>
+    </row>
+    <row r="53" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="Z53" s="8"/>
+    </row>
+    <row r="54" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="Z54" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5193,6 +3536,10 @@
       <c r="C7" s="7">
         <v>0.17699999999999999</v>
       </c>
+      <c r="E7">
+        <f>SUM(C2:C25)</f>
+        <v>4.7489999999999997</v>
+      </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
     </row>
@@ -5811,7 +4158,7 @@
         <v>4.7699999999999999E-2</v>
       </c>
       <c r="F2" s="8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J2" s="12"/>
       <c r="K2" s="12"/>
@@ -5836,7 +4183,7 @@
         <v>0.25109999999999999</v>
       </c>
       <c r="F3" s="8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J3" s="8"/>
       <c r="K3" s="8"/>
@@ -5861,7 +4208,7 @@
         <v>0.18640000000000001</v>
       </c>
       <c r="F4" s="8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J4" s="8"/>
       <c r="K4" s="8"/>
@@ -5887,7 +4234,7 @@
         <v>0.19409999999999999</v>
       </c>
       <c r="F5" s="8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J5" s="8"/>
       <c r="K5" s="8"/>
@@ -5913,7 +4260,7 @@
         <v>0.70699999999999996</v>
       </c>
       <c r="F6" s="8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J6" s="8"/>
       <c r="K6" s="8"/>
@@ -5939,7 +4286,7 @@
         <v>0.61880000000000002</v>
       </c>
       <c r="F7" s="8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
@@ -5965,7 +4312,7 @@
         <v>0.2351</v>
       </c>
       <c r="F8" s="8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J8" s="8"/>
       <c r="K8" s="8"/>
@@ -5991,7 +4338,7 @@
         <v>0.74</v>
       </c>
       <c r="F9" s="8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J9" s="8"/>
       <c r="K9" s="8"/>
@@ -6017,7 +4364,7 @@
         <v>0.74</v>
       </c>
       <c r="F10" s="8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J10" s="8"/>
       <c r="K10" s="8"/>
@@ -6043,7 +4390,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="F11" s="8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J11" s="8"/>
       <c r="K11" s="8"/>
@@ -6069,7 +4416,7 @@
         <v>0.12379999999999999</v>
       </c>
       <c r="F12" s="8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J12" s="8"/>
       <c r="K12" s="8"/>
@@ -6095,7 +4442,7 @@
         <v>1.155</v>
       </c>
       <c r="F13" s="8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J13" s="8"/>
       <c r="K13" s="8"/>
@@ -6121,7 +4468,7 @@
         <v>0.71289999999999998</v>
       </c>
       <c r="F14" s="8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J14" s="8"/>
       <c r="K14" s="8"/>
@@ -6147,7 +4494,7 @@
         <v>0.52600000000000002</v>
       </c>
       <c r="F15" s="8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J15" s="8"/>
       <c r="K15" s="8"/>
@@ -6173,7 +4520,7 @@
         <v>0.54500000000000004</v>
       </c>
       <c r="F16" s="8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J16" s="8"/>
       <c r="K16" s="8"/>
@@ -6199,7 +4546,7 @@
         <v>1.7210000000000001</v>
       </c>
       <c r="F17" s="8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
@@ -6225,7 +4572,7 @@
         <v>0.57399999999999995</v>
       </c>
       <c r="F18" s="8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J18" s="8"/>
       <c r="K18" s="8"/>
@@ -6251,7 +4598,7 @@
         <v>0.1565</v>
       </c>
       <c r="F19" s="8">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="J19" s="8"/>
       <c r="K19" s="8"/>
@@ -6277,7 +4624,7 @@
         <v>1.3553999999999999</v>
       </c>
       <c r="F20" s="8">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="J20" s="8"/>
       <c r="K20" s="8"/>
@@ -6303,7 +4650,7 @@
         <v>0.47839999999999999</v>
       </c>
       <c r="F21" s="8">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="J21" s="8"/>
       <c r="K21" s="8"/>
@@ -6329,7 +4676,7 @@
         <v>0.93730000000000002</v>
       </c>
       <c r="F22" s="8">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="J22" s="8"/>
       <c r="K22" s="8"/>
@@ -6355,7 +4702,7 @@
         <v>0.30830000000000002</v>
       </c>
       <c r="F23" s="8">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="J23" s="8"/>
       <c r="K23" s="8"/>
@@ -6381,7 +4728,7 @@
         <v>0.70909999999999995</v>
       </c>
       <c r="F24" s="8">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="J24" s="8"/>
       <c r="K24" s="8"/>
@@ -6407,7 +4754,7 @@
         <v>0.70109999999999995</v>
       </c>
       <c r="F25" s="8">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="J25" s="8"/>
       <c r="K25" s="8"/>
@@ -6433,7 +4780,7 @@
         <v>0.10340000000000001</v>
       </c>
       <c r="F26" s="8">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="H26" s="8"/>
       <c r="J26" s="8"/>
@@ -6460,7 +4807,7 @@
         <v>0.1447</v>
       </c>
       <c r="F27" s="8">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="J27" s="8"/>
       <c r="K27" s="8"/>
@@ -6486,7 +4833,7 @@
         <v>0.93369999999999997</v>
       </c>
       <c r="F28" s="8">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="J28" s="8"/>
       <c r="K28" s="8"/>
@@ -6512,7 +4859,7 @@
         <v>0.7006</v>
       </c>
       <c r="F29" s="8">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="J29" s="8"/>
       <c r="K29" s="8"/>
@@ -6538,7 +4885,7 @@
         <v>0.25850000000000001</v>
       </c>
       <c r="F30" s="8">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="J30" s="8"/>
       <c r="K30" s="8"/>
@@ -6564,7 +4911,7 @@
         <v>0.96299999999999997</v>
       </c>
       <c r="F31" s="8">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="J31" s="8"/>
       <c r="K31" s="8"/>
@@ -6590,7 +4937,7 @@
         <v>0.3619</v>
       </c>
       <c r="F32" s="8">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="J32" s="8"/>
       <c r="K32" s="8"/>
@@ -6616,7 +4963,7 @@
         <v>0.5302</v>
       </c>
       <c r="F33" s="8">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="J33" s="8"/>
       <c r="K33" s="8"/>
@@ -6626,6 +4973,9 @@
       <c r="O33" s="6"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
       <c r="J34" s="8"/>
       <c r="K34" s="8"/>
       <c r="L34" s="8"/>
@@ -6634,6 +4984,8 @@
       <c r="O34" s="6"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
       <c r="K35" s="6"/>
       <c r="L35" s="6"/>
       <c r="M35" s="6"/>
@@ -6641,6 +4993,8 @@
       <c r="O35" s="6"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
       <c r="K36" s="6"/>
       <c r="L36" s="6"/>
       <c r="M36" s="6"/>

--- a/Inputs/Time_Series.xlsx
+++ b/Inputs/Time_Series.xlsx
@@ -152,214 +152,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:val>
-            <c:numRef>
-              <c:f>load_profile!$A$28:$A$51</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
-                <c:pt idx="0">
-                  <c:v>6.4599968265141319E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>9.9399951169582765E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.15349992459286682</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.27443286518432708</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.13006693610436743</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>7.0799965219380881E-2</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.18533290895485199</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1.3912823165298855</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.65203267968769163</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.63463268823547114</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.58276671371473088</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.33769983410430698</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>9.3199954215343203E-2</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.10719994733781968</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.1097999460605653</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.21759989310363387</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.44901677941964313</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>1.0476994853156123</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1.1567324317529679</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.65523267811568653</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.57831671590080069</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.54359973295558539</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.46329977240309561</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.22523288935390981</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:marker val="1"/>
-        <c:smooth val="0"/>
-        <c:axId val="145281792"/>
-        <c:axId val="145284096"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="145281792"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="145284096"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="145284096"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="145281792"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:layout/>
-      <c:overlay val="0"/>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>17929</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>94129</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>466165</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>147918</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="Chart 5"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3275,7 +3067,7 @@
     </row>
     <row r="29" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A29" s="7">
-        <f t="shared" ref="A29:A52" si="0">SUM(B3:AH3)</f>
+        <f t="shared" ref="A29:A51" si="0">SUM(B3:AH3)</f>
         <v>9.9399951169582765E-2</v>
       </c>
     </row>
@@ -3445,7 +3237,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
